--- a/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
+++ b/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
@@ -15,50 +15,164 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="89">
   <si>
     <t>AT32F415RBT7_WorkBench</t>
   </si>
   <si>
-    <t>lto-llvm-51078c.o</t>
+    <t>lcd.o</t>
   </si>
   <si>
     <t>startup_at32f415.o</t>
   </si>
   <si>
+    <t>ha01_handle.o</t>
+  </si>
+  <si>
+    <t>tmt.o</t>
+  </si>
+  <si>
+    <t>encoderec11.o</t>
+  </si>
+  <si>
+    <t>key_handle.o</t>
+  </si>
+  <si>
+    <t>output_handle.o</t>
+  </si>
+  <si>
+    <t>lcd_handle.o</t>
+  </si>
+  <si>
+    <t>adc_filter.o</t>
+  </si>
+  <si>
+    <t>pid_operation.o</t>
+  </si>
+  <si>
+    <t>at32_usart.o</t>
+  </si>
+  <si>
+    <t>flash_handle.o</t>
+  </si>
+  <si>
+    <t>beep.o</t>
+  </si>
+  <si>
+    <t>at32f415_int.o</t>
+  </si>
+  <si>
+    <t>ec11_handle.o</t>
+  </si>
+  <si>
+    <t>wk_system.o</t>
+  </si>
+  <si>
+    <t>system_at32f415.o</t>
+  </si>
+  <si>
+    <t>main.o</t>
+  </si>
+  <si>
+    <t>key.o</t>
+  </si>
+  <si>
     <t>mf_w.l</t>
   </si>
   <si>
+    <t>at32f415_crm.o</t>
+  </si>
+  <si>
+    <t>at32f415_tmr.o</t>
+  </si>
+  <si>
+    <t>at32f415_wk_config.o</t>
+  </si>
+  <si>
+    <t>at32_spiflash.o</t>
+  </si>
+  <si>
+    <t>wk_tmr.o</t>
+  </si>
+  <si>
+    <t>at32f415_adc.o</t>
+  </si>
+  <si>
     <t>dadd.o</t>
   </si>
   <si>
+    <t>at32f415_usart.o</t>
+  </si>
+  <si>
     <t>mc_w.l</t>
   </si>
   <si>
+    <t>at32f415_spi.o</t>
+  </si>
+  <si>
+    <t>at32f415_dma.o</t>
+  </si>
+  <si>
+    <t>wk_gpio.o</t>
+  </si>
+  <si>
+    <t>at32f415_gpio.o</t>
+  </si>
+  <si>
     <t>dmul.o</t>
   </si>
   <si>
     <t>ddiv.o</t>
   </si>
   <si>
+    <t>at32f415_flash.o</t>
+  </si>
+  <si>
     <t>depilogue.o</t>
   </si>
   <si>
     <t>fadd.o</t>
   </si>
   <si>
+    <t>at32f415_misc.o</t>
+  </si>
+  <si>
+    <t>wk_adc.o</t>
+  </si>
+  <si>
     <t>fdiv.o</t>
   </si>
   <si>
+    <t>wk_usart.o</t>
+  </si>
+  <si>
+    <t>wk_spi.o</t>
+  </si>
+  <si>
     <t>fepilogue.o</t>
   </si>
   <si>
     <t>fmul.o</t>
   </si>
   <si>
+    <t>at32f415_crc.o</t>
+  </si>
+  <si>
+    <t>util_queue.o</t>
+  </si>
+  <si>
+    <t>__dczerorl2.o</t>
+  </si>
+  <si>
+    <t>wk_dma.o</t>
+  </si>
+  <si>
     <t>dfixi.o</t>
   </si>
   <si>
+    <t>at32f415_wdt.o</t>
+  </si>
+  <si>
     <t>d2f.o</t>
   </si>
   <si>
@@ -71,9 +185,15 @@
     <t>init.o</t>
   </si>
   <si>
+    <t>wk_crc.o</t>
+  </si>
+  <si>
     <t>ffixui.o</t>
   </si>
   <si>
+    <t>flash.o</t>
+  </si>
+  <si>
     <t>f2d.o</t>
   </si>
   <si>
@@ -107,12 +227,18 @@
     <t>fcmpeq.o</t>
   </si>
   <si>
+    <t>wk_wdt.o</t>
+  </si>
+  <si>
     <t>dfltui.o</t>
   </si>
   <si>
     <t>fflti.o</t>
   </si>
   <si>
+    <t>wk_debug.o</t>
+  </si>
+  <si>
     <t>ffltui.o</t>
   </si>
   <si>
@@ -120,6 +246,9 @@
   </si>
   <si>
     <t>entry2.o</t>
+  </si>
+  <si>
+    <t>beep_handle.o</t>
   </si>
   <si>
     <t>entry5.o</t>
@@ -242,16 +371,67 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>ram_percent!$A$3:$A$38</c:f>
+              <c:f>ram_percent!$A$3:$A$81</c:f>
               <c:strCache>
-                <c:ptCount val="36"/>
+                <c:ptCount val="79"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-51078c.o</c:v>
+                  <c:v>lcd.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>startup_at32f415.o</c:v>
                 </c:pt>
-                <c:pt idx="35">
+                <c:pt idx="2">
+                  <c:v>ha01_handle.o</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>tmt.o</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>encoderec11.o</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>key_handle.o</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>output_handle.o</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>lcd_handle.o</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>adc_filter.o</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>pid_operation.o</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>at32_usart.o</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>flash_handle.o</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>beep.o</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>at32f415_int.o</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>ec11_handle.o</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>wk_system.o</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>system_at32f415.o</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>main.o</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>key.o</c:v>
+                </c:pt>
+                <c:pt idx="78">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -259,17 +439,68 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ram_percent!$B$3:$B$38</c:f>
+              <c:f>ram_percent!$B$3:$B$81</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="36"/>
+                <c:ptCount val="79"/>
                 <c:pt idx="0">
-                  <c:v>70.98328399658203</c:v>
+                  <c:v>27.70539665222168</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>29.0167179107666</c:v>
-                </c:pt>
-                <c:pt idx="35">
+                  <c:v>27.2268009185791</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>25.95054435729981</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.935123682022095</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.031108856201172</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.791810750961304</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.632278680801392</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.409199714660645</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.276256322860718</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.169901609420776</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.9571922421455383</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.6381281614303589</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.4520074427127838</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.3722414374351502</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.1329433619976044</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.1063546910881996</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.1063546910881996</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.07976602017879486</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.0265886727720499</c:v>
+                </c:pt>
+                <c:pt idx="78">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -337,115 +568,244 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>flash_percent!$A$3:$A$38</c:f>
+              <c:f>flash_percent!$A$3:$A$81</c:f>
               <c:strCache>
-                <c:ptCount val="36"/>
+                <c:ptCount val="79"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-51078c.o</c:v>
+                  <c:v>lcd.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>lcd_handle.o</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>ec11_handle.o</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>mf_w.l</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
+                  <c:v>flash_handle.o</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>key_handle.o</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>output_handle.o</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>at32f415_crm.o</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>encoderec11.o</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>at32f415_tmr.o</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>main.o</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>at32f415_int.o</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>startup_at32f415.o</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="13">
+                  <c:v>tmt.o</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>at32f415_wk_config.o</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>at32_spiflash.o</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>wk_tmr.o</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>at32f415_adc.o</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>dadd.o</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="19">
+                  <c:v>at32f415_usart.o</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>mc_w.l</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="21">
+                  <c:v>at32f415_spi.o</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>system_at32f415.o</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>pid_operation.o</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>at32f415_dma.o</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>wk_gpio.o</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>at32f415_gpio.o</c:v>
+                </c:pt>
+                <c:pt idx="27">
                   <c:v>dmul.o</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="28">
                   <c:v>ddiv.o</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="29">
+                  <c:v>at32f415_flash.o</c:v>
+                </c:pt>
+                <c:pt idx="30">
                   <c:v>depilogue.o</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="31">
+                  <c:v>adc_filter.o</c:v>
+                </c:pt>
+                <c:pt idx="32">
                   <c:v>fadd.o</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="33">
+                  <c:v>at32f415_misc.o</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>ha01_handle.o</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>key.o</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>beep.o</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>wk_adc.o</c:v>
+                </c:pt>
+                <c:pt idx="38">
                   <c:v>fdiv.o</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="39">
+                  <c:v>wk_usart.o</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>wk_spi.o</c:v>
+                </c:pt>
+                <c:pt idx="41">
                   <c:v>fepilogue.o</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="42">
+                  <c:v>wk_system.o</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>at32_usart.o</c:v>
+                </c:pt>
+                <c:pt idx="44">
                   <c:v>fmul.o</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="45">
+                  <c:v>at32f415_crc.o</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>util_queue.o</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>__dczerorl2.o</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>wk_dma.o</c:v>
+                </c:pt>
+                <c:pt idx="49">
                   <c:v>dfixi.o</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="50">
+                  <c:v>at32f415_wdt.o</c:v>
+                </c:pt>
+                <c:pt idx="51">
                   <c:v>d2f.o</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="52">
                   <c:v>ffixi.o</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="53">
                   <c:v>dfixui.o</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="54">
                   <c:v>init.o</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="55">
+                  <c:v>wk_crc.o</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>ffixui.o</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="57">
+                  <c:v>flash.o</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>f2d.o</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="59">
                   <c:v>memseta.o</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="60">
                   <c:v>llsshr.o</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="61">
                   <c:v>llushr.o</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="62">
                   <c:v>llshl.o</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="63">
                   <c:v>handlers.o</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="64">
                   <c:v>fcmplt.o</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="65">
                   <c:v>fcmple.o</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="66">
                   <c:v>fcmpgt.o</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="67">
                   <c:v>fcmpge.o</c:v>
                 </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="68">
                   <c:v>fcmpeq.o</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="69">
+                  <c:v>wk_wdt.o</c:v>
+                </c:pt>
+                <c:pt idx="70">
                   <c:v>dfltui.o</c:v>
                 </c:pt>
-                <c:pt idx="30">
+                <c:pt idx="71">
                   <c:v>fflti.o</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="72">
+                  <c:v>wk_debug.o</c:v>
+                </c:pt>
+                <c:pt idx="73">
                   <c:v>ffltui.o</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="74">
                   <c:v>entry9a.o</c:v>
                 </c:pt>
-                <c:pt idx="33">
+                <c:pt idx="75">
                   <c:v>entry2.o</c:v>
                 </c:pt>
-                <c:pt idx="34">
+                <c:pt idx="76">
+                  <c:v>beep_handle.o</c:v>
+                </c:pt>
+                <c:pt idx="77">
                   <c:v>entry5.o</c:v>
                 </c:pt>
-                <c:pt idx="35">
+                <c:pt idx="78">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -453,116 +813,245 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>flash_percent!$B$3:$B$38</c:f>
+              <c:f>flash_percent!$B$3:$B$81</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="36"/>
+                <c:ptCount val="79"/>
                 <c:pt idx="0">
-                  <c:v>95.18217468261719</c:v>
+                  <c:v>74.48508453369141</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.974027037620544</c:v>
+                  <c:v>4.40053653717041</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.4048258364200592</c:v>
+                  <c:v>3.123021364212036</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.3346827626228333</c:v>
+                  <c:v>1.834332704544067</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.2324742525815964</c:v>
+                  <c:v>1.782189249992371</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.2284660637378693</c:v>
+                  <c:v>1.687213659286499</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.2224538028240204</c:v>
+                  <c:v>1.460017085075378</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.1863802224397659</c:v>
+                  <c:v>0.709523618221283</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.1763597726821899</c:v>
+                  <c:v>0.6629669666290283</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.12425347417593</c:v>
+                  <c:v>0.597787618637085</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.1102248579263687</c:v>
+                  <c:v>0.5065365433692932</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.1002044156193733</c:v>
+                  <c:v>0.4078364074230194</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.06212673708796501</c:v>
+                  <c:v>0.3761778771877289</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.05611447244882584</c:v>
+                  <c:v>0.3631420135498047</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.05010220780968666</c:v>
+                  <c:v>0.3482438921928406</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.05010220780968666</c:v>
+                  <c:v>0.3352080285549164</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.0480981208384037</c:v>
+                  <c:v>0.3333457410335541</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.04008176550269127</c:v>
+                  <c:v>0.3277589380741119</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.03807767853140831</c:v>
+                  <c:v>0.3109985589981079</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.03607359156012535</c:v>
+                  <c:v>0.3035494685173035</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.03607359156012535</c:v>
+                  <c:v>0.2961004078388214</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.03206541389226914</c:v>
+                  <c:v>0.2942381501197815</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.03006132505834103</c:v>
+                  <c:v>0.2905136048793793</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.03006132505834103</c:v>
+                  <c:v>0.2588550746440888</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.02805723622441292</c:v>
+                  <c:v>0.2495437413454056</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.02805723622441292</c:v>
+                  <c:v>0.2458192110061646</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.02805723622441292</c:v>
+                  <c:v>0.2439569383859634</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.02805723622441292</c:v>
+                  <c:v>0.2122984081506729</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.02805723622441292</c:v>
+                  <c:v>0.2067116051912308</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.02605314925312996</c:v>
+                  <c:v>0.1974002718925476</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.01803679578006268</c:v>
+                  <c:v>0.1731908023357391</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.01002044137567282</c:v>
+                  <c:v>0.1676040142774582</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.008016353473067284</c:v>
+                  <c:v>0.163879469037056</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.008016353473067284</c:v>
+                  <c:v>0.163879469037056</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.004008176736533642</c:v>
+                  <c:v>0.1564304083585739</c:v>
                 </c:pt>
                 <c:pt idx="35">
+                  <c:v>0.1461879462003708</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.1387388706207275</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.1340832114219666</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.1154605373740196</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.1117360070347786</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.1117360070347786</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.1024246737360954</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.1005624011158943</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.1005624011158943</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.09311334043741226</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.09311334043741226</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.08193973451852799</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.08007746934890747</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.05959253758192062</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.05773026868700981</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.0558680035173893</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.05214346945285797</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.04655667021870613</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.04655667021870613</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.04469440132379532</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.04469440132379532</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.03724533319473267</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.03724533319473267</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.03538306802511215</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.03352080285549164</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.03352080285549164</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.02979626879096031</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.02793400175869465</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.02793400175869465</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.02607173472642899</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.02607173472642899</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.02607173472642899</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.02607173472642899</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.02607173472642899</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.02607173472642899</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.02420946769416332</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.01676040142774582</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.01117360033094883</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.009311333298683167</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.007449067197740078</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.007449067197740078</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.007449067197740078</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.003724533598870039</c:v>
+                </c:pt>
+                <c:pt idx="78">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -667,8 +1156,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H38" totalsRowCount="1">
-  <autoFilter ref="A2:H37"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H81" totalsRowCount="1">
+  <autoFilter ref="A2:H80"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="ram_percent" totalsRowFunction="sum"/>
@@ -684,8 +1173,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H38" totalsRowCount="1">
-  <autoFilter ref="A2:H37"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H81" totalsRowCount="1">
+  <autoFilter ref="A2:H80"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="flash_percent" totalsRowFunction="sum"/>
@@ -985,7 +1474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -998,28 +1487,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>79</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
-        <v>41</v>
+        <v>84</v>
       </c>
       <c r="F2" t="s">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="G2" t="s">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="H2" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1027,25 +1516,25 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>70.98328399658203</v>
+        <v>27.70539665222168</v>
       </c>
       <c r="C3" s="1">
-        <v>2505</v>
+        <v>1042</v>
       </c>
       <c r="D3" s="1">
-        <v>94988</v>
+        <v>79994</v>
       </c>
       <c r="E3" s="1">
-        <v>19408</v>
+        <v>3520</v>
       </c>
       <c r="F3" s="1">
-        <v>75388</v>
+        <v>76474</v>
       </c>
       <c r="G3" s="1">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="H3" s="1">
-        <v>2313</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1053,7 +1542,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>29.0167179107666</v>
+        <v>27.2268009185791</v>
       </c>
       <c r="C4" s="1">
         <v>1024</v>
@@ -1074,35 +1563,477 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
-      <c r="A38" t="s">
-        <v>37</v>
-      </c>
-      <c r="B38">
+    <row r="5" spans="1:8">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2">
+        <v>25.95054435729981</v>
+      </c>
+      <c r="C5" s="1">
+        <v>976</v>
+      </c>
+      <c r="D5" s="1">
+        <v>168</v>
+      </c>
+      <c r="E5" s="1">
+        <v>168</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2">
+        <v>3.935123682022095</v>
+      </c>
+      <c r="C6" s="1">
+        <v>148</v>
+      </c>
+      <c r="D6" s="1">
+        <v>390</v>
+      </c>
+      <c r="E6" s="1">
+        <v>390</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2">
+        <v>3.031108856201172</v>
+      </c>
+      <c r="C7" s="1">
+        <v>114</v>
+      </c>
+      <c r="D7" s="1">
+        <v>712</v>
+      </c>
+      <c r="E7" s="1">
+        <v>600</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>112</v>
+      </c>
+      <c r="H7" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2">
+        <v>2.791810750961304</v>
+      </c>
+      <c r="C8" s="1">
+        <v>105</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1812</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1708</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>104</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2">
+        <v>2.632278680801392</v>
+      </c>
+      <c r="C9" s="1">
+        <v>99</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1568</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1486</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>82</v>
+      </c>
+      <c r="H9" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2">
+        <v>1.409199714660645</v>
+      </c>
+      <c r="C10" s="1">
+        <v>53</v>
+      </c>
+      <c r="D10" s="1">
+        <v>4726</v>
+      </c>
+      <c r="E10" s="1">
+        <v>4702</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1">
+        <v>24</v>
+      </c>
+      <c r="H10" s="1">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2">
+        <v>1.276256322860718</v>
+      </c>
+      <c r="C11" s="1">
+        <v>48</v>
+      </c>
+      <c r="D11" s="1">
+        <v>180</v>
+      </c>
+      <c r="E11" s="1">
+        <v>180</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2">
+        <v>1.169901609420776</v>
+      </c>
+      <c r="C12" s="1">
+        <v>44</v>
+      </c>
+      <c r="D12" s="1">
+        <v>278</v>
+      </c>
+      <c r="E12" s="1">
+        <v>278</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0.9571922421455383</v>
+      </c>
+      <c r="C13" s="1">
+        <v>36</v>
+      </c>
+      <c r="D13" s="1">
+        <v>108</v>
+      </c>
+      <c r="E13" s="1">
+        <v>108</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0.6381281614303589</v>
+      </c>
+      <c r="C14" s="1">
+        <v>24</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1914</v>
+      </c>
+      <c r="E14" s="1">
+        <v>1914</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0.4520074427127838</v>
+      </c>
+      <c r="C15" s="1">
+        <v>17</v>
+      </c>
+      <c r="D15" s="1">
+        <v>149</v>
+      </c>
+      <c r="E15" s="1">
+        <v>128</v>
+      </c>
+      <c r="F15" s="1">
+        <v>5</v>
+      </c>
+      <c r="G15" s="1">
+        <v>16</v>
+      </c>
+      <c r="H15" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0.3722414374351502</v>
+      </c>
+      <c r="C16" s="1">
+        <v>14</v>
+      </c>
+      <c r="D16" s="1">
+        <v>438</v>
+      </c>
+      <c r="E16" s="1">
+        <v>432</v>
+      </c>
+      <c r="F16" s="1">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1">
+        <v>6</v>
+      </c>
+      <c r="H16" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2">
+        <v>0.1329433619976044</v>
+      </c>
+      <c r="C17" s="1">
+        <v>5</v>
+      </c>
+      <c r="D17" s="1">
+        <v>3354</v>
+      </c>
+      <c r="E17" s="1">
+        <v>3352</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0</v>
+      </c>
+      <c r="G17" s="1">
+        <v>2</v>
+      </c>
+      <c r="H17" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2">
+        <v>0.1063546910881996</v>
+      </c>
+      <c r="C18" s="1">
+        <v>4</v>
+      </c>
+      <c r="D18" s="1">
+        <v>108</v>
+      </c>
+      <c r="E18" s="1">
+        <v>108</v>
+      </c>
+      <c r="F18" s="1">
+        <v>0</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="2">
+        <v>0.1063546910881996</v>
+      </c>
+      <c r="C19" s="1">
+        <v>4</v>
+      </c>
+      <c r="D19" s="1">
+        <v>312</v>
+      </c>
+      <c r="E19" s="1">
+        <v>308</v>
+      </c>
+      <c r="F19" s="1">
+        <v>0</v>
+      </c>
+      <c r="G19" s="1">
+        <v>4</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="2">
+        <v>0.07976602017879486</v>
+      </c>
+      <c r="C20" s="1">
+        <v>3</v>
+      </c>
+      <c r="D20" s="1">
+        <v>544</v>
+      </c>
+      <c r="E20" s="1">
+        <v>544</v>
+      </c>
+      <c r="F20" s="1">
+        <v>0</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="2">
+        <v>0.0265886727720499</v>
+      </c>
+      <c r="C21" s="1">
+        <v>1</v>
+      </c>
+      <c r="D21" s="1">
+        <v>157</v>
+      </c>
+      <c r="E21" s="1">
+        <v>156</v>
+      </c>
+      <c r="F21" s="1">
+        <v>0</v>
+      </c>
+      <c r="G21" s="1">
+        <v>1</v>
+      </c>
+      <c r="H21" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
+      <c r="A81" t="s">
+        <v>80</v>
+      </c>
+      <c r="B81">
         <f>SUBTOTAL(109,[ram_percent])</f>
         <v>0</v>
       </c>
-      <c r="C38">
+      <c r="C81">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="D38">
+      <c r="D81">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="E38">
+      <c r="E81">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F38">
+      <c r="F81">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G38">
+      <c r="G81">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H38">
+      <c r="H81">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
@@ -1118,7 +2049,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1131,28 +2062,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>79</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="E2" t="s">
-        <v>41</v>
+        <v>84</v>
       </c>
       <c r="F2" t="s">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="G2" t="s">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="H2" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1160,94 +2091,94 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>95.18217468261719</v>
+        <v>74.48508453369141</v>
       </c>
       <c r="C3" s="1">
-        <v>94988</v>
+        <v>79994</v>
       </c>
       <c r="D3" s="1">
-        <v>2505</v>
+        <v>1042</v>
       </c>
       <c r="E3" s="1">
-        <v>19408</v>
+        <v>3520</v>
       </c>
       <c r="F3" s="1">
-        <v>75388</v>
+        <v>76474</v>
       </c>
       <c r="G3" s="1">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="H3" s="1">
-        <v>2313</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B4" s="2">
-        <v>1.974027037620544</v>
+        <v>4.40053653717041</v>
       </c>
       <c r="C4" s="1">
-        <v>1970</v>
+        <v>4726</v>
       </c>
       <c r="D4" s="1">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="E4" s="1">
-        <v>1970</v>
+        <v>4702</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H4" s="1">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="2">
+        <v>3.123021364212036</v>
+      </c>
+      <c r="C5" s="1">
+        <v>3354</v>
+      </c>
+      <c r="D5" s="1">
+        <v>5</v>
+      </c>
+      <c r="E5" s="1">
+        <v>3352</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1">
         <v>2</v>
       </c>
-      <c r="B5" s="2">
-        <v>0.4048258364200592</v>
-      </c>
-      <c r="C5" s="1">
-        <v>404</v>
-      </c>
-      <c r="D5" s="1">
-        <v>1024</v>
-      </c>
-      <c r="E5" s="1">
-        <v>36</v>
-      </c>
-      <c r="F5" s="1">
-        <v>368</v>
-      </c>
-      <c r="G5" s="1">
-        <v>0</v>
-      </c>
       <c r="H5" s="1">
-        <v>1024</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="B6" s="2">
-        <v>0.3346827626228333</v>
+        <v>1.834332704544067</v>
       </c>
       <c r="C6" s="1">
-        <v>334</v>
+        <v>1970</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
       </c>
       <c r="E6" s="1">
-        <v>334</v>
+        <v>1970</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
@@ -1261,19 +2192,19 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B7" s="2">
-        <v>0.2324742525815964</v>
+        <v>1.782189249992371</v>
       </c>
       <c r="C7" s="1">
-        <v>232</v>
+        <v>1914</v>
       </c>
       <c r="D7" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E7" s="1">
-        <v>232</v>
+        <v>1914</v>
       </c>
       <c r="F7" s="1">
         <v>0</v>
@@ -1282,7 +2213,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1290,25 +2221,25 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>0.2284660637378693</v>
+        <v>1.687213659286499</v>
       </c>
       <c r="C8" s="1">
-        <v>228</v>
+        <v>1812</v>
       </c>
       <c r="D8" s="1">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="E8" s="1">
-        <v>228</v>
+        <v>1708</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="H8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1316,45 +2247,45 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.2224538028240204</v>
+        <v>1.460017085075378</v>
       </c>
       <c r="C9" s="1">
-        <v>222</v>
+        <v>1568</v>
       </c>
       <c r="D9" s="1">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="E9" s="1">
-        <v>222</v>
+        <v>1486</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="H9" s="1">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0.709523618221283</v>
+      </c>
+      <c r="C10" s="1">
+        <v>762</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0</v>
+      </c>
+      <c r="E10" s="1">
+        <v>754</v>
+      </c>
+      <c r="F10" s="1">
         <v>8</v>
-      </c>
-      <c r="B10" s="2">
-        <v>0.1863802224397659</v>
-      </c>
-      <c r="C10" s="1">
-        <v>186</v>
-      </c>
-      <c r="D10" s="1">
-        <v>0</v>
-      </c>
-      <c r="E10" s="1">
-        <v>186</v>
-      </c>
-      <c r="F10" s="1">
-        <v>0</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -1365,45 +2296,45 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B11" s="2">
-        <v>0.1763597726821899</v>
+        <v>0.6629669666290283</v>
       </c>
       <c r="C11" s="1">
-        <v>176</v>
+        <v>712</v>
       </c>
       <c r="D11" s="1">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="E11" s="1">
-        <v>176</v>
+        <v>600</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="H11" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B12" s="2">
-        <v>0.12425347417593</v>
+        <v>0.597787618637085</v>
       </c>
       <c r="C12" s="1">
-        <v>124</v>
+        <v>642</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
       </c>
       <c r="E12" s="1">
-        <v>124</v>
+        <v>642</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
@@ -1417,19 +2348,19 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B13" s="2">
-        <v>0.1102248579263687</v>
+        <v>0.5065365433692932</v>
       </c>
       <c r="C13" s="1">
-        <v>110</v>
+        <v>544</v>
       </c>
       <c r="D13" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E13" s="1">
-        <v>110</v>
+        <v>544</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
@@ -1438,76 +2369,76 @@
         <v>0</v>
       </c>
       <c r="H13" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B14" s="2">
-        <v>0.1002044156193733</v>
+        <v>0.4078364074230194</v>
       </c>
       <c r="C14" s="1">
-        <v>100</v>
+        <v>438</v>
       </c>
       <c r="D14" s="1">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E14" s="1">
-        <v>100</v>
+        <v>432</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H14" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B15" s="2">
-        <v>0.06212673708796501</v>
+        <v>0.3761778771877289</v>
       </c>
       <c r="C15" s="1">
-        <v>62</v>
+        <v>404</v>
       </c>
       <c r="D15" s="1">
-        <v>0</v>
+        <v>1024</v>
       </c>
       <c r="E15" s="1">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="F15" s="1">
-        <v>0</v>
+        <v>368</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
       </c>
       <c r="H15" s="1">
-        <v>0</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="B16" s="2">
-        <v>0.05611447244882584</v>
+        <v>0.3631420135498047</v>
       </c>
       <c r="C16" s="1">
-        <v>56</v>
+        <v>390</v>
       </c>
       <c r="D16" s="1">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="E16" s="1">
-        <v>56</v>
+        <v>390</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
@@ -1516,24 +2447,24 @@
         <v>0</v>
       </c>
       <c r="H16" s="1">
-        <v>0</v>
+        <v>148</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B17" s="2">
-        <v>0.05010220780968666</v>
+        <v>0.3482438921928406</v>
       </c>
       <c r="C17" s="1">
-        <v>50</v>
+        <v>374</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
       </c>
       <c r="E17" s="1">
-        <v>50</v>
+        <v>374</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
@@ -1547,19 +2478,19 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B18" s="2">
-        <v>0.05010220780968666</v>
+        <v>0.3352080285549164</v>
       </c>
       <c r="C18" s="1">
-        <v>50</v>
+        <v>360</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
       </c>
       <c r="E18" s="1">
-        <v>50</v>
+        <v>360</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -1573,19 +2504,19 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B19" s="2">
-        <v>0.0480981208384037</v>
+        <v>0.3333457410335541</v>
       </c>
       <c r="C19" s="1">
-        <v>48</v>
+        <v>358</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
       </c>
       <c r="E19" s="1">
-        <v>48</v>
+        <v>358</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
@@ -1599,19 +2530,19 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B20" s="2">
-        <v>0.04008176550269127</v>
+        <v>0.3277589380741119</v>
       </c>
       <c r="C20" s="1">
-        <v>40</v>
+        <v>352</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
       </c>
       <c r="E20" s="1">
-        <v>40</v>
+        <v>352</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
@@ -1625,19 +2556,19 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B21" s="2">
-        <v>0.03807767853140831</v>
+        <v>0.3109985589981079</v>
       </c>
       <c r="C21" s="1">
-        <v>38</v>
+        <v>334</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
       </c>
       <c r="E21" s="1">
-        <v>38</v>
+        <v>334</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
@@ -1651,19 +2582,19 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="B22" s="2">
-        <v>0.03607359156012535</v>
+        <v>0.3035494685173035</v>
       </c>
       <c r="C22" s="1">
-        <v>36</v>
+        <v>326</v>
       </c>
       <c r="D22" s="1">
         <v>0</v>
       </c>
       <c r="E22" s="1">
-        <v>36</v>
+        <v>326</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
@@ -1677,19 +2608,19 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="B23" s="2">
-        <v>0.03607359156012535</v>
+        <v>0.2961004078388214</v>
       </c>
       <c r="C23" s="1">
-        <v>36</v>
+        <v>318</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
       </c>
       <c r="E23" s="1">
-        <v>36</v>
+        <v>318</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
@@ -1703,19 +2634,19 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B24" s="2">
-        <v>0.03206541389226914</v>
+        <v>0.2942381501197815</v>
       </c>
       <c r="C24" s="1">
-        <v>32</v>
+        <v>316</v>
       </c>
       <c r="D24" s="1">
         <v>0</v>
       </c>
       <c r="E24" s="1">
-        <v>32</v>
+        <v>316</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
@@ -1729,25 +2660,25 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B25" s="2">
-        <v>0.03006132505834103</v>
+        <v>0.2905136048793793</v>
       </c>
       <c r="C25" s="1">
-        <v>30</v>
+        <v>312</v>
       </c>
       <c r="D25" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E25" s="1">
-        <v>30</v>
+        <v>308</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
       </c>
       <c r="G25" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H25" s="1">
         <v>0</v>
@@ -1755,19 +2686,19 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="B26" s="2">
-        <v>0.03006132505834103</v>
+        <v>0.2588550746440888</v>
       </c>
       <c r="C26" s="1">
-        <v>30</v>
+        <v>278</v>
       </c>
       <c r="D26" s="1">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="E26" s="1">
-        <v>30</v>
+        <v>278</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
@@ -1776,24 +2707,24 @@
         <v>0</v>
       </c>
       <c r="H26" s="1">
-        <v>0</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B27" s="2">
-        <v>0.02805723622441292</v>
+        <v>0.2495437413454056</v>
       </c>
       <c r="C27" s="1">
-        <v>28</v>
+        <v>268</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
       </c>
       <c r="E27" s="1">
-        <v>28</v>
+        <v>268</v>
       </c>
       <c r="F27" s="1">
         <v>0</v>
@@ -1807,19 +2738,19 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B28" s="2">
-        <v>0.02805723622441292</v>
+        <v>0.2458192110061646</v>
       </c>
       <c r="C28" s="1">
-        <v>28</v>
+        <v>264</v>
       </c>
       <c r="D28" s="1">
         <v>0</v>
       </c>
       <c r="E28" s="1">
-        <v>28</v>
+        <v>264</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
@@ -1833,19 +2764,19 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B29" s="2">
-        <v>0.02805723622441292</v>
+        <v>0.2439569383859634</v>
       </c>
       <c r="C29" s="1">
-        <v>28</v>
+        <v>262</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
       </c>
       <c r="E29" s="1">
-        <v>28</v>
+        <v>262</v>
       </c>
       <c r="F29" s="1">
         <v>0</v>
@@ -1859,19 +2790,19 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B30" s="2">
-        <v>0.02805723622441292</v>
+        <v>0.2122984081506729</v>
       </c>
       <c r="C30" s="1">
-        <v>28</v>
+        <v>228</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
       </c>
       <c r="E30" s="1">
-        <v>28</v>
+        <v>228</v>
       </c>
       <c r="F30" s="1">
         <v>0</v>
@@ -1885,19 +2816,19 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B31" s="2">
-        <v>0.02805723622441292</v>
+        <v>0.2067116051912308</v>
       </c>
       <c r="C31" s="1">
-        <v>28</v>
+        <v>222</v>
       </c>
       <c r="D31" s="1">
         <v>0</v>
       </c>
       <c r="E31" s="1">
-        <v>28</v>
+        <v>222</v>
       </c>
       <c r="F31" s="1">
         <v>0</v>
@@ -1911,19 +2842,19 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B32" s="2">
-        <v>0.02605314925312996</v>
+        <v>0.1974002718925476</v>
       </c>
       <c r="C32" s="1">
-        <v>26</v>
+        <v>212</v>
       </c>
       <c r="D32" s="1">
         <v>0</v>
       </c>
       <c r="E32" s="1">
-        <v>26</v>
+        <v>212</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
@@ -1937,19 +2868,19 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B33" s="2">
-        <v>0.01803679578006268</v>
+        <v>0.1731908023357391</v>
       </c>
       <c r="C33" s="1">
-        <v>18</v>
+        <v>186</v>
       </c>
       <c r="D33" s="1">
         <v>0</v>
       </c>
       <c r="E33" s="1">
-        <v>18</v>
+        <v>186</v>
       </c>
       <c r="F33" s="1">
         <v>0</v>
@@ -1963,19 +2894,19 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="B34" s="2">
-        <v>0.01002044137567282</v>
+        <v>0.1676040142774582</v>
       </c>
       <c r="C34" s="1">
-        <v>10</v>
+        <v>180</v>
       </c>
       <c r="D34" s="1">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="E34" s="1">
-        <v>10</v>
+        <v>180</v>
       </c>
       <c r="F34" s="1">
         <v>0</v>
@@ -1984,24 +2915,24 @@
         <v>0</v>
       </c>
       <c r="H34" s="1">
-        <v>0</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B35" s="2">
-        <v>0.008016353473067284</v>
+        <v>0.163879469037056</v>
       </c>
       <c r="C35" s="1">
-        <v>8</v>
+        <v>176</v>
       </c>
       <c r="D35" s="1">
         <v>0</v>
       </c>
       <c r="E35" s="1">
-        <v>8</v>
+        <v>176</v>
       </c>
       <c r="F35" s="1">
         <v>0</v>
@@ -2015,19 +2946,19 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B36" s="2">
-        <v>0.008016353473067284</v>
+        <v>0.163879469037056</v>
       </c>
       <c r="C36" s="1">
-        <v>8</v>
+        <v>176</v>
       </c>
       <c r="D36" s="1">
         <v>0</v>
       </c>
       <c r="E36" s="1">
-        <v>8</v>
+        <v>176</v>
       </c>
       <c r="F36" s="1">
         <v>0</v>
@@ -2041,59 +2972,1177 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1" t="s">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="B37" s="2">
-        <v>0.004008176736533642</v>
+        <v>0.1564304083585739</v>
       </c>
       <c r="C37" s="1">
+        <v>168</v>
+      </c>
+      <c r="D37" s="1">
+        <v>976</v>
+      </c>
+      <c r="E37" s="1">
+        <v>168</v>
+      </c>
+      <c r="F37" s="1">
+        <v>0</v>
+      </c>
+      <c r="G37" s="1">
+        <v>0</v>
+      </c>
+      <c r="H37" s="1">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B38" s="2">
+        <v>0.1461879462003708</v>
+      </c>
+      <c r="C38" s="1">
+        <v>157</v>
+      </c>
+      <c r="D38" s="1">
+        <v>1</v>
+      </c>
+      <c r="E38" s="1">
+        <v>156</v>
+      </c>
+      <c r="F38" s="1">
+        <v>0</v>
+      </c>
+      <c r="G38" s="1">
+        <v>1</v>
+      </c>
+      <c r="H38" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" s="2">
+        <v>0.1387388706207275</v>
+      </c>
+      <c r="C39" s="1">
+        <v>149</v>
+      </c>
+      <c r="D39" s="1">
+        <v>17</v>
+      </c>
+      <c r="E39" s="1">
+        <v>128</v>
+      </c>
+      <c r="F39" s="1">
+        <v>5</v>
+      </c>
+      <c r="G39" s="1">
+        <v>16</v>
+      </c>
+      <c r="H39" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="2">
+        <v>0.1340832114219666</v>
+      </c>
+      <c r="C40" s="1">
+        <v>144</v>
+      </c>
+      <c r="D40" s="1">
+        <v>0</v>
+      </c>
+      <c r="E40" s="1">
+        <v>144</v>
+      </c>
+      <c r="F40" s="1">
+        <v>0</v>
+      </c>
+      <c r="G40" s="1">
+        <v>0</v>
+      </c>
+      <c r="H40" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="2">
+        <v>0.1154605373740196</v>
+      </c>
+      <c r="C41" s="1">
+        <v>124</v>
+      </c>
+      <c r="D41" s="1">
+        <v>0</v>
+      </c>
+      <c r="E41" s="1">
+        <v>124</v>
+      </c>
+      <c r="F41" s="1">
+        <v>0</v>
+      </c>
+      <c r="G41" s="1">
+        <v>0</v>
+      </c>
+      <c r="H41" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" s="2">
+        <v>0.1117360070347786</v>
+      </c>
+      <c r="C42" s="1">
+        <v>120</v>
+      </c>
+      <c r="D42" s="1">
+        <v>0</v>
+      </c>
+      <c r="E42" s="1">
+        <v>120</v>
+      </c>
+      <c r="F42" s="1">
+        <v>0</v>
+      </c>
+      <c r="G42" s="1">
+        <v>0</v>
+      </c>
+      <c r="H42" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B43" s="2">
+        <v>0.1117360070347786</v>
+      </c>
+      <c r="C43" s="1">
+        <v>120</v>
+      </c>
+      <c r="D43" s="1">
+        <v>0</v>
+      </c>
+      <c r="E43" s="1">
+        <v>120</v>
+      </c>
+      <c r="F43" s="1">
+        <v>0</v>
+      </c>
+      <c r="G43" s="1">
+        <v>0</v>
+      </c>
+      <c r="H43" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B44" s="2">
+        <v>0.1024246737360954</v>
+      </c>
+      <c r="C44" s="1">
+        <v>110</v>
+      </c>
+      <c r="D44" s="1">
+        <v>0</v>
+      </c>
+      <c r="E44" s="1">
+        <v>110</v>
+      </c>
+      <c r="F44" s="1">
+        <v>0</v>
+      </c>
+      <c r="G44" s="1">
+        <v>0</v>
+      </c>
+      <c r="H44" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B45" s="2">
+        <v>0.1005624011158943</v>
+      </c>
+      <c r="C45" s="1">
+        <v>108</v>
+      </c>
+      <c r="D45" s="1">
         <v>4</v>
       </c>
-      <c r="D37" s="1">
-        <v>0</v>
-      </c>
-      <c r="E37" s="1">
+      <c r="E45" s="1">
+        <v>108</v>
+      </c>
+      <c r="F45" s="1">
+        <v>0</v>
+      </c>
+      <c r="G45" s="1">
+        <v>0</v>
+      </c>
+      <c r="H45" s="1">
         <v>4</v>
       </c>
-      <c r="F37" s="1">
-        <v>0</v>
-      </c>
-      <c r="G37" s="1">
-        <v>0</v>
-      </c>
-      <c r="H37" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" t="s">
-        <v>37</v>
-      </c>
-      <c r="B38">
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B46" s="2">
+        <v>0.1005624011158943</v>
+      </c>
+      <c r="C46" s="1">
+        <v>108</v>
+      </c>
+      <c r="D46" s="1">
+        <v>36</v>
+      </c>
+      <c r="E46" s="1">
+        <v>108</v>
+      </c>
+      <c r="F46" s="1">
+        <v>0</v>
+      </c>
+      <c r="G46" s="1">
+        <v>0</v>
+      </c>
+      <c r="H46" s="1">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B47" s="2">
+        <v>0.09311334043741226</v>
+      </c>
+      <c r="C47" s="1">
+        <v>100</v>
+      </c>
+      <c r="D47" s="1">
+        <v>0</v>
+      </c>
+      <c r="E47" s="1">
+        <v>100</v>
+      </c>
+      <c r="F47" s="1">
+        <v>0</v>
+      </c>
+      <c r="G47" s="1">
+        <v>0</v>
+      </c>
+      <c r="H47" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B48" s="2">
+        <v>0.09311334043741226</v>
+      </c>
+      <c r="C48" s="1">
+        <v>100</v>
+      </c>
+      <c r="D48" s="1">
+        <v>0</v>
+      </c>
+      <c r="E48" s="1">
+        <v>100</v>
+      </c>
+      <c r="F48" s="1">
+        <v>0</v>
+      </c>
+      <c r="G48" s="1">
+        <v>0</v>
+      </c>
+      <c r="H48" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B49" s="2">
+        <v>0.08193973451852799</v>
+      </c>
+      <c r="C49" s="1">
+        <v>88</v>
+      </c>
+      <c r="D49" s="1">
+        <v>0</v>
+      </c>
+      <c r="E49" s="1">
+        <v>88</v>
+      </c>
+      <c r="F49" s="1">
+        <v>0</v>
+      </c>
+      <c r="G49" s="1">
+        <v>0</v>
+      </c>
+      <c r="H49" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B50" s="2">
+        <v>0.08007746934890747</v>
+      </c>
+      <c r="C50" s="1">
+        <v>86</v>
+      </c>
+      <c r="D50" s="1">
+        <v>0</v>
+      </c>
+      <c r="E50" s="1">
+        <v>86</v>
+      </c>
+      <c r="F50" s="1">
+        <v>0</v>
+      </c>
+      <c r="G50" s="1">
+        <v>0</v>
+      </c>
+      <c r="H50" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B51" s="2">
+        <v>0.05959253758192062</v>
+      </c>
+      <c r="C51" s="1">
+        <v>64</v>
+      </c>
+      <c r="D51" s="1">
+        <v>0</v>
+      </c>
+      <c r="E51" s="1">
+        <v>64</v>
+      </c>
+      <c r="F51" s="1">
+        <v>0</v>
+      </c>
+      <c r="G51" s="1">
+        <v>0</v>
+      </c>
+      <c r="H51" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B52" s="2">
+        <v>0.05773026868700981</v>
+      </c>
+      <c r="C52" s="1">
+        <v>62</v>
+      </c>
+      <c r="D52" s="1">
+        <v>0</v>
+      </c>
+      <c r="E52" s="1">
+        <v>62</v>
+      </c>
+      <c r="F52" s="1">
+        <v>0</v>
+      </c>
+      <c r="G52" s="1">
+        <v>0</v>
+      </c>
+      <c r="H52" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B53" s="2">
+        <v>0.0558680035173893</v>
+      </c>
+      <c r="C53" s="1">
+        <v>60</v>
+      </c>
+      <c r="D53" s="1">
+        <v>0</v>
+      </c>
+      <c r="E53" s="1">
+        <v>60</v>
+      </c>
+      <c r="F53" s="1">
+        <v>0</v>
+      </c>
+      <c r="G53" s="1">
+        <v>0</v>
+      </c>
+      <c r="H53" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B54" s="2">
+        <v>0.05214346945285797</v>
+      </c>
+      <c r="C54" s="1">
+        <v>56</v>
+      </c>
+      <c r="D54" s="1">
+        <v>0</v>
+      </c>
+      <c r="E54" s="1">
+        <v>56</v>
+      </c>
+      <c r="F54" s="1">
+        <v>0</v>
+      </c>
+      <c r="G54" s="1">
+        <v>0</v>
+      </c>
+      <c r="H54" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B55" s="2">
+        <v>0.04655667021870613</v>
+      </c>
+      <c r="C55" s="1">
+        <v>50</v>
+      </c>
+      <c r="D55" s="1">
+        <v>0</v>
+      </c>
+      <c r="E55" s="1">
+        <v>50</v>
+      </c>
+      <c r="F55" s="1">
+        <v>0</v>
+      </c>
+      <c r="G55" s="1">
+        <v>0</v>
+      </c>
+      <c r="H55" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B56" s="2">
+        <v>0.04655667021870613</v>
+      </c>
+      <c r="C56" s="1">
+        <v>50</v>
+      </c>
+      <c r="D56" s="1">
+        <v>0</v>
+      </c>
+      <c r="E56" s="1">
+        <v>50</v>
+      </c>
+      <c r="F56" s="1">
+        <v>0</v>
+      </c>
+      <c r="G56" s="1">
+        <v>0</v>
+      </c>
+      <c r="H56" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B57" s="2">
+        <v>0.04469440132379532</v>
+      </c>
+      <c r="C57" s="1">
+        <v>48</v>
+      </c>
+      <c r="D57" s="1">
+        <v>0</v>
+      </c>
+      <c r="E57" s="1">
+        <v>48</v>
+      </c>
+      <c r="F57" s="1">
+        <v>0</v>
+      </c>
+      <c r="G57" s="1">
+        <v>0</v>
+      </c>
+      <c r="H57" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B58" s="2">
+        <v>0.04469440132379532</v>
+      </c>
+      <c r="C58" s="1">
+        <v>48</v>
+      </c>
+      <c r="D58" s="1">
+        <v>0</v>
+      </c>
+      <c r="E58" s="1">
+        <v>48</v>
+      </c>
+      <c r="F58" s="1">
+        <v>0</v>
+      </c>
+      <c r="G58" s="1">
+        <v>0</v>
+      </c>
+      <c r="H58" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B59" s="2">
+        <v>0.03724533319473267</v>
+      </c>
+      <c r="C59" s="1">
+        <v>40</v>
+      </c>
+      <c r="D59" s="1">
+        <v>0</v>
+      </c>
+      <c r="E59" s="1">
+        <v>40</v>
+      </c>
+      <c r="F59" s="1">
+        <v>0</v>
+      </c>
+      <c r="G59" s="1">
+        <v>0</v>
+      </c>
+      <c r="H59" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B60" s="2">
+        <v>0.03724533319473267</v>
+      </c>
+      <c r="C60" s="1">
+        <v>40</v>
+      </c>
+      <c r="D60" s="1">
+        <v>0</v>
+      </c>
+      <c r="E60" s="1">
+        <v>40</v>
+      </c>
+      <c r="F60" s="1">
+        <v>0</v>
+      </c>
+      <c r="G60" s="1">
+        <v>0</v>
+      </c>
+      <c r="H60" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B61" s="2">
+        <v>0.03538306802511215</v>
+      </c>
+      <c r="C61" s="1">
+        <v>38</v>
+      </c>
+      <c r="D61" s="1">
+        <v>0</v>
+      </c>
+      <c r="E61" s="1">
+        <v>38</v>
+      </c>
+      <c r="F61" s="1">
+        <v>0</v>
+      </c>
+      <c r="G61" s="1">
+        <v>0</v>
+      </c>
+      <c r="H61" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B62" s="2">
+        <v>0.03352080285549164</v>
+      </c>
+      <c r="C62" s="1">
+        <v>36</v>
+      </c>
+      <c r="D62" s="1">
+        <v>0</v>
+      </c>
+      <c r="E62" s="1">
+        <v>36</v>
+      </c>
+      <c r="F62" s="1">
+        <v>0</v>
+      </c>
+      <c r="G62" s="1">
+        <v>0</v>
+      </c>
+      <c r="H62" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B63" s="2">
+        <v>0.03352080285549164</v>
+      </c>
+      <c r="C63" s="1">
+        <v>36</v>
+      </c>
+      <c r="D63" s="1">
+        <v>0</v>
+      </c>
+      <c r="E63" s="1">
+        <v>36</v>
+      </c>
+      <c r="F63" s="1">
+        <v>0</v>
+      </c>
+      <c r="G63" s="1">
+        <v>0</v>
+      </c>
+      <c r="H63" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B64" s="2">
+        <v>0.02979626879096031</v>
+      </c>
+      <c r="C64" s="1">
+        <v>32</v>
+      </c>
+      <c r="D64" s="1">
+        <v>0</v>
+      </c>
+      <c r="E64" s="1">
+        <v>32</v>
+      </c>
+      <c r="F64" s="1">
+        <v>0</v>
+      </c>
+      <c r="G64" s="1">
+        <v>0</v>
+      </c>
+      <c r="H64" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B65" s="2">
+        <v>0.02793400175869465</v>
+      </c>
+      <c r="C65" s="1">
+        <v>30</v>
+      </c>
+      <c r="D65" s="1">
+        <v>0</v>
+      </c>
+      <c r="E65" s="1">
+        <v>30</v>
+      </c>
+      <c r="F65" s="1">
+        <v>0</v>
+      </c>
+      <c r="G65" s="1">
+        <v>0</v>
+      </c>
+      <c r="H65" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B66" s="2">
+        <v>0.02793400175869465</v>
+      </c>
+      <c r="C66" s="1">
+        <v>30</v>
+      </c>
+      <c r="D66" s="1">
+        <v>0</v>
+      </c>
+      <c r="E66" s="1">
+        <v>30</v>
+      </c>
+      <c r="F66" s="1">
+        <v>0</v>
+      </c>
+      <c r="G66" s="1">
+        <v>0</v>
+      </c>
+      <c r="H66" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B67" s="2">
+        <v>0.02607173472642899</v>
+      </c>
+      <c r="C67" s="1">
+        <v>28</v>
+      </c>
+      <c r="D67" s="1">
+        <v>0</v>
+      </c>
+      <c r="E67" s="1">
+        <v>28</v>
+      </c>
+      <c r="F67" s="1">
+        <v>0</v>
+      </c>
+      <c r="G67" s="1">
+        <v>0</v>
+      </c>
+      <c r="H67" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B68" s="2">
+        <v>0.02607173472642899</v>
+      </c>
+      <c r="C68" s="1">
+        <v>28</v>
+      </c>
+      <c r="D68" s="1">
+        <v>0</v>
+      </c>
+      <c r="E68" s="1">
+        <v>28</v>
+      </c>
+      <c r="F68" s="1">
+        <v>0</v>
+      </c>
+      <c r="G68" s="1">
+        <v>0</v>
+      </c>
+      <c r="H68" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B69" s="2">
+        <v>0.02607173472642899</v>
+      </c>
+      <c r="C69" s="1">
+        <v>28</v>
+      </c>
+      <c r="D69" s="1">
+        <v>0</v>
+      </c>
+      <c r="E69" s="1">
+        <v>28</v>
+      </c>
+      <c r="F69" s="1">
+        <v>0</v>
+      </c>
+      <c r="G69" s="1">
+        <v>0</v>
+      </c>
+      <c r="H69" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B70" s="2">
+        <v>0.02607173472642899</v>
+      </c>
+      <c r="C70" s="1">
+        <v>28</v>
+      </c>
+      <c r="D70" s="1">
+        <v>0</v>
+      </c>
+      <c r="E70" s="1">
+        <v>28</v>
+      </c>
+      <c r="F70" s="1">
+        <v>0</v>
+      </c>
+      <c r="G70" s="1">
+        <v>0</v>
+      </c>
+      <c r="H70" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B71" s="2">
+        <v>0.02607173472642899</v>
+      </c>
+      <c r="C71" s="1">
+        <v>28</v>
+      </c>
+      <c r="D71" s="1">
+        <v>0</v>
+      </c>
+      <c r="E71" s="1">
+        <v>28</v>
+      </c>
+      <c r="F71" s="1">
+        <v>0</v>
+      </c>
+      <c r="G71" s="1">
+        <v>0</v>
+      </c>
+      <c r="H71" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B72" s="2">
+        <v>0.02607173472642899</v>
+      </c>
+      <c r="C72" s="1">
+        <v>28</v>
+      </c>
+      <c r="D72" s="1">
+        <v>0</v>
+      </c>
+      <c r="E72" s="1">
+        <v>28</v>
+      </c>
+      <c r="F72" s="1">
+        <v>0</v>
+      </c>
+      <c r="G72" s="1">
+        <v>0</v>
+      </c>
+      <c r="H72" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B73" s="2">
+        <v>0.02420946769416332</v>
+      </c>
+      <c r="C73" s="1">
+        <v>26</v>
+      </c>
+      <c r="D73" s="1">
+        <v>0</v>
+      </c>
+      <c r="E73" s="1">
+        <v>26</v>
+      </c>
+      <c r="F73" s="1">
+        <v>0</v>
+      </c>
+      <c r="G73" s="1">
+        <v>0</v>
+      </c>
+      <c r="H73" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B74" s="2">
+        <v>0.01676040142774582</v>
+      </c>
+      <c r="C74" s="1">
+        <v>18</v>
+      </c>
+      <c r="D74" s="1">
+        <v>0</v>
+      </c>
+      <c r="E74" s="1">
+        <v>18</v>
+      </c>
+      <c r="F74" s="1">
+        <v>0</v>
+      </c>
+      <c r="G74" s="1">
+        <v>0</v>
+      </c>
+      <c r="H74" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B75" s="2">
+        <v>0.01117360033094883</v>
+      </c>
+      <c r="C75" s="1">
+        <v>12</v>
+      </c>
+      <c r="D75" s="1">
+        <v>0</v>
+      </c>
+      <c r="E75" s="1">
+        <v>12</v>
+      </c>
+      <c r="F75" s="1">
+        <v>0</v>
+      </c>
+      <c r="G75" s="1">
+        <v>0</v>
+      </c>
+      <c r="H75" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B76" s="2">
+        <v>0.009311333298683167</v>
+      </c>
+      <c r="C76" s="1">
+        <v>10</v>
+      </c>
+      <c r="D76" s="1">
+        <v>0</v>
+      </c>
+      <c r="E76" s="1">
+        <v>10</v>
+      </c>
+      <c r="F76" s="1">
+        <v>0</v>
+      </c>
+      <c r="G76" s="1">
+        <v>0</v>
+      </c>
+      <c r="H76" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B77" s="2">
+        <v>0.007449067197740078</v>
+      </c>
+      <c r="C77" s="1">
+        <v>8</v>
+      </c>
+      <c r="D77" s="1">
+        <v>0</v>
+      </c>
+      <c r="E77" s="1">
+        <v>8</v>
+      </c>
+      <c r="F77" s="1">
+        <v>0</v>
+      </c>
+      <c r="G77" s="1">
+        <v>0</v>
+      </c>
+      <c r="H77" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B78" s="2">
+        <v>0.007449067197740078</v>
+      </c>
+      <c r="C78" s="1">
+        <v>8</v>
+      </c>
+      <c r="D78" s="1">
+        <v>0</v>
+      </c>
+      <c r="E78" s="1">
+        <v>8</v>
+      </c>
+      <c r="F78" s="1">
+        <v>0</v>
+      </c>
+      <c r="G78" s="1">
+        <v>0</v>
+      </c>
+      <c r="H78" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B79" s="2">
+        <v>0.007449067197740078</v>
+      </c>
+      <c r="C79" s="1">
+        <v>8</v>
+      </c>
+      <c r="D79" s="1">
+        <v>0</v>
+      </c>
+      <c r="E79" s="1">
+        <v>8</v>
+      </c>
+      <c r="F79" s="1">
+        <v>0</v>
+      </c>
+      <c r="G79" s="1">
+        <v>0</v>
+      </c>
+      <c r="H79" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B80" s="2">
+        <v>0.003724533598870039</v>
+      </c>
+      <c r="C80" s="1">
+        <v>4</v>
+      </c>
+      <c r="D80" s="1">
+        <v>0</v>
+      </c>
+      <c r="E80" s="1">
+        <v>4</v>
+      </c>
+      <c r="F80" s="1">
+        <v>0</v>
+      </c>
+      <c r="G80" s="1">
+        <v>0</v>
+      </c>
+      <c r="H80" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
+      <c r="A81" t="s">
+        <v>80</v>
+      </c>
+      <c r="B81">
         <f>SUBTOTAL(109,[flash_percent])</f>
         <v>0</v>
       </c>
-      <c r="C38">
+      <c r="C81">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="D38">
+      <c r="D81">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="E38">
+      <c r="E81">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F38">
+      <c r="F81">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G38">
+      <c r="G81">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H38">
+      <c r="H81">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>

--- a/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
+++ b/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
@@ -29,27 +29,27 @@
     <t>ha01_handle.o</t>
   </si>
   <si>
+    <t>key_handle.o</t>
+  </si>
+  <si>
     <t>tmt.o</t>
   </si>
   <si>
     <t>encoderec11.o</t>
   </si>
   <si>
-    <t>key_handle.o</t>
-  </si>
-  <si>
     <t>output_handle.o</t>
   </si>
   <si>
+    <t>adc_filter.o</t>
+  </si>
+  <si>
+    <t>pid_operation.o</t>
+  </si>
+  <si>
     <t>lcd_handle.o</t>
   </si>
   <si>
-    <t>adc_filter.o</t>
-  </si>
-  <si>
-    <t>pid_operation.o</t>
-  </si>
-  <si>
     <t>at32_usart.o</t>
   </si>
   <si>
@@ -71,12 +71,12 @@
     <t>system_at32f415.o</t>
   </si>
   <si>
+    <t>key.o</t>
+  </si>
+  <si>
     <t>main.o</t>
   </si>
   <si>
-    <t>key.o</t>
-  </si>
-  <si>
     <t>mf_w.l</t>
   </si>
   <si>
@@ -239,6 +239,9 @@
     <t>wk_debug.o</t>
   </si>
   <si>
+    <t>beep_handle.o</t>
+  </si>
+  <si>
     <t>ffltui.o</t>
   </si>
   <si>
@@ -246,9 +249,6 @@
   </si>
   <si>
     <t>entry2.o</t>
-  </si>
-  <si>
-    <t>beep_handle.o</t>
   </si>
   <si>
     <t>entry5.o</t>
@@ -384,25 +384,25 @@
                   <c:v>ha01_handle.o</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>key_handle.o</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>tmt.o</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>encoderec11.o</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>key_handle.o</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>output_handle.o</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>adc_filter.o</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>pid_operation.o</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>lcd_handle.o</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>adc_filter.o</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>pid_operation.o</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>at32_usart.o</c:v>
@@ -426,10 +426,10 @@
                   <c:v>system_at32f415.o</c:v>
                 </c:pt>
                 <c:pt idx="17">
+                  <c:v>key.o</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>main.o</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>key.o</c:v>
                 </c:pt>
                 <c:pt idx="78">
                   <c:v>Totals</c:v>
@@ -444,61 +444,61 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="79"/>
                 <c:pt idx="0">
-                  <c:v>27.70539665222168</c:v>
+                  <c:v>27.20626640319824</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>27.2268009185791</c:v>
+                  <c:v>26.73629188537598</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>25.95054435729981</c:v>
+                  <c:v>26.10966110229492</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.935123682022095</c:v>
+                  <c:v>4.229764938354492</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.031108856201172</c:v>
+                  <c:v>3.864229679107666</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.791810750961304</c:v>
+                  <c:v>2.976501226425171</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.632278680801392</c:v>
+                  <c:v>2.584856510162354</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.409199714660645</c:v>
+                  <c:v>1.253263711929321</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.276256322860718</c:v>
+                  <c:v>1.14882504940033</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.169901609420776</c:v>
+                  <c:v>0.9921671152114868</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.9571922421455383</c:v>
+                  <c:v>0.939947783946991</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.6381281614303589</c:v>
+                  <c:v>0.6788511872291565</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.4520074427127838</c:v>
+                  <c:v>0.4438642263412476</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.3722414374351502</c:v>
+                  <c:v>0.4177545607089996</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.1329433619976044</c:v>
+                  <c:v>0.1305482983589172</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.1063546910881996</c:v>
+                  <c:v>0.1044386401772499</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.1063546910881996</c:v>
+                  <c:v>0.1044386401772499</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.07976602017879486</c:v>
+                  <c:v>0.05221932008862495</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.0265886727720499</c:v>
+                  <c:v>0.02610966004431248</c:v>
                 </c:pt>
                 <c:pt idx="78">
                   <c:v>0</c:v>
@@ -581,13 +581,13 @@
                   <c:v>ec11_handle.o</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>mf_w.l</c:v>
+                  <c:v>key_handle.o</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>flash_handle.o</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>key_handle.o</c:v>
+                  <c:v>mf_w.l</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>output_handle.o</c:v>
@@ -602,82 +602,82 @@
                   <c:v>at32f415_tmr.o</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>at32f415_int.o</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>main.o</c:v>
                 </c:pt>
-                <c:pt idx="11">
-                  <c:v>at32f415_int.o</c:v>
-                </c:pt>
                 <c:pt idx="12">
+                  <c:v>key.o</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>startup_at32f415.o</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>tmt.o</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>at32f415_wk_config.o</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>at32_spiflash.o</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>wk_tmr.o</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>at32f415_adc.o</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>dadd.o</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
                   <c:v>at32f415_usart.o</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="21">
                   <c:v>mc_w.l</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="22">
                   <c:v>at32f415_spi.o</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="23">
                   <c:v>system_at32f415.o</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="24">
                   <c:v>pid_operation.o</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="25">
                   <c:v>at32f415_dma.o</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="26">
                   <c:v>wk_gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="27">
                   <c:v>at32f415_gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="28">
+                  <c:v>ha01_handle.o</c:v>
+                </c:pt>
+                <c:pt idx="29">
                   <c:v>dmul.o</c:v>
                 </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="30">
                   <c:v>ddiv.o</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="31">
                   <c:v>at32f415_flash.o</c:v>
                 </c:pt>
-                <c:pt idx="30">
+                <c:pt idx="32">
                   <c:v>depilogue.o</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="33">
                   <c:v>adc_filter.o</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="34">
                   <c:v>fadd.o</c:v>
                 </c:pt>
-                <c:pt idx="33">
+                <c:pt idx="35">
                   <c:v>at32f415_misc.o</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>ha01_handle.o</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>key.o</c:v>
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>beep.o</c:v>
@@ -791,16 +791,16 @@
                   <c:v>wk_debug.o</c:v>
                 </c:pt>
                 <c:pt idx="73">
+                  <c:v>beep_handle.o</c:v>
+                </c:pt>
+                <c:pt idx="74">
                   <c:v>ffltui.o</c:v>
                 </c:pt>
-                <c:pt idx="74">
+                <c:pt idx="75">
                   <c:v>entry9a.o</c:v>
                 </c:pt>
-                <c:pt idx="75">
+                <c:pt idx="76">
                   <c:v>entry2.o</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>beep_handle.o</c:v>
                 </c:pt>
                 <c:pt idx="77">
                   <c:v>entry5.o</c:v>
@@ -818,238 +818,238 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="79"/>
                 <c:pt idx="0">
-                  <c:v>74.48508453369141</c:v>
+                  <c:v>72.69774627685547</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.40053653717041</c:v>
+                  <c:v>4.766440868377686</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.123021364212036</c:v>
+                  <c:v>3.741302251815796</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.834332704544067</c:v>
+                  <c:v>2.309736967086792</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.782189249992371</c:v>
+                  <c:v>1.970443367958069</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.687213659286499</c:v>
+                  <c:v>1.787188529968262</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.460017085075378</c:v>
+                  <c:v>1.496883749961853</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.709523618221283</c:v>
+                  <c:v>0.6912881135940552</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.6629669666290283</c:v>
+                  <c:v>0.6459280252456665</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.597787618637085</c:v>
+                  <c:v>0.5824238657951355</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.5065365433692932</c:v>
+                  <c:v>0.4608587622642517</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.4078364074230194</c:v>
+                  <c:v>0.4227562546730042</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.3761778771877289</c:v>
+                  <c:v>0.3792105615139008</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.3631420135498047</c:v>
+                  <c:v>0.3665097057819367</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.3482438921928406</c:v>
+                  <c:v>0.3538088798522949</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.3352080285549164</c:v>
+                  <c:v>0.3392936587333679</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.3333457410335541</c:v>
+                  <c:v>0.3265928328037262</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.3277589380741119</c:v>
+                  <c:v>0.3247784078121185</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.3109985589981079</c:v>
+                  <c:v>0.3193351924419403</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.3035494685173035</c:v>
+                  <c:v>0.3030055463314056</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.2961004078388214</c:v>
+                  <c:v>0.2957479357719421</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.2942381501197815</c:v>
+                  <c:v>0.2884903252124786</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.2905136048793793</c:v>
+                  <c:v>0.2866759300231934</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.2588550746440888</c:v>
+                  <c:v>0.2830471098423004</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.2495437413454056</c:v>
+                  <c:v>0.2522022426128388</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.2458192110061646</c:v>
+                  <c:v>0.2431302070617676</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.2439569383859634</c:v>
+                  <c:v>0.2395014017820358</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.2122984081506729</c:v>
+                  <c:v>0.2376869916915894</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.2067116051912308</c:v>
+                  <c:v>0.2104709297418594</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.1974002718925476</c:v>
+                  <c:v>0.2068421244621277</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.1731908023357391</c:v>
+                  <c:v>0.2013989090919495</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.1676040142774582</c:v>
+                  <c:v>0.1923268884420395</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.163879469037056</c:v>
+                  <c:v>0.1687396168708801</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.163879469037056</c:v>
+                  <c:v>0.1632964164018631</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.1564304083585739</c:v>
+                  <c:v>0.1596675962209702</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.1461879462003708</c:v>
+                  <c:v>0.1596675962209702</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.1387388706207275</c:v>
+                  <c:v>0.1351731419563294</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.1340832114219666</c:v>
+                  <c:v>0.1306371241807938</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.1154605373740196</c:v>
+                  <c:v>0.1124930828809738</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.1117360070347786</c:v>
+                  <c:v>0.1088642701506615</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.1117360070347786</c:v>
+                  <c:v>0.1088642701506615</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.1024246737360954</c:v>
+                  <c:v>0.0997922495007515</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.1005624011158943</c:v>
+                  <c:v>0.09797784686088562</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.1005624011158943</c:v>
+                  <c:v>0.09797784686088562</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.09311334043741226</c:v>
+                  <c:v>0.09072022885084152</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.09311334043741226</c:v>
+                  <c:v>0.09072022885084152</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.08193973451852799</c:v>
+                  <c:v>0.07983379811048508</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.08007746934890747</c:v>
+                  <c:v>0.0780193954706192</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.05959253758192062</c:v>
+                  <c:v>0.05806094408035278</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.05773026868700981</c:v>
+                  <c:v>0.05624654144048691</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.0558680035173893</c:v>
+                  <c:v>0.05443213507533073</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.05214346945285797</c:v>
+                  <c:v>0.05080332607030869</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.04655667021870613</c:v>
+                  <c:v>0.04536011442542076</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.04655667021870613</c:v>
+                  <c:v>0.04536011442542076</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.04469440132379532</c:v>
+                  <c:v>0.04354570806026459</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.04469440132379532</c:v>
+                  <c:v>0.04354570806026459</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.03724533319473267</c:v>
+                  <c:v>0.03628809005022049</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.03724533319473267</c:v>
+                  <c:v>0.03628809005022049</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.03538306802511215</c:v>
+                  <c:v>0.03447368741035461</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.03352080285549164</c:v>
+                  <c:v>0.03265928104519844</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.03352080285549164</c:v>
+                  <c:v>0.03265928104519844</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.02979626879096031</c:v>
+                  <c:v>0.02903047204017639</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.02793400175869465</c:v>
+                  <c:v>0.02721606753766537</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.02793400175869465</c:v>
+                  <c:v>0.02721606753766537</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.02607173472642899</c:v>
+                  <c:v>0.02540166303515434</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.02607173472642899</c:v>
+                  <c:v>0.02540166303515434</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.02607173472642899</c:v>
+                  <c:v>0.02540166303515434</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.02607173472642899</c:v>
+                  <c:v>0.02540166303515434</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.02607173472642899</c:v>
+                  <c:v>0.02540166303515434</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.02607173472642899</c:v>
+                  <c:v>0.02540166303515434</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.02420946769416332</c:v>
+                  <c:v>0.02358725853264332</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.01676040142774582</c:v>
+                  <c:v>0.01632964052259922</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.01117360033094883</c:v>
+                  <c:v>0.01088642701506615</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.009311333298683167</c:v>
+                  <c:v>0.01088642701506615</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.007449067197740078</c:v>
+                  <c:v>0.009072022512555122</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0.007449067197740078</c:v>
+                  <c:v>0.007257618010044098</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>0.007449067197740078</c:v>
+                  <c:v>0.007257618010044098</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>0.003724533598870039</c:v>
+                  <c:v>0.003628809005022049</c:v>
                 </c:pt>
                 <c:pt idx="78">
                   <c:v>0</c:v>
@@ -1516,19 +1516,19 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>27.70539665222168</v>
+        <v>27.20626640319824</v>
       </c>
       <c r="C3" s="1">
         <v>1042</v>
       </c>
       <c r="D3" s="1">
-        <v>79994</v>
+        <v>80134</v>
       </c>
       <c r="E3" s="1">
-        <v>3520</v>
+        <v>3516</v>
       </c>
       <c r="F3" s="1">
-        <v>76474</v>
+        <v>76618</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -1542,7 +1542,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>27.2268009185791</v>
+        <v>26.73629188537598</v>
       </c>
       <c r="C4" s="1">
         <v>1024</v>
@@ -1568,16 +1568,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>25.95054435729981</v>
+        <v>26.10966110229492</v>
       </c>
       <c r="C5" s="1">
-        <v>976</v>
+        <v>1000</v>
       </c>
       <c r="D5" s="1">
-        <v>168</v>
+        <v>232</v>
       </c>
       <c r="E5" s="1">
-        <v>168</v>
+        <v>232</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
@@ -1586,7 +1586,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="1">
-        <v>976</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1594,25 +1594,25 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>3.935123682022095</v>
+        <v>4.229764938354492</v>
       </c>
       <c r="C6" s="1">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="D6" s="1">
-        <v>390</v>
+        <v>2546</v>
       </c>
       <c r="E6" s="1">
-        <v>390</v>
+        <v>2370</v>
       </c>
       <c r="F6" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="H6" s="1">
-        <v>148</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1620,25 +1620,25 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>3.031108856201172</v>
+        <v>3.864229679107666</v>
       </c>
       <c r="C7" s="1">
-        <v>114</v>
+        <v>148</v>
       </c>
       <c r="D7" s="1">
-        <v>712</v>
+        <v>390</v>
       </c>
       <c r="E7" s="1">
-        <v>600</v>
+        <v>390</v>
       </c>
       <c r="F7" s="1">
         <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="H7" s="1">
-        <v>2</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1646,25 +1646,25 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>2.791810750961304</v>
+        <v>2.976501226425171</v>
       </c>
       <c r="C8" s="1">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="D8" s="1">
-        <v>1812</v>
+        <v>712</v>
       </c>
       <c r="E8" s="1">
-        <v>1708</v>
+        <v>600</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="H8" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1672,16 +1672,16 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>2.632278680801392</v>
+        <v>2.584856510162354</v>
       </c>
       <c r="C9" s="1">
         <v>99</v>
       </c>
       <c r="D9" s="1">
+        <v>1650</v>
+      </c>
+      <c r="E9" s="1">
         <v>1568</v>
-      </c>
-      <c r="E9" s="1">
-        <v>1486</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
@@ -1698,25 +1698,25 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>1.409199714660645</v>
+        <v>1.253263711929321</v>
       </c>
       <c r="C10" s="1">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D10" s="1">
-        <v>4726</v>
+        <v>180</v>
       </c>
       <c r="E10" s="1">
-        <v>4702</v>
+        <v>180</v>
       </c>
       <c r="F10" s="1">
         <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H10" s="1">
-        <v>29</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1724,16 +1724,16 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>1.276256322860718</v>
+        <v>1.14882504940033</v>
       </c>
       <c r="C11" s="1">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D11" s="1">
-        <v>180</v>
+        <v>278</v>
       </c>
       <c r="E11" s="1">
-        <v>180</v>
+        <v>278</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>
@@ -1742,7 +1742,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="1">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1750,25 +1750,25 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>1.169901609420776</v>
+        <v>0.9921671152114868</v>
       </c>
       <c r="C12" s="1">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D12" s="1">
-        <v>278</v>
+        <v>5254</v>
       </c>
       <c r="E12" s="1">
-        <v>278</v>
+        <v>5242</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H12" s="1">
-        <v>44</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1776,7 +1776,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.9571922421455383</v>
+        <v>0.939947783946991</v>
       </c>
       <c r="C13" s="1">
         <v>36</v>
@@ -1802,16 +1802,16 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.6381281614303589</v>
+        <v>0.6788511872291565</v>
       </c>
       <c r="C14" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D14" s="1">
-        <v>1914</v>
+        <v>2172</v>
       </c>
       <c r="E14" s="1">
-        <v>1914</v>
+        <v>2172</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
@@ -1820,7 +1820,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1828,7 +1828,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.4520074427127838</v>
+        <v>0.4438642263412476</v>
       </c>
       <c r="C15" s="1">
         <v>17</v>
@@ -1854,22 +1854,22 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.3722414374351502</v>
+        <v>0.4177545607089996</v>
       </c>
       <c r="C16" s="1">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D16" s="1">
-        <v>438</v>
+        <v>508</v>
       </c>
       <c r="E16" s="1">
-        <v>432</v>
+        <v>500</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H16" s="1">
         <v>8</v>
@@ -1880,16 +1880,16 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.1329433619976044</v>
+        <v>0.1305482983589172</v>
       </c>
       <c r="C17" s="1">
         <v>5</v>
       </c>
       <c r="D17" s="1">
-        <v>3354</v>
+        <v>4124</v>
       </c>
       <c r="E17" s="1">
-        <v>3352</v>
+        <v>4122</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.1063546910881996</v>
+        <v>0.1044386401772499</v>
       </c>
       <c r="C18" s="1">
         <v>4</v>
@@ -1932,7 +1932,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.1063546910881996</v>
+        <v>0.1044386401772499</v>
       </c>
       <c r="C19" s="1">
         <v>4</v>
@@ -1958,25 +1958,25 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.07976602017879486</v>
+        <v>0.05221932008862495</v>
       </c>
       <c r="C20" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D20" s="1">
-        <v>544</v>
+        <v>418</v>
       </c>
       <c r="E20" s="1">
-        <v>544</v>
+        <v>416</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H20" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1984,25 +1984,25 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.0265886727720499</v>
+        <v>0.02610966004431248</v>
       </c>
       <c r="C21" s="1">
         <v>1</v>
       </c>
       <c r="D21" s="1">
-        <v>157</v>
+        <v>466</v>
       </c>
       <c r="E21" s="1">
-        <v>156</v>
+        <v>466</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
       </c>
       <c r="G21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21" s="1">
         <v>1</v>
-      </c>
-      <c r="H21" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -2091,19 +2091,19 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>74.48508453369141</v>
+        <v>72.69774627685547</v>
       </c>
       <c r="C3" s="1">
-        <v>79994</v>
+        <v>80134</v>
       </c>
       <c r="D3" s="1">
         <v>1042</v>
       </c>
       <c r="E3" s="1">
-        <v>3520</v>
+        <v>3516</v>
       </c>
       <c r="F3" s="1">
-        <v>76474</v>
+        <v>76618</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -2114,28 +2114,28 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" s="2">
-        <v>4.40053653717041</v>
+        <v>4.766440868377686</v>
       </c>
       <c r="C4" s="1">
-        <v>4726</v>
+        <v>5254</v>
       </c>
       <c r="D4" s="1">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="E4" s="1">
-        <v>4702</v>
+        <v>5242</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="H4" s="1">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2143,16 +2143,16 @@
         <v>15</v>
       </c>
       <c r="B5" s="2">
-        <v>3.123021364212036</v>
+        <v>3.741302251815796</v>
       </c>
       <c r="C5" s="1">
-        <v>3354</v>
+        <v>4124</v>
       </c>
       <c r="D5" s="1">
         <v>5</v>
       </c>
       <c r="E5" s="1">
-        <v>3352</v>
+        <v>4122</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
@@ -2166,28 +2166,28 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>1.834332704544067</v>
+        <v>2.309736967086792</v>
       </c>
       <c r="C6" s="1">
-        <v>1970</v>
+        <v>2546</v>
       </c>
       <c r="D6" s="1">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="E6" s="1">
-        <v>1970</v>
+        <v>2370</v>
       </c>
       <c r="F6" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="H6" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -2195,16 +2195,16 @@
         <v>12</v>
       </c>
       <c r="B7" s="2">
-        <v>1.782189249992371</v>
+        <v>1.970443367958069</v>
       </c>
       <c r="C7" s="1">
-        <v>1914</v>
+        <v>2172</v>
       </c>
       <c r="D7" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E7" s="1">
-        <v>1914</v>
+        <v>2172</v>
       </c>
       <c r="F7" s="1">
         <v>0</v>
@@ -2213,33 +2213,33 @@
         <v>0</v>
       </c>
       <c r="H7" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B8" s="2">
-        <v>1.687213659286499</v>
+        <v>1.787188529968262</v>
       </c>
       <c r="C8" s="1">
-        <v>1812</v>
+        <v>1970</v>
       </c>
       <c r="D8" s="1">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="E8" s="1">
-        <v>1708</v>
+        <v>1970</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="H8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -2247,16 +2247,16 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>1.460017085075378</v>
+        <v>1.496883749961853</v>
       </c>
       <c r="C9" s="1">
-        <v>1568</v>
+        <v>1650</v>
       </c>
       <c r="D9" s="1">
         <v>99</v>
       </c>
       <c r="E9" s="1">
-        <v>1486</v>
+        <v>1568</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
@@ -2273,7 +2273,7 @@
         <v>21</v>
       </c>
       <c r="B10" s="2">
-        <v>0.709523618221283</v>
+        <v>0.6912881135940552</v>
       </c>
       <c r="C10" s="1">
         <v>762</v>
@@ -2296,10 +2296,10 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B11" s="2">
-        <v>0.6629669666290283</v>
+        <v>0.6459280252456665</v>
       </c>
       <c r="C11" s="1">
         <v>712</v>
@@ -2325,7 +2325,7 @@
         <v>22</v>
       </c>
       <c r="B12" s="2">
-        <v>0.597787618637085</v>
+        <v>0.5824238657951355</v>
       </c>
       <c r="C12" s="1">
         <v>642</v>
@@ -2348,123 +2348,123 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B13" s="2">
-        <v>0.5065365433692932</v>
+        <v>0.4608587622642517</v>
       </c>
       <c r="C13" s="1">
-        <v>544</v>
+        <v>508</v>
       </c>
       <c r="D13" s="1">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E13" s="1">
-        <v>544</v>
+        <v>500</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H13" s="1">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B14" s="2">
-        <v>0.4078364074230194</v>
+        <v>0.4227562546730042</v>
       </c>
       <c r="C14" s="1">
-        <v>438</v>
+        <v>466</v>
       </c>
       <c r="D14" s="1">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E14" s="1">
-        <v>432</v>
+        <v>466</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H14" s="1">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0.3792105615139008</v>
+      </c>
+      <c r="C15" s="1">
+        <v>418</v>
+      </c>
+      <c r="D15" s="1">
         <v>2</v>
       </c>
-      <c r="B15" s="2">
-        <v>0.3761778771877289</v>
-      </c>
-      <c r="C15" s="1">
-        <v>404</v>
-      </c>
-      <c r="D15" s="1">
-        <v>1024</v>
-      </c>
       <c r="E15" s="1">
-        <v>36</v>
+        <v>416</v>
       </c>
       <c r="F15" s="1">
-        <v>368</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15" s="1">
-        <v>1024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B16" s="2">
-        <v>0.3631420135498047</v>
+        <v>0.3665097057819367</v>
       </c>
       <c r="C16" s="1">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="D16" s="1">
-        <v>148</v>
+        <v>1024</v>
       </c>
       <c r="E16" s="1">
-        <v>390</v>
+        <v>36</v>
       </c>
       <c r="F16" s="1">
-        <v>0</v>
+        <v>368</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
       </c>
       <c r="H16" s="1">
-        <v>148</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B17" s="2">
-        <v>0.3482438921928406</v>
+        <v>0.3538088798522949</v>
       </c>
       <c r="C17" s="1">
-        <v>374</v>
+        <v>390</v>
       </c>
       <c r="D17" s="1">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="E17" s="1">
-        <v>374</v>
+        <v>390</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
@@ -2473,24 +2473,24 @@
         <v>0</v>
       </c>
       <c r="H17" s="1">
-        <v>0</v>
+        <v>148</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B18" s="2">
-        <v>0.3352080285549164</v>
+        <v>0.3392936587333679</v>
       </c>
       <c r="C18" s="1">
-        <v>360</v>
+        <v>374</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
       </c>
       <c r="E18" s="1">
-        <v>360</v>
+        <v>374</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -2504,19 +2504,19 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B19" s="2">
-        <v>0.3333457410335541</v>
+        <v>0.3265928328037262</v>
       </c>
       <c r="C19" s="1">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
       </c>
       <c r="E19" s="1">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
@@ -2530,19 +2530,19 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B20" s="2">
-        <v>0.3277589380741119</v>
+        <v>0.3247784078121185</v>
       </c>
       <c r="C20" s="1">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
       </c>
       <c r="E20" s="1">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
@@ -2556,19 +2556,19 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B21" s="2">
-        <v>0.3109985589981079</v>
+        <v>0.3193351924419403</v>
       </c>
       <c r="C21" s="1">
-        <v>334</v>
+        <v>352</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
       </c>
       <c r="E21" s="1">
-        <v>334</v>
+        <v>352</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
@@ -2582,19 +2582,19 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B22" s="2">
-        <v>0.3035494685173035</v>
+        <v>0.3030055463314056</v>
       </c>
       <c r="C22" s="1">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="D22" s="1">
         <v>0</v>
       </c>
       <c r="E22" s="1">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
@@ -2608,19 +2608,19 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B23" s="2">
-        <v>0.2961004078388214</v>
+        <v>0.2957479357719421</v>
       </c>
       <c r="C23" s="1">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
       </c>
       <c r="E23" s="1">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
@@ -2634,19 +2634,19 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B24" s="2">
-        <v>0.2942381501197815</v>
+        <v>0.2884903252124786</v>
       </c>
       <c r="C24" s="1">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D24" s="1">
         <v>0</v>
       </c>
       <c r="E24" s="1">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
@@ -2660,25 +2660,25 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="B25" s="2">
-        <v>0.2905136048793793</v>
+        <v>0.2866759300231934</v>
       </c>
       <c r="C25" s="1">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="D25" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E25" s="1">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
       </c>
       <c r="G25" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H25" s="1">
         <v>0</v>
@@ -2686,45 +2686,45 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B26" s="2">
-        <v>0.2588550746440888</v>
+        <v>0.2830471098423004</v>
       </c>
       <c r="C26" s="1">
-        <v>278</v>
+        <v>312</v>
       </c>
       <c r="D26" s="1">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="E26" s="1">
-        <v>278</v>
+        <v>308</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
       </c>
       <c r="G26" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H26" s="1">
-        <v>44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="B27" s="2">
-        <v>0.2495437413454056</v>
+        <v>0.2522022426128388</v>
       </c>
       <c r="C27" s="1">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="D27" s="1">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="E27" s="1">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="F27" s="1">
         <v>0</v>
@@ -2733,24 +2733,24 @@
         <v>0</v>
       </c>
       <c r="H27" s="1">
-        <v>0</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B28" s="2">
-        <v>0.2458192110061646</v>
+        <v>0.2431302070617676</v>
       </c>
       <c r="C28" s="1">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D28" s="1">
         <v>0</v>
       </c>
       <c r="E28" s="1">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
@@ -2764,19 +2764,19 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B29" s="2">
-        <v>0.2439569383859634</v>
+        <v>0.2395014017820358</v>
       </c>
       <c r="C29" s="1">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
       </c>
       <c r="E29" s="1">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F29" s="1">
         <v>0</v>
@@ -2790,19 +2790,19 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B30" s="2">
-        <v>0.2122984081506729</v>
+        <v>0.2376869916915894</v>
       </c>
       <c r="C30" s="1">
-        <v>228</v>
+        <v>262</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
       </c>
       <c r="E30" s="1">
-        <v>228</v>
+        <v>262</v>
       </c>
       <c r="F30" s="1">
         <v>0</v>
@@ -2816,19 +2816,19 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="B31" s="2">
-        <v>0.2067116051912308</v>
+        <v>0.2104709297418594</v>
       </c>
       <c r="C31" s="1">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="D31" s="1">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E31" s="1">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="F31" s="1">
         <v>0</v>
@@ -2837,24 +2837,24 @@
         <v>0</v>
       </c>
       <c r="H31" s="1">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B32" s="2">
-        <v>0.1974002718925476</v>
+        <v>0.2068421244621277</v>
       </c>
       <c r="C32" s="1">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="D32" s="1">
         <v>0</v>
       </c>
       <c r="E32" s="1">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
@@ -2868,19 +2868,19 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B33" s="2">
-        <v>0.1731908023357391</v>
+        <v>0.2013989090919495</v>
       </c>
       <c r="C33" s="1">
-        <v>186</v>
+        <v>222</v>
       </c>
       <c r="D33" s="1">
         <v>0</v>
       </c>
       <c r="E33" s="1">
-        <v>186</v>
+        <v>222</v>
       </c>
       <c r="F33" s="1">
         <v>0</v>
@@ -2894,19 +2894,19 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="B34" s="2">
-        <v>0.1676040142774582</v>
+        <v>0.1923268884420395</v>
       </c>
       <c r="C34" s="1">
-        <v>180</v>
+        <v>212</v>
       </c>
       <c r="D34" s="1">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="E34" s="1">
-        <v>180</v>
+        <v>212</v>
       </c>
       <c r="F34" s="1">
         <v>0</v>
@@ -2915,24 +2915,24 @@
         <v>0</v>
       </c>
       <c r="H34" s="1">
-        <v>48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B35" s="2">
-        <v>0.163879469037056</v>
+        <v>0.1687396168708801</v>
       </c>
       <c r="C35" s="1">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="D35" s="1">
         <v>0</v>
       </c>
       <c r="E35" s="1">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="F35" s="1">
         <v>0</v>
@@ -2946,19 +2946,19 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="B36" s="2">
-        <v>0.163879469037056</v>
+        <v>0.1632964164018631</v>
       </c>
       <c r="C36" s="1">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D36" s="1">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="E36" s="1">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F36" s="1">
         <v>0</v>
@@ -2967,24 +2967,24 @@
         <v>0</v>
       </c>
       <c r="H36" s="1">
-        <v>0</v>
+        <v>48</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1" t="s">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="B37" s="2">
-        <v>0.1564304083585739</v>
+        <v>0.1596675962209702</v>
       </c>
       <c r="C37" s="1">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="D37" s="1">
-        <v>976</v>
+        <v>0</v>
       </c>
       <c r="E37" s="1">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="F37" s="1">
         <v>0</v>
@@ -2993,30 +2993,30 @@
         <v>0</v>
       </c>
       <c r="H37" s="1">
-        <v>976</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="B38" s="2">
-        <v>0.1461879462003708</v>
+        <v>0.1596675962209702</v>
       </c>
       <c r="C38" s="1">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="D38" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38" s="1">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="F38" s="1">
         <v>0</v>
       </c>
       <c r="G38" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H38" s="1">
         <v>0</v>
@@ -3027,7 +3027,7 @@
         <v>13</v>
       </c>
       <c r="B39" s="2">
-        <v>0.1387388706207275</v>
+        <v>0.1351731419563294</v>
       </c>
       <c r="C39" s="1">
         <v>149</v>
@@ -3053,7 +3053,7 @@
         <v>40</v>
       </c>
       <c r="B40" s="2">
-        <v>0.1340832114219666</v>
+        <v>0.1306371241807938</v>
       </c>
       <c r="C40" s="1">
         <v>144</v>
@@ -3079,7 +3079,7 @@
         <v>41</v>
       </c>
       <c r="B41" s="2">
-        <v>0.1154605373740196</v>
+        <v>0.1124930828809738</v>
       </c>
       <c r="C41" s="1">
         <v>124</v>
@@ -3105,7 +3105,7 @@
         <v>42</v>
       </c>
       <c r="B42" s="2">
-        <v>0.1117360070347786</v>
+        <v>0.1088642701506615</v>
       </c>
       <c r="C42" s="1">
         <v>120</v>
@@ -3131,7 +3131,7 @@
         <v>43</v>
       </c>
       <c r="B43" s="2">
-        <v>0.1117360070347786</v>
+        <v>0.1088642701506615</v>
       </c>
       <c r="C43" s="1">
         <v>120</v>
@@ -3157,7 +3157,7 @@
         <v>44</v>
       </c>
       <c r="B44" s="2">
-        <v>0.1024246737360954</v>
+        <v>0.0997922495007515</v>
       </c>
       <c r="C44" s="1">
         <v>110</v>
@@ -3183,7 +3183,7 @@
         <v>16</v>
       </c>
       <c r="B45" s="2">
-        <v>0.1005624011158943</v>
+        <v>0.09797784686088562</v>
       </c>
       <c r="C45" s="1">
         <v>108</v>
@@ -3209,7 +3209,7 @@
         <v>11</v>
       </c>
       <c r="B46" s="2">
-        <v>0.1005624011158943</v>
+        <v>0.09797784686088562</v>
       </c>
       <c r="C46" s="1">
         <v>108</v>
@@ -3235,7 +3235,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="2">
-        <v>0.09311334043741226</v>
+        <v>0.09072022885084152</v>
       </c>
       <c r="C47" s="1">
         <v>100</v>
@@ -3261,7 +3261,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="2">
-        <v>0.09311334043741226</v>
+        <v>0.09072022885084152</v>
       </c>
       <c r="C48" s="1">
         <v>100</v>
@@ -3287,7 +3287,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="2">
-        <v>0.08193973451852799</v>
+        <v>0.07983379811048508</v>
       </c>
       <c r="C49" s="1">
         <v>88</v>
@@ -3313,7 +3313,7 @@
         <v>48</v>
       </c>
       <c r="B50" s="2">
-        <v>0.08007746934890747</v>
+        <v>0.0780193954706192</v>
       </c>
       <c r="C50" s="1">
         <v>86</v>
@@ -3339,7 +3339,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="2">
-        <v>0.05959253758192062</v>
+        <v>0.05806094408035278</v>
       </c>
       <c r="C51" s="1">
         <v>64</v>
@@ -3365,7 +3365,7 @@
         <v>50</v>
       </c>
       <c r="B52" s="2">
-        <v>0.05773026868700981</v>
+        <v>0.05624654144048691</v>
       </c>
       <c r="C52" s="1">
         <v>62</v>
@@ -3391,7 +3391,7 @@
         <v>51</v>
       </c>
       <c r="B53" s="2">
-        <v>0.0558680035173893</v>
+        <v>0.05443213507533073</v>
       </c>
       <c r="C53" s="1">
         <v>60</v>
@@ -3417,7 +3417,7 @@
         <v>52</v>
       </c>
       <c r="B54" s="2">
-        <v>0.05214346945285797</v>
+        <v>0.05080332607030869</v>
       </c>
       <c r="C54" s="1">
         <v>56</v>
@@ -3443,7 +3443,7 @@
         <v>53</v>
       </c>
       <c r="B55" s="2">
-        <v>0.04655667021870613</v>
+        <v>0.04536011442542076</v>
       </c>
       <c r="C55" s="1">
         <v>50</v>
@@ -3469,7 +3469,7 @@
         <v>54</v>
       </c>
       <c r="B56" s="2">
-        <v>0.04655667021870613</v>
+        <v>0.04536011442542076</v>
       </c>
       <c r="C56" s="1">
         <v>50</v>
@@ -3495,7 +3495,7 @@
         <v>55</v>
       </c>
       <c r="B57" s="2">
-        <v>0.04469440132379532</v>
+        <v>0.04354570806026459</v>
       </c>
       <c r="C57" s="1">
         <v>48</v>
@@ -3521,7 +3521,7 @@
         <v>56</v>
       </c>
       <c r="B58" s="2">
-        <v>0.04469440132379532</v>
+        <v>0.04354570806026459</v>
       </c>
       <c r="C58" s="1">
         <v>48</v>
@@ -3547,7 +3547,7 @@
         <v>57</v>
       </c>
       <c r="B59" s="2">
-        <v>0.03724533319473267</v>
+        <v>0.03628809005022049</v>
       </c>
       <c r="C59" s="1">
         <v>40</v>
@@ -3573,7 +3573,7 @@
         <v>58</v>
       </c>
       <c r="B60" s="2">
-        <v>0.03724533319473267</v>
+        <v>0.03628809005022049</v>
       </c>
       <c r="C60" s="1">
         <v>40</v>
@@ -3599,7 +3599,7 @@
         <v>59</v>
       </c>
       <c r="B61" s="2">
-        <v>0.03538306802511215</v>
+        <v>0.03447368741035461</v>
       </c>
       <c r="C61" s="1">
         <v>38</v>
@@ -3625,7 +3625,7 @@
         <v>60</v>
       </c>
       <c r="B62" s="2">
-        <v>0.03352080285549164</v>
+        <v>0.03265928104519844</v>
       </c>
       <c r="C62" s="1">
         <v>36</v>
@@ -3651,7 +3651,7 @@
         <v>61</v>
       </c>
       <c r="B63" s="2">
-        <v>0.03352080285549164</v>
+        <v>0.03265928104519844</v>
       </c>
       <c r="C63" s="1">
         <v>36</v>
@@ -3677,7 +3677,7 @@
         <v>62</v>
       </c>
       <c r="B64" s="2">
-        <v>0.02979626879096031</v>
+        <v>0.02903047204017639</v>
       </c>
       <c r="C64" s="1">
         <v>32</v>
@@ -3703,7 +3703,7 @@
         <v>63</v>
       </c>
       <c r="B65" s="2">
-        <v>0.02793400175869465</v>
+        <v>0.02721606753766537</v>
       </c>
       <c r="C65" s="1">
         <v>30</v>
@@ -3729,7 +3729,7 @@
         <v>64</v>
       </c>
       <c r="B66" s="2">
-        <v>0.02793400175869465</v>
+        <v>0.02721606753766537</v>
       </c>
       <c r="C66" s="1">
         <v>30</v>
@@ -3755,7 +3755,7 @@
         <v>65</v>
       </c>
       <c r="B67" s="2">
-        <v>0.02607173472642899</v>
+        <v>0.02540166303515434</v>
       </c>
       <c r="C67" s="1">
         <v>28</v>
@@ -3781,7 +3781,7 @@
         <v>66</v>
       </c>
       <c r="B68" s="2">
-        <v>0.02607173472642899</v>
+        <v>0.02540166303515434</v>
       </c>
       <c r="C68" s="1">
         <v>28</v>
@@ -3807,7 +3807,7 @@
         <v>67</v>
       </c>
       <c r="B69" s="2">
-        <v>0.02607173472642899</v>
+        <v>0.02540166303515434</v>
       </c>
       <c r="C69" s="1">
         <v>28</v>
@@ -3833,7 +3833,7 @@
         <v>68</v>
       </c>
       <c r="B70" s="2">
-        <v>0.02607173472642899</v>
+        <v>0.02540166303515434</v>
       </c>
       <c r="C70" s="1">
         <v>28</v>
@@ -3859,7 +3859,7 @@
         <v>69</v>
       </c>
       <c r="B71" s="2">
-        <v>0.02607173472642899</v>
+        <v>0.02540166303515434</v>
       </c>
       <c r="C71" s="1">
         <v>28</v>
@@ -3885,7 +3885,7 @@
         <v>70</v>
       </c>
       <c r="B72" s="2">
-        <v>0.02607173472642899</v>
+        <v>0.02540166303515434</v>
       </c>
       <c r="C72" s="1">
         <v>28</v>
@@ -3911,7 +3911,7 @@
         <v>71</v>
       </c>
       <c r="B73" s="2">
-        <v>0.02420946769416332</v>
+        <v>0.02358725853264332</v>
       </c>
       <c r="C73" s="1">
         <v>26</v>
@@ -3937,7 +3937,7 @@
         <v>72</v>
       </c>
       <c r="B74" s="2">
-        <v>0.01676040142774582</v>
+        <v>0.01632964052259922</v>
       </c>
       <c r="C74" s="1">
         <v>18</v>
@@ -3963,7 +3963,7 @@
         <v>73</v>
       </c>
       <c r="B75" s="2">
-        <v>0.01117360033094883</v>
+        <v>0.01088642701506615</v>
       </c>
       <c r="C75" s="1">
         <v>12</v>
@@ -3989,16 +3989,16 @@
         <v>74</v>
       </c>
       <c r="B76" s="2">
-        <v>0.009311333298683167</v>
+        <v>0.01088642701506615</v>
       </c>
       <c r="C76" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D76" s="1">
         <v>0</v>
       </c>
       <c r="E76" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F76" s="1">
         <v>0</v>
@@ -4015,16 +4015,16 @@
         <v>75</v>
       </c>
       <c r="B77" s="2">
-        <v>0.007449067197740078</v>
+        <v>0.009072022512555122</v>
       </c>
       <c r="C77" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D77" s="1">
         <v>0</v>
       </c>
       <c r="E77" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F77" s="1">
         <v>0</v>
@@ -4041,7 +4041,7 @@
         <v>76</v>
       </c>
       <c r="B78" s="2">
-        <v>0.007449067197740078</v>
+        <v>0.007257618010044098</v>
       </c>
       <c r="C78" s="1">
         <v>8</v>
@@ -4067,7 +4067,7 @@
         <v>77</v>
       </c>
       <c r="B79" s="2">
-        <v>0.007449067197740078</v>
+        <v>0.007257618010044098</v>
       </c>
       <c r="C79" s="1">
         <v>8</v>
@@ -4093,7 +4093,7 @@
         <v>78</v>
       </c>
       <c r="B80" s="2">
-        <v>0.003724533598870039</v>
+        <v>0.003628809005022049</v>
       </c>
       <c r="C80" s="1">
         <v>4</v>

--- a/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
+++ b/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
@@ -80,19 +80,19 @@
     <t>mf_w.l</t>
   </si>
   <si>
+    <t>at32f415_tmr.o</t>
+  </si>
+  <si>
     <t>at32f415_crm.o</t>
   </si>
   <si>
-    <t>at32f415_tmr.o</t>
+    <t>wk_tmr.o</t>
   </si>
   <si>
     <t>at32f415_wk_config.o</t>
   </si>
   <si>
     <t>at32_spiflash.o</t>
-  </si>
-  <si>
-    <t>wk_tmr.o</t>
   </si>
   <si>
     <t>at32f415_adc.o</t>
@@ -444,61 +444,61 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="79"/>
                 <c:pt idx="0">
-                  <c:v>27.20626640319824</c:v>
+                  <c:v>27.22047996520996</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>26.73629188537598</c:v>
+                  <c:v>26.7502613067627</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>26.10966110229492</c:v>
+                  <c:v>26.1233024597168</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.229764938354492</c:v>
+                  <c:v>4.231975078582764</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.864229679107666</c:v>
+                  <c:v>3.866248607635498</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.976501226425171</c:v>
+                  <c:v>2.97805643081665</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.584856510162354</c:v>
+                  <c:v>2.560083627700806</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.253263711929321</c:v>
+                  <c:v>1.253918528556824</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.14882504940033</c:v>
+                  <c:v>1.149425268173218</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.9921671152114868</c:v>
+                  <c:v>0.9926854968070984</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.939947783946991</c:v>
+                  <c:v>0.9404388666152954</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.6788511872291565</c:v>
+                  <c:v>0.6792058348655701</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.4438642263412476</c:v>
+                  <c:v>0.4440961480140686</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.4177545607089996</c:v>
+                  <c:v>0.3657262325286865</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.1305482983589172</c:v>
+                  <c:v>0.156739816069603</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.1044386401772499</c:v>
+                  <c:v>0.1044932082295418</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.1044386401772499</c:v>
+                  <c:v>0.1044932082295418</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.05221932008862495</c:v>
+                  <c:v>0.05224660411477089</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.02610966004431248</c:v>
+                  <c:v>0.02612330205738545</c:v>
                 </c:pt>
                 <c:pt idx="78">
                   <c:v>0</c:v>
@@ -593,37 +593,37 @@
                   <c:v>output_handle.o</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>at32f415_tmr.o</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>at32f415_crm.o</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>encoderec11.o</c:v>
                 </c:pt>
-                <c:pt idx="9">
-                  <c:v>at32f415_tmr.o</c:v>
-                </c:pt>
                 <c:pt idx="10">
+                  <c:v>main.o</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>at32f415_int.o</c:v>
                 </c:pt>
-                <c:pt idx="11">
-                  <c:v>main.o</c:v>
-                </c:pt>
                 <c:pt idx="12">
+                  <c:v>wk_tmr.o</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>key.o</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>startup_at32f415.o</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>tmt.o</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>at32f415_wk_config.o</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>at32_spiflash.o</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>wk_tmr.o</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>at32f415_adc.o</c:v>
@@ -818,238 +818,238 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="79"/>
                 <c:pt idx="0">
-                  <c:v>72.69774627685547</c:v>
+                  <c:v>71.4697265625</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.766440868377686</c:v>
+                  <c:v>4.766194343566895</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.741302251815796</c:v>
+                  <c:v>4.7198166847229</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.309736967086792</c:v>
+                  <c:v>2.572175264358521</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.970443367958069</c:v>
+                  <c:v>1.937158346176148</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.787188529968262</c:v>
+                  <c:v>1.756999015808106</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.496883749961853</c:v>
+                  <c:v>1.259331226348877</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.6912881135940552</c:v>
+                  <c:v>0.9382553100585938</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.6459280252456665</c:v>
+                  <c:v>0.6796107888221741</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.5824238657951355</c:v>
+                  <c:v>0.6350169181823731</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.4608587622642517</c:v>
+                  <c:v>0.44058758020401</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.4227562546730042</c:v>
+                  <c:v>0.4334525465965271</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.3792105615139008</c:v>
+                  <c:v>0.4191825091838837</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.3665097057819367</c:v>
+                  <c:v>0.3728048801422119</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.3538088798522949</c:v>
+                  <c:v>0.3603185713291168</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.3392936587333679</c:v>
+                  <c:v>0.3478322923183441</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.3265928328037262</c:v>
+                  <c:v>0.3406972587108612</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.3247784078121185</c:v>
+                  <c:v>0.321075975894928</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.3193351924419403</c:v>
+                  <c:v>0.3139409422874451</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.3030055463314056</c:v>
+                  <c:v>0.2978871464729309</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.2957479357719421</c:v>
+                  <c:v>0.290752112865448</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.2884903252124786</c:v>
+                  <c:v>0.2836171090602875</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.2866759300231934</c:v>
+                  <c:v>0.2818333506584168</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.2830471098423004</c:v>
+                  <c:v>0.2782658338546753</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.2522022426128388</c:v>
+                  <c:v>0.2479419857263565</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.2431302070617676</c:v>
+                  <c:v>0.2390232086181641</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.2395014017820358</c:v>
+                  <c:v>0.2354557067155838</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.2376869916915894</c:v>
+                  <c:v>0.2336719483137131</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.2104709297418594</c:v>
+                  <c:v>0.2069156169891357</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.2068421244621277</c:v>
+                  <c:v>0.2033481150865555</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.2013989090919495</c:v>
+                  <c:v>0.1979968398809433</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.1923268884420395</c:v>
+                  <c:v>0.1890780627727509</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.1687396168708801</c:v>
+                  <c:v>0.165889248251915</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.1632964164018631</c:v>
+                  <c:v>0.160537987947464</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.1596675962209702</c:v>
+                  <c:v>0.1569704711437225</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.1596675962209702</c:v>
+                  <c:v>0.1569704711437225</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.1351731419563294</c:v>
+                  <c:v>0.1328897774219513</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.1306371241807938</c:v>
+                  <c:v>0.1284303814172745</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.1124930828809738</c:v>
+                  <c:v>0.1105928346514702</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.1088642701506615</c:v>
+                  <c:v>0.1070253178477287</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.1088642701506615</c:v>
+                  <c:v>0.1070253178477287</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.0997922495007515</c:v>
+                  <c:v>0.09810654073953629</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.09797784686088562</c:v>
+                  <c:v>0.09632278978824616</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.09797784686088562</c:v>
+                  <c:v>0.09632278978824616</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.09072022885084152</c:v>
+                  <c:v>0.08918776363134384</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.09072022885084152</c:v>
+                  <c:v>0.08918776363134384</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.07983379811048508</c:v>
+                  <c:v>0.07848523557186127</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.0780193954706192</c:v>
+                  <c:v>0.07670147716999054</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.05806094408035278</c:v>
+                  <c:v>0.05708017200231552</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.05624654144048691</c:v>
+                  <c:v>0.05529641732573509</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.05443213507533073</c:v>
+                  <c:v>0.05351265892386437</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.05080332607030869</c:v>
+                  <c:v>0.04994514957070351</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.04536011442542076</c:v>
+                  <c:v>0.04459388181567192</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.04536011442542076</c:v>
+                  <c:v>0.04459388181567192</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.04354570806026459</c:v>
+                  <c:v>0.04281012713909149</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.04354570806026459</c:v>
+                  <c:v>0.04281012713909149</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.03628809005022049</c:v>
+                  <c:v>0.03567510843276978</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.03628809005022049</c:v>
+                  <c:v>0.03567510843276978</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.03447368741035461</c:v>
+                  <c:v>0.03389135003089905</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.03265928104519844</c:v>
+                  <c:v>0.03210759535431862</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.03265928104519844</c:v>
+                  <c:v>0.03210759535431862</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.02903047204017639</c:v>
+                  <c:v>0.02854008600115776</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.02721606753766537</c:v>
+                  <c:v>0.02675632946193218</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.02721606753766537</c:v>
+                  <c:v>0.02675632946193218</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.02540166303515434</c:v>
+                  <c:v>0.02497257478535175</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.02540166303515434</c:v>
+                  <c:v>0.02497257478535175</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.02540166303515434</c:v>
+                  <c:v>0.02497257478535175</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.02540166303515434</c:v>
+                  <c:v>0.02497257478535175</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.02540166303515434</c:v>
+                  <c:v>0.02497257478535175</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.02540166303515434</c:v>
+                  <c:v>0.02497257478535175</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.02358725853264332</c:v>
+                  <c:v>0.02318882010877132</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.01632964052259922</c:v>
+                  <c:v>0.01605379767715931</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.01088642701506615</c:v>
+                  <c:v>0.01070253178477287</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.01088642701506615</c:v>
+                  <c:v>0.01070253178477287</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.009072022512555122</c:v>
+                  <c:v>0.008918777108192444</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0.007257618010044098</c:v>
+                  <c:v>0.00713502150028944</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>0.007257618010044098</c:v>
+                  <c:v>0.00713502150028944</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>0.003628809005022049</c:v>
+                  <c:v>0.00356751075014472</c:v>
                 </c:pt>
                 <c:pt idx="78">
                   <c:v>0</c:v>
@@ -1516,7 +1516,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>27.20626640319824</v>
+        <v>27.22047996520996</v>
       </c>
       <c r="C3" s="1">
         <v>1042</v>
@@ -1542,7 +1542,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>26.73629188537598</v>
+        <v>26.7502613067627</v>
       </c>
       <c r="C4" s="1">
         <v>1024</v>
@@ -1568,7 +1568,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>26.10966110229492</v>
+        <v>26.1233024597168</v>
       </c>
       <c r="C5" s="1">
         <v>1000</v>
@@ -1594,16 +1594,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>4.229764938354492</v>
+        <v>4.231975078582764</v>
       </c>
       <c r="C6" s="1">
         <v>162</v>
       </c>
       <c r="D6" s="1">
-        <v>2546</v>
+        <v>2884</v>
       </c>
       <c r="E6" s="1">
-        <v>2370</v>
+        <v>2708</v>
       </c>
       <c r="F6" s="1">
         <v>24</v>
@@ -1620,7 +1620,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>3.864229679107666</v>
+        <v>3.866248607635498</v>
       </c>
       <c r="C7" s="1">
         <v>148</v>
@@ -1646,7 +1646,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>2.976501226425171</v>
+        <v>2.97805643081665</v>
       </c>
       <c r="C8" s="1">
         <v>114</v>
@@ -1672,16 +1672,16 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>2.584856510162354</v>
+        <v>2.560083627700806</v>
       </c>
       <c r="C9" s="1">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D9" s="1">
-        <v>1650</v>
+        <v>1412</v>
       </c>
       <c r="E9" s="1">
-        <v>1568</v>
+        <v>1330</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
@@ -1690,7 +1690,7 @@
         <v>82</v>
       </c>
       <c r="H9" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1698,7 +1698,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>1.253263711929321</v>
+        <v>1.253918528556824</v>
       </c>
       <c r="C10" s="1">
         <v>48</v>
@@ -1724,7 +1724,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>1.14882504940033</v>
+        <v>1.149425268173218</v>
       </c>
       <c r="C11" s="1">
         <v>44</v>
@@ -1750,16 +1750,16 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.9921671152114868</v>
+        <v>0.9926854968070984</v>
       </c>
       <c r="C12" s="1">
         <v>38</v>
       </c>
       <c r="D12" s="1">
-        <v>5254</v>
+        <v>5344</v>
       </c>
       <c r="E12" s="1">
-        <v>5242</v>
+        <v>5332</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
@@ -1776,7 +1776,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.939947783946991</v>
+        <v>0.9404388666152954</v>
       </c>
       <c r="C13" s="1">
         <v>36</v>
@@ -1802,7 +1802,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.6788511872291565</v>
+        <v>0.6792058348655701</v>
       </c>
       <c r="C14" s="1">
         <v>26</v>
@@ -1828,7 +1828,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.4438642263412476</v>
+        <v>0.4440961480140686</v>
       </c>
       <c r="C15" s="1">
         <v>17</v>
@@ -1854,22 +1854,22 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.4177545607089996</v>
+        <v>0.3657262325286865</v>
       </c>
       <c r="C16" s="1">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D16" s="1">
-        <v>508</v>
+        <v>486</v>
       </c>
       <c r="E16" s="1">
-        <v>500</v>
+        <v>480</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H16" s="1">
         <v>8</v>
@@ -1880,16 +1880,16 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.1305482983589172</v>
+        <v>0.156739816069603</v>
       </c>
       <c r="C17" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D17" s="1">
-        <v>4124</v>
+        <v>5292</v>
       </c>
       <c r="E17" s="1">
-        <v>4122</v>
+        <v>5290</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
@@ -1898,7 +1898,7 @@
         <v>2</v>
       </c>
       <c r="H17" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1906,7 +1906,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.1044386401772499</v>
+        <v>0.1044932082295418</v>
       </c>
       <c r="C18" s="1">
         <v>4</v>
@@ -1932,7 +1932,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.1044386401772499</v>
+        <v>0.1044932082295418</v>
       </c>
       <c r="C19" s="1">
         <v>4</v>
@@ -1958,7 +1958,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.05221932008862495</v>
+        <v>0.05224660411477089</v>
       </c>
       <c r="C20" s="1">
         <v>2</v>
@@ -1984,16 +1984,16 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.02610966004431248</v>
+        <v>0.02612330205738545</v>
       </c>
       <c r="C21" s="1">
         <v>1</v>
       </c>
       <c r="D21" s="1">
-        <v>466</v>
+        <v>494</v>
       </c>
       <c r="E21" s="1">
-        <v>466</v>
+        <v>494</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
@@ -2091,7 +2091,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>72.69774627685547</v>
+        <v>71.4697265625</v>
       </c>
       <c r="C3" s="1">
         <v>80134</v>
@@ -2117,16 +2117,16 @@
         <v>10</v>
       </c>
       <c r="B4" s="2">
-        <v>4.766440868377686</v>
+        <v>4.766194343566895</v>
       </c>
       <c r="C4" s="1">
-        <v>5254</v>
+        <v>5344</v>
       </c>
       <c r="D4" s="1">
         <v>38</v>
       </c>
       <c r="E4" s="1">
-        <v>5242</v>
+        <v>5332</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
@@ -2143,16 +2143,16 @@
         <v>15</v>
       </c>
       <c r="B5" s="2">
-        <v>3.741302251815796</v>
+        <v>4.7198166847229</v>
       </c>
       <c r="C5" s="1">
-        <v>4124</v>
+        <v>5292</v>
       </c>
       <c r="D5" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E5" s="1">
-        <v>4122</v>
+        <v>5290</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
@@ -2161,7 +2161,7 @@
         <v>2</v>
       </c>
       <c r="H5" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -2169,16 +2169,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>2.309736967086792</v>
+        <v>2.572175264358521</v>
       </c>
       <c r="C6" s="1">
-        <v>2546</v>
+        <v>2884</v>
       </c>
       <c r="D6" s="1">
         <v>162</v>
       </c>
       <c r="E6" s="1">
-        <v>2370</v>
+        <v>2708</v>
       </c>
       <c r="F6" s="1">
         <v>24</v>
@@ -2195,7 +2195,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="2">
-        <v>1.970443367958069</v>
+        <v>1.937158346176148</v>
       </c>
       <c r="C7" s="1">
         <v>2172</v>
@@ -2221,7 +2221,7 @@
         <v>20</v>
       </c>
       <c r="B8" s="2">
-        <v>1.787188529968262</v>
+        <v>1.756999015808106</v>
       </c>
       <c r="C8" s="1">
         <v>1970</v>
@@ -2247,16 +2247,16 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>1.496883749961853</v>
+        <v>1.259331226348877</v>
       </c>
       <c r="C9" s="1">
-        <v>1650</v>
+        <v>1412</v>
       </c>
       <c r="D9" s="1">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E9" s="1">
-        <v>1568</v>
+        <v>1330</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
@@ -2265,7 +2265,7 @@
         <v>82</v>
       </c>
       <c r="H9" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -2273,19 +2273,19 @@
         <v>21</v>
       </c>
       <c r="B10" s="2">
-        <v>0.6912881135940552</v>
+        <v>0.9382553100585938</v>
       </c>
       <c r="C10" s="1">
-        <v>762</v>
+        <v>1052</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
       </c>
       <c r="E10" s="1">
-        <v>754</v>
+        <v>1052</v>
       </c>
       <c r="F10" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -2296,129 +2296,129 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="B11" s="2">
-        <v>0.6459280252456665</v>
+        <v>0.6796107888221741</v>
       </c>
       <c r="C11" s="1">
-        <v>712</v>
+        <v>762</v>
       </c>
       <c r="D11" s="1">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="E11" s="1">
-        <v>600</v>
+        <v>754</v>
       </c>
       <c r="F11" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G11" s="1">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="H11" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="B12" s="2">
-        <v>0.5824238657951355</v>
+        <v>0.6350169181823731</v>
       </c>
       <c r="C12" s="1">
-        <v>642</v>
+        <v>712</v>
       </c>
       <c r="D12" s="1">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="E12" s="1">
-        <v>642</v>
+        <v>600</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="H12" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B13" s="2">
-        <v>0.4608587622642517</v>
+        <v>0.44058758020401</v>
       </c>
       <c r="C13" s="1">
-        <v>508</v>
+        <v>494</v>
       </c>
       <c r="D13" s="1">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E13" s="1">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H13" s="1">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B14" s="2">
-        <v>0.4227562546730042</v>
+        <v>0.4334525465965271</v>
       </c>
       <c r="C14" s="1">
-        <v>466</v>
+        <v>486</v>
       </c>
       <c r="D14" s="1">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E14" s="1">
-        <v>466</v>
+        <v>480</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H14" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B15" s="2">
-        <v>0.3792105615139008</v>
+        <v>0.4191825091838837</v>
       </c>
       <c r="C15" s="1">
-        <v>418</v>
+        <v>470</v>
       </c>
       <c r="D15" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E15" s="1">
-        <v>416</v>
+        <v>470</v>
       </c>
       <c r="F15" s="1">
         <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H15" s="1">
         <v>0</v>
@@ -2426,71 +2426,71 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0.3728048801422119</v>
+      </c>
+      <c r="C16" s="1">
+        <v>418</v>
+      </c>
+      <c r="D16" s="1">
         <v>2</v>
       </c>
-      <c r="B16" s="2">
-        <v>0.3665097057819367</v>
-      </c>
-      <c r="C16" s="1">
-        <v>404</v>
-      </c>
-      <c r="D16" s="1">
-        <v>1024</v>
-      </c>
       <c r="E16" s="1">
-        <v>36</v>
+        <v>416</v>
       </c>
       <c r="F16" s="1">
-        <v>368</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16" s="1">
-        <v>1024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B17" s="2">
-        <v>0.3538088798522949</v>
+        <v>0.3603185713291168</v>
       </c>
       <c r="C17" s="1">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="D17" s="1">
-        <v>148</v>
+        <v>1024</v>
       </c>
       <c r="E17" s="1">
-        <v>390</v>
+        <v>36</v>
       </c>
       <c r="F17" s="1">
-        <v>0</v>
+        <v>368</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
       </c>
       <c r="H17" s="1">
-        <v>148</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B18" s="2">
-        <v>0.3392936587333679</v>
+        <v>0.3478322923183441</v>
       </c>
       <c r="C18" s="1">
-        <v>374</v>
+        <v>390</v>
       </c>
       <c r="D18" s="1">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="E18" s="1">
-        <v>374</v>
+        <v>390</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -2499,7 +2499,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="1">
-        <v>0</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -2507,16 +2507,16 @@
         <v>24</v>
       </c>
       <c r="B19" s="2">
-        <v>0.3265928328037262</v>
+        <v>0.3406972587108612</v>
       </c>
       <c r="C19" s="1">
-        <v>360</v>
+        <v>382</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
       </c>
       <c r="E19" s="1">
-        <v>360</v>
+        <v>382</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
@@ -2533,16 +2533,16 @@
         <v>25</v>
       </c>
       <c r="B20" s="2">
-        <v>0.3247784078121185</v>
+        <v>0.321075975894928</v>
       </c>
       <c r="C20" s="1">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
       </c>
       <c r="E20" s="1">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
@@ -2559,7 +2559,7 @@
         <v>26</v>
       </c>
       <c r="B21" s="2">
-        <v>0.3193351924419403</v>
+        <v>0.3139409422874451</v>
       </c>
       <c r="C21" s="1">
         <v>352</v>
@@ -2585,7 +2585,7 @@
         <v>27</v>
       </c>
       <c r="B22" s="2">
-        <v>0.3030055463314056</v>
+        <v>0.2978871464729309</v>
       </c>
       <c r="C22" s="1">
         <v>334</v>
@@ -2611,7 +2611,7 @@
         <v>28</v>
       </c>
       <c r="B23" s="2">
-        <v>0.2957479357719421</v>
+        <v>0.290752112865448</v>
       </c>
       <c r="C23" s="1">
         <v>326</v>
@@ -2637,7 +2637,7 @@
         <v>29</v>
       </c>
       <c r="B24" s="2">
-        <v>0.2884903252124786</v>
+        <v>0.2836171090602875</v>
       </c>
       <c r="C24" s="1">
         <v>318</v>
@@ -2663,7 +2663,7 @@
         <v>30</v>
       </c>
       <c r="B25" s="2">
-        <v>0.2866759300231934</v>
+        <v>0.2818333506584168</v>
       </c>
       <c r="C25" s="1">
         <v>316</v>
@@ -2689,7 +2689,7 @@
         <v>17</v>
       </c>
       <c r="B26" s="2">
-        <v>0.2830471098423004</v>
+        <v>0.2782658338546753</v>
       </c>
       <c r="C26" s="1">
         <v>312</v>
@@ -2715,7 +2715,7 @@
         <v>9</v>
       </c>
       <c r="B27" s="2">
-        <v>0.2522022426128388</v>
+        <v>0.2479419857263565</v>
       </c>
       <c r="C27" s="1">
         <v>278</v>
@@ -2741,7 +2741,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="2">
-        <v>0.2431302070617676</v>
+        <v>0.2390232086181641</v>
       </c>
       <c r="C28" s="1">
         <v>268</v>
@@ -2767,7 +2767,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="2">
-        <v>0.2395014017820358</v>
+        <v>0.2354557067155838</v>
       </c>
       <c r="C29" s="1">
         <v>264</v>
@@ -2793,7 +2793,7 @@
         <v>33</v>
       </c>
       <c r="B30" s="2">
-        <v>0.2376869916915894</v>
+        <v>0.2336719483137131</v>
       </c>
       <c r="C30" s="1">
         <v>262</v>
@@ -2819,7 +2819,7 @@
         <v>3</v>
       </c>
       <c r="B31" s="2">
-        <v>0.2104709297418594</v>
+        <v>0.2069156169891357</v>
       </c>
       <c r="C31" s="1">
         <v>232</v>
@@ -2845,7 +2845,7 @@
         <v>34</v>
       </c>
       <c r="B32" s="2">
-        <v>0.2068421244621277</v>
+        <v>0.2033481150865555</v>
       </c>
       <c r="C32" s="1">
         <v>228</v>
@@ -2871,7 +2871,7 @@
         <v>35</v>
       </c>
       <c r="B33" s="2">
-        <v>0.2013989090919495</v>
+        <v>0.1979968398809433</v>
       </c>
       <c r="C33" s="1">
         <v>222</v>
@@ -2897,7 +2897,7 @@
         <v>36</v>
       </c>
       <c r="B34" s="2">
-        <v>0.1923268884420395</v>
+        <v>0.1890780627727509</v>
       </c>
       <c r="C34" s="1">
         <v>212</v>
@@ -2923,7 +2923,7 @@
         <v>37</v>
       </c>
       <c r="B35" s="2">
-        <v>0.1687396168708801</v>
+        <v>0.165889248251915</v>
       </c>
       <c r="C35" s="1">
         <v>186</v>
@@ -2949,7 +2949,7 @@
         <v>8</v>
       </c>
       <c r="B36" s="2">
-        <v>0.1632964164018631</v>
+        <v>0.160537987947464</v>
       </c>
       <c r="C36" s="1">
         <v>180</v>
@@ -2975,7 +2975,7 @@
         <v>38</v>
       </c>
       <c r="B37" s="2">
-        <v>0.1596675962209702</v>
+        <v>0.1569704711437225</v>
       </c>
       <c r="C37" s="1">
         <v>176</v>
@@ -3001,7 +3001,7 @@
         <v>39</v>
       </c>
       <c r="B38" s="2">
-        <v>0.1596675962209702</v>
+        <v>0.1569704711437225</v>
       </c>
       <c r="C38" s="1">
         <v>176</v>
@@ -3027,7 +3027,7 @@
         <v>13</v>
       </c>
       <c r="B39" s="2">
-        <v>0.1351731419563294</v>
+        <v>0.1328897774219513</v>
       </c>
       <c r="C39" s="1">
         <v>149</v>
@@ -3053,7 +3053,7 @@
         <v>40</v>
       </c>
       <c r="B40" s="2">
-        <v>0.1306371241807938</v>
+        <v>0.1284303814172745</v>
       </c>
       <c r="C40" s="1">
         <v>144</v>
@@ -3079,7 +3079,7 @@
         <v>41</v>
       </c>
       <c r="B41" s="2">
-        <v>0.1124930828809738</v>
+        <v>0.1105928346514702</v>
       </c>
       <c r="C41" s="1">
         <v>124</v>
@@ -3105,7 +3105,7 @@
         <v>42</v>
       </c>
       <c r="B42" s="2">
-        <v>0.1088642701506615</v>
+        <v>0.1070253178477287</v>
       </c>
       <c r="C42" s="1">
         <v>120</v>
@@ -3131,7 +3131,7 @@
         <v>43</v>
       </c>
       <c r="B43" s="2">
-        <v>0.1088642701506615</v>
+        <v>0.1070253178477287</v>
       </c>
       <c r="C43" s="1">
         <v>120</v>
@@ -3157,7 +3157,7 @@
         <v>44</v>
       </c>
       <c r="B44" s="2">
-        <v>0.0997922495007515</v>
+        <v>0.09810654073953629</v>
       </c>
       <c r="C44" s="1">
         <v>110</v>
@@ -3183,7 +3183,7 @@
         <v>16</v>
       </c>
       <c r="B45" s="2">
-        <v>0.09797784686088562</v>
+        <v>0.09632278978824616</v>
       </c>
       <c r="C45" s="1">
         <v>108</v>
@@ -3209,7 +3209,7 @@
         <v>11</v>
       </c>
       <c r="B46" s="2">
-        <v>0.09797784686088562</v>
+        <v>0.09632278978824616</v>
       </c>
       <c r="C46" s="1">
         <v>108</v>
@@ -3235,7 +3235,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="2">
-        <v>0.09072022885084152</v>
+        <v>0.08918776363134384</v>
       </c>
       <c r="C47" s="1">
         <v>100</v>
@@ -3261,7 +3261,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="2">
-        <v>0.09072022885084152</v>
+        <v>0.08918776363134384</v>
       </c>
       <c r="C48" s="1">
         <v>100</v>
@@ -3287,7 +3287,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="2">
-        <v>0.07983379811048508</v>
+        <v>0.07848523557186127</v>
       </c>
       <c r="C49" s="1">
         <v>88</v>
@@ -3313,7 +3313,7 @@
         <v>48</v>
       </c>
       <c r="B50" s="2">
-        <v>0.0780193954706192</v>
+        <v>0.07670147716999054</v>
       </c>
       <c r="C50" s="1">
         <v>86</v>
@@ -3339,7 +3339,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="2">
-        <v>0.05806094408035278</v>
+        <v>0.05708017200231552</v>
       </c>
       <c r="C51" s="1">
         <v>64</v>
@@ -3365,7 +3365,7 @@
         <v>50</v>
       </c>
       <c r="B52" s="2">
-        <v>0.05624654144048691</v>
+        <v>0.05529641732573509</v>
       </c>
       <c r="C52" s="1">
         <v>62</v>
@@ -3391,7 +3391,7 @@
         <v>51</v>
       </c>
       <c r="B53" s="2">
-        <v>0.05443213507533073</v>
+        <v>0.05351265892386437</v>
       </c>
       <c r="C53" s="1">
         <v>60</v>
@@ -3417,7 +3417,7 @@
         <v>52</v>
       </c>
       <c r="B54" s="2">
-        <v>0.05080332607030869</v>
+        <v>0.04994514957070351</v>
       </c>
       <c r="C54" s="1">
         <v>56</v>
@@ -3443,7 +3443,7 @@
         <v>53</v>
       </c>
       <c r="B55" s="2">
-        <v>0.04536011442542076</v>
+        <v>0.04459388181567192</v>
       </c>
       <c r="C55" s="1">
         <v>50</v>
@@ -3469,7 +3469,7 @@
         <v>54</v>
       </c>
       <c r="B56" s="2">
-        <v>0.04536011442542076</v>
+        <v>0.04459388181567192</v>
       </c>
       <c r="C56" s="1">
         <v>50</v>
@@ -3495,7 +3495,7 @@
         <v>55</v>
       </c>
       <c r="B57" s="2">
-        <v>0.04354570806026459</v>
+        <v>0.04281012713909149</v>
       </c>
       <c r="C57" s="1">
         <v>48</v>
@@ -3521,7 +3521,7 @@
         <v>56</v>
       </c>
       <c r="B58" s="2">
-        <v>0.04354570806026459</v>
+        <v>0.04281012713909149</v>
       </c>
       <c r="C58" s="1">
         <v>48</v>
@@ -3547,7 +3547,7 @@
         <v>57</v>
       </c>
       <c r="B59" s="2">
-        <v>0.03628809005022049</v>
+        <v>0.03567510843276978</v>
       </c>
       <c r="C59" s="1">
         <v>40</v>
@@ -3573,7 +3573,7 @@
         <v>58</v>
       </c>
       <c r="B60" s="2">
-        <v>0.03628809005022049</v>
+        <v>0.03567510843276978</v>
       </c>
       <c r="C60" s="1">
         <v>40</v>
@@ -3599,7 +3599,7 @@
         <v>59</v>
       </c>
       <c r="B61" s="2">
-        <v>0.03447368741035461</v>
+        <v>0.03389135003089905</v>
       </c>
       <c r="C61" s="1">
         <v>38</v>
@@ -3625,7 +3625,7 @@
         <v>60</v>
       </c>
       <c r="B62" s="2">
-        <v>0.03265928104519844</v>
+        <v>0.03210759535431862</v>
       </c>
       <c r="C62" s="1">
         <v>36</v>
@@ -3651,7 +3651,7 @@
         <v>61</v>
       </c>
       <c r="B63" s="2">
-        <v>0.03265928104519844</v>
+        <v>0.03210759535431862</v>
       </c>
       <c r="C63" s="1">
         <v>36</v>
@@ -3677,7 +3677,7 @@
         <v>62</v>
       </c>
       <c r="B64" s="2">
-        <v>0.02903047204017639</v>
+        <v>0.02854008600115776</v>
       </c>
       <c r="C64" s="1">
         <v>32</v>
@@ -3703,7 +3703,7 @@
         <v>63</v>
       </c>
       <c r="B65" s="2">
-        <v>0.02721606753766537</v>
+        <v>0.02675632946193218</v>
       </c>
       <c r="C65" s="1">
         <v>30</v>
@@ -3729,7 +3729,7 @@
         <v>64</v>
       </c>
       <c r="B66" s="2">
-        <v>0.02721606753766537</v>
+        <v>0.02675632946193218</v>
       </c>
       <c r="C66" s="1">
         <v>30</v>
@@ -3755,7 +3755,7 @@
         <v>65</v>
       </c>
       <c r="B67" s="2">
-        <v>0.02540166303515434</v>
+        <v>0.02497257478535175</v>
       </c>
       <c r="C67" s="1">
         <v>28</v>
@@ -3781,7 +3781,7 @@
         <v>66</v>
       </c>
       <c r="B68" s="2">
-        <v>0.02540166303515434</v>
+        <v>0.02497257478535175</v>
       </c>
       <c r="C68" s="1">
         <v>28</v>
@@ -3807,7 +3807,7 @@
         <v>67</v>
       </c>
       <c r="B69" s="2">
-        <v>0.02540166303515434</v>
+        <v>0.02497257478535175</v>
       </c>
       <c r="C69" s="1">
         <v>28</v>
@@ -3833,7 +3833,7 @@
         <v>68</v>
       </c>
       <c r="B70" s="2">
-        <v>0.02540166303515434</v>
+        <v>0.02497257478535175</v>
       </c>
       <c r="C70" s="1">
         <v>28</v>
@@ -3859,7 +3859,7 @@
         <v>69</v>
       </c>
       <c r="B71" s="2">
-        <v>0.02540166303515434</v>
+        <v>0.02497257478535175</v>
       </c>
       <c r="C71" s="1">
         <v>28</v>
@@ -3885,7 +3885,7 @@
         <v>70</v>
       </c>
       <c r="B72" s="2">
-        <v>0.02540166303515434</v>
+        <v>0.02497257478535175</v>
       </c>
       <c r="C72" s="1">
         <v>28</v>
@@ -3911,7 +3911,7 @@
         <v>71</v>
       </c>
       <c r="B73" s="2">
-        <v>0.02358725853264332</v>
+        <v>0.02318882010877132</v>
       </c>
       <c r="C73" s="1">
         <v>26</v>
@@ -3937,7 +3937,7 @@
         <v>72</v>
       </c>
       <c r="B74" s="2">
-        <v>0.01632964052259922</v>
+        <v>0.01605379767715931</v>
       </c>
       <c r="C74" s="1">
         <v>18</v>
@@ -3963,7 +3963,7 @@
         <v>73</v>
       </c>
       <c r="B75" s="2">
-        <v>0.01088642701506615</v>
+        <v>0.01070253178477287</v>
       </c>
       <c r="C75" s="1">
         <v>12</v>
@@ -3989,7 +3989,7 @@
         <v>74</v>
       </c>
       <c r="B76" s="2">
-        <v>0.01088642701506615</v>
+        <v>0.01070253178477287</v>
       </c>
       <c r="C76" s="1">
         <v>12</v>
@@ -4015,7 +4015,7 @@
         <v>75</v>
       </c>
       <c r="B77" s="2">
-        <v>0.009072022512555122</v>
+        <v>0.008918777108192444</v>
       </c>
       <c r="C77" s="1">
         <v>10</v>
@@ -4041,7 +4041,7 @@
         <v>76</v>
       </c>
       <c r="B78" s="2">
-        <v>0.007257618010044098</v>
+        <v>0.00713502150028944</v>
       </c>
       <c r="C78" s="1">
         <v>8</v>
@@ -4067,7 +4067,7 @@
         <v>77</v>
       </c>
       <c r="B79" s="2">
-        <v>0.007257618010044098</v>
+        <v>0.00713502150028944</v>
       </c>
       <c r="C79" s="1">
         <v>8</v>
@@ -4093,7 +4093,7 @@
         <v>78</v>
       </c>
       <c r="B80" s="2">
-        <v>0.003628809005022049</v>
+        <v>0.00356751075014472</v>
       </c>
       <c r="C80" s="1">
         <v>4</v>

--- a/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
+++ b/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
@@ -15,12 +15,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="47">
   <si>
     <t>AT32F415RBT7_WorkBench</t>
   </si>
   <si>
-    <t>lto-llvm-cde366.o</t>
+    <t>lto-llvm-9f4555.o</t>
   </si>
   <si>
     <t>startup_at32f415.o</t>
@@ -60,6 +60,9 @@
   </si>
   <si>
     <t>d2f.o</t>
+  </si>
+  <si>
+    <t>dcmpgt.o</t>
   </si>
   <si>
     <t>ffixi.o</t>
@@ -242,16 +245,16 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>ram_percent!$A$3:$A$38</c:f>
+              <c:f>ram_percent!$A$3:$A$39</c:f>
               <c:strCache>
-                <c:ptCount val="36"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-cde366.o</c:v>
+                  <c:v>lto-llvm-9f4555.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>startup_at32f415.o</c:v>
                 </c:pt>
-                <c:pt idx="35">
+                <c:pt idx="36">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -259,17 +262,17 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ram_percent!$B$3:$B$38</c:f>
+              <c:f>ram_percent!$B$3:$B$39</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="36"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>71.88358306884766</c:v>
+                  <c:v>71.90672302246094</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>28.11641883850098</c:v>
-                </c:pt>
-                <c:pt idx="35">
+                  <c:v>28.0932788848877</c:v>
+                </c:pt>
+                <c:pt idx="36">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -337,11 +340,11 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>flash_percent!$A$3:$A$38</c:f>
+              <c:f>flash_percent!$A$3:$A$39</c:f>
               <c:strCache>
-                <c:ptCount val="36"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-cde366.o</c:v>
+                  <c:v>lto-llvm-9f4555.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>mf_w.l</c:v>
@@ -383,69 +386,72 @@
                   <c:v>d2f.o</c:v>
                 </c:pt>
                 <c:pt idx="14">
+                  <c:v>dcmpgt.o</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>ffixi.o</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>dfixui.o</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>init.o</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>ffixui.o</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>f2d.o</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
                   <c:v>memseta.o</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="21">
                   <c:v>llsshr.o</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="22">
                   <c:v>llushr.o</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="23">
                   <c:v>llshl.o</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="24">
                   <c:v>handlers.o</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="25">
                   <c:v>fcmplt.o</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="26">
                   <c:v>fcmple.o</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="27">
                   <c:v>fcmpgt.o</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="28">
                   <c:v>fcmpge.o</c:v>
                 </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="29">
                   <c:v>fcmpeq.o</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="30">
                   <c:v>dfltui.o</c:v>
                 </c:pt>
-                <c:pt idx="30">
+                <c:pt idx="31">
                   <c:v>fflti.o</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="32">
                   <c:v>ffltui.o</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="33">
                   <c:v>entry9a.o</c:v>
                 </c:pt>
-                <c:pt idx="33">
+                <c:pt idx="34">
                   <c:v>entry2.o</c:v>
                 </c:pt>
-                <c:pt idx="34">
+                <c:pt idx="35">
                   <c:v>entry5.o</c:v>
                 </c:pt>
-                <c:pt idx="35">
+                <c:pt idx="36">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -453,116 +459,119 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>flash_percent!$B$3:$B$38</c:f>
+              <c:f>flash_percent!$B$3:$B$39</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="36"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>95.55473327636719</c:v>
+                  <c:v>95.46787261962891</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.821375727653503</c:v>
+                  <c:v>1.865953683853149</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.373520702123642</c:v>
+                  <c:v>0.3724532127380371</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.3088017702102661</c:v>
+                  <c:v>0.3079192340373993</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.2144970446825028</c:v>
+                  <c:v>0.2138840258121491</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.2107988148927689</c:v>
+                  <c:v>0.2101963609457016</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.2052514851093292</c:v>
+                  <c:v>0.2046648859977722</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.1719674617052078</c:v>
+                  <c:v>0.1714759767055512</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.1627218872308731</c:v>
+                  <c:v>0.1622568517923355</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.114644967019558</c:v>
+                  <c:v>0.1143173202872276</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.1017011851072311</c:v>
+                  <c:v>0.1014105305075645</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.09245561808347702</c:v>
+                  <c:v>0.09219139069318771</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.05732248350977898</c:v>
+                  <c:v>0.05715866014361382</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.05177514627575874</c:v>
+                  <c:v>0.05162717774510384</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.04622780904173851</c:v>
+                  <c:v>0.04978334903717041</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.04622780904173851</c:v>
+                  <c:v>0.04609569534659386</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.04437869787216187</c:v>
+                  <c:v>0.04609569534659386</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.03698224946856499</c:v>
+                  <c:v>0.04425186663866043</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.03513313457369804</c:v>
+                  <c:v>0.03687655553221703</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.0332840234041214</c:v>
+                  <c:v>0.0350327268242836</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.0332840234041214</c:v>
+                  <c:v>0.03318890184164047</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.02958579920232296</c:v>
+                  <c:v>0.03318890184164047</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.02773668617010117</c:v>
+                  <c:v>0.02950124442577362</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.02773668617010117</c:v>
+                  <c:v>0.02765741758048534</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.02588757313787937</c:v>
+                  <c:v>0.02765741758048534</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.02588757313787937</c:v>
+                  <c:v>0.02581358887255192</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.02588757313787937</c:v>
+                  <c:v>0.02581358887255192</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.02588757313787937</c:v>
+                  <c:v>0.02581358887255192</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.02588757313787937</c:v>
+                  <c:v>0.02581358887255192</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.02403846196830273</c:v>
+                  <c:v>0.02581358887255192</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.0166420117020607</c:v>
+                  <c:v>0.02396976202726364</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.009245562367141247</c:v>
+                  <c:v>0.01659445092082024</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.00739644980058074</c:v>
+                  <c:v>0.009219138883054256</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.00739644980058074</c:v>
+                  <c:v>0.007375311106443405</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.00369822490029037</c:v>
+                  <c:v>0.007375311106443405</c:v>
                 </c:pt>
                 <c:pt idx="35">
+                  <c:v>0.003687655553221703</c:v>
+                </c:pt>
+                <c:pt idx="36">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -667,8 +676,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H38" totalsRowCount="1">
-  <autoFilter ref="A2:H37"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H39" totalsRowCount="1">
+  <autoFilter ref="A2:H38"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="ram_percent" totalsRowFunction="sum"/>
@@ -684,8 +693,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H38" totalsRowCount="1">
-  <autoFilter ref="A2:H37"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H39" totalsRowCount="1">
+  <autoFilter ref="A2:H38"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="flash_percent" totalsRowFunction="sum"/>
@@ -985,7 +994,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -998,28 +1007,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1027,25 +1036,25 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>71.88358306884766</v>
+        <v>71.90672302246094</v>
       </c>
       <c r="C3" s="1">
-        <v>2618</v>
+        <v>2621</v>
       </c>
       <c r="D3" s="1">
-        <v>103352</v>
+        <v>103554</v>
       </c>
       <c r="E3" s="1">
-        <v>26374</v>
+        <v>26568</v>
       </c>
       <c r="F3" s="1">
-        <v>76718</v>
+        <v>76726</v>
       </c>
       <c r="G3" s="1">
         <v>260</v>
       </c>
       <c r="H3" s="1">
-        <v>2358</v>
+        <v>2361</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1053,7 +1062,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>28.11641883850098</v>
+        <v>28.0932788848877</v>
       </c>
       <c r="C4" s="1">
         <v>1024</v>
@@ -1074,35 +1083,35 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
-      <c r="A38" t="s">
-        <v>37</v>
-      </c>
-      <c r="B38">
+    <row r="39" spans="1:8">
+      <c r="A39" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39">
         <f>SUBTOTAL(109,[ram_percent])</f>
         <v>0</v>
       </c>
-      <c r="C38">
+      <c r="C39">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="D38">
+      <c r="D39">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="E38">
+      <c r="E39">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F38">
+      <c r="F39">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G38">
+      <c r="G39">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H38">
+      <c r="H39">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
@@ -1118,7 +1127,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1131,28 +1140,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H2" t="s">
         <v>45</v>
-      </c>
-      <c r="C2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H2" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1160,25 +1169,25 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>95.55473327636719</v>
+        <v>95.46787261962891</v>
       </c>
       <c r="C3" s="1">
-        <v>103352</v>
+        <v>103554</v>
       </c>
       <c r="D3" s="1">
-        <v>2618</v>
+        <v>2621</v>
       </c>
       <c r="E3" s="1">
-        <v>26374</v>
+        <v>26568</v>
       </c>
       <c r="F3" s="1">
-        <v>76718</v>
+        <v>76726</v>
       </c>
       <c r="G3" s="1">
         <v>260</v>
       </c>
       <c r="H3" s="1">
-        <v>2358</v>
+        <v>2361</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1186,16 +1195,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>1.821375727653503</v>
+        <v>1.865953683853149</v>
       </c>
       <c r="C4" s="1">
-        <v>1970</v>
+        <v>2024</v>
       </c>
       <c r="D4" s="1">
         <v>0</v>
       </c>
       <c r="E4" s="1">
-        <v>1970</v>
+        <v>2024</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
@@ -1212,7 +1221,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2">
-        <v>0.373520702123642</v>
+        <v>0.3724532127380371</v>
       </c>
       <c r="C5" s="1">
         <v>404</v>
@@ -1238,7 +1247,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>0.3088017702102661</v>
+        <v>0.3079192340373993</v>
       </c>
       <c r="C6" s="1">
         <v>334</v>
@@ -1264,7 +1273,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>0.2144970446825028</v>
+        <v>0.2138840258121491</v>
       </c>
       <c r="C7" s="1">
         <v>232</v>
@@ -1290,7 +1299,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>0.2107988148927689</v>
+        <v>0.2101963609457016</v>
       </c>
       <c r="C8" s="1">
         <v>228</v>
@@ -1316,7 +1325,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.2052514851093292</v>
+        <v>0.2046648859977722</v>
       </c>
       <c r="C9" s="1">
         <v>222</v>
@@ -1342,7 +1351,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.1719674617052078</v>
+        <v>0.1714759767055512</v>
       </c>
       <c r="C10" s="1">
         <v>186</v>
@@ -1368,7 +1377,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.1627218872308731</v>
+        <v>0.1622568517923355</v>
       </c>
       <c r="C11" s="1">
         <v>176</v>
@@ -1394,7 +1403,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.114644967019558</v>
+        <v>0.1143173202872276</v>
       </c>
       <c r="C12" s="1">
         <v>124</v>
@@ -1420,7 +1429,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.1017011851072311</v>
+        <v>0.1014105305075645</v>
       </c>
       <c r="C13" s="1">
         <v>110</v>
@@ -1446,7 +1455,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.09245561808347702</v>
+        <v>0.09219139069318771</v>
       </c>
       <c r="C14" s="1">
         <v>100</v>
@@ -1472,7 +1481,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.05732248350977898</v>
+        <v>0.05715866014361382</v>
       </c>
       <c r="C15" s="1">
         <v>62</v>
@@ -1498,7 +1507,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.05177514627575874</v>
+        <v>0.05162717774510384</v>
       </c>
       <c r="C16" s="1">
         <v>56</v>
@@ -1524,16 +1533,16 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.04622780904173851</v>
+        <v>0.04978334903717041</v>
       </c>
       <c r="C17" s="1">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
       </c>
       <c r="E17" s="1">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
@@ -1550,7 +1559,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.04622780904173851</v>
+        <v>0.04609569534659386</v>
       </c>
       <c r="C18" s="1">
         <v>50</v>
@@ -1576,16 +1585,16 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.04437869787216187</v>
+        <v>0.04609569534659386</v>
       </c>
       <c r="C19" s="1">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
       </c>
       <c r="E19" s="1">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
@@ -1602,16 +1611,16 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.03698224946856499</v>
+        <v>0.04425186663866043</v>
       </c>
       <c r="C20" s="1">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
       </c>
       <c r="E20" s="1">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
@@ -1628,16 +1637,16 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.03513313457369804</v>
+        <v>0.03687655553221703</v>
       </c>
       <c r="C21" s="1">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
       </c>
       <c r="E21" s="1">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
@@ -1654,16 +1663,16 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.0332840234041214</v>
+        <v>0.0350327268242836</v>
       </c>
       <c r="C22" s="1">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D22" s="1">
         <v>0</v>
       </c>
       <c r="E22" s="1">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
@@ -1680,7 +1689,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.0332840234041214</v>
+        <v>0.03318890184164047</v>
       </c>
       <c r="C23" s="1">
         <v>36</v>
@@ -1706,16 +1715,16 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.02958579920232296</v>
+        <v>0.03318890184164047</v>
       </c>
       <c r="C24" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D24" s="1">
         <v>0</v>
       </c>
       <c r="E24" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
@@ -1732,16 +1741,16 @@
         <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>0.02773668617010117</v>
+        <v>0.02950124442577362</v>
       </c>
       <c r="C25" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D25" s="1">
         <v>0</v>
       </c>
       <c r="E25" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
@@ -1758,7 +1767,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>0.02773668617010117</v>
+        <v>0.02765741758048534</v>
       </c>
       <c r="C26" s="1">
         <v>30</v>
@@ -1784,16 +1793,16 @@
         <v>25</v>
       </c>
       <c r="B27" s="2">
-        <v>0.02588757313787937</v>
+        <v>0.02765741758048534</v>
       </c>
       <c r="C27" s="1">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
       </c>
       <c r="E27" s="1">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F27" s="1">
         <v>0</v>
@@ -1810,7 +1819,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="2">
-        <v>0.02588757313787937</v>
+        <v>0.02581358887255192</v>
       </c>
       <c r="C28" s="1">
         <v>28</v>
@@ -1836,7 +1845,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="2">
-        <v>0.02588757313787937</v>
+        <v>0.02581358887255192</v>
       </c>
       <c r="C29" s="1">
         <v>28</v>
@@ -1862,7 +1871,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="2">
-        <v>0.02588757313787937</v>
+        <v>0.02581358887255192</v>
       </c>
       <c r="C30" s="1">
         <v>28</v>
@@ -1888,7 +1897,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="2">
-        <v>0.02588757313787937</v>
+        <v>0.02581358887255192</v>
       </c>
       <c r="C31" s="1">
         <v>28</v>
@@ -1914,16 +1923,16 @@
         <v>30</v>
       </c>
       <c r="B32" s="2">
-        <v>0.02403846196830273</v>
+        <v>0.02581358887255192</v>
       </c>
       <c r="C32" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D32" s="1">
         <v>0</v>
       </c>
       <c r="E32" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
@@ -1940,16 +1949,16 @@
         <v>31</v>
       </c>
       <c r="B33" s="2">
-        <v>0.0166420117020607</v>
+        <v>0.02396976202726364</v>
       </c>
       <c r="C33" s="1">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D33" s="1">
         <v>0</v>
       </c>
       <c r="E33" s="1">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F33" s="1">
         <v>0</v>
@@ -1966,16 +1975,16 @@
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.009245562367141247</v>
+        <v>0.01659445092082024</v>
       </c>
       <c r="C34" s="1">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D34" s="1">
         <v>0</v>
       </c>
       <c r="E34" s="1">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F34" s="1">
         <v>0</v>
@@ -1992,16 +2001,16 @@
         <v>33</v>
       </c>
       <c r="B35" s="2">
-        <v>0.00739644980058074</v>
+        <v>0.009219138883054256</v>
       </c>
       <c r="C35" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D35" s="1">
         <v>0</v>
       </c>
       <c r="E35" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F35" s="1">
         <v>0</v>
@@ -2018,7 +2027,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="2">
-        <v>0.00739644980058074</v>
+        <v>0.007375311106443405</v>
       </c>
       <c r="C36" s="1">
         <v>8</v>
@@ -2044,56 +2053,82 @@
         <v>35</v>
       </c>
       <c r="B37" s="2">
-        <v>0.00369822490029037</v>
+        <v>0.007375311106443405</v>
       </c>
       <c r="C37" s="1">
+        <v>8</v>
+      </c>
+      <c r="D37" s="1">
+        <v>0</v>
+      </c>
+      <c r="E37" s="1">
+        <v>8</v>
+      </c>
+      <c r="F37" s="1">
+        <v>0</v>
+      </c>
+      <c r="G37" s="1">
+        <v>0</v>
+      </c>
+      <c r="H37" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" s="2">
+        <v>0.003687655553221703</v>
+      </c>
+      <c r="C38" s="1">
         <v>4</v>
       </c>
-      <c r="D37" s="1">
-        <v>0</v>
-      </c>
-      <c r="E37" s="1">
+      <c r="D38" s="1">
+        <v>0</v>
+      </c>
+      <c r="E38" s="1">
         <v>4</v>
       </c>
-      <c r="F37" s="1">
-        <v>0</v>
-      </c>
-      <c r="G37" s="1">
-        <v>0</v>
-      </c>
-      <c r="H37" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" t="s">
-        <v>37</v>
-      </c>
-      <c r="B38">
+      <c r="F38" s="1">
+        <v>0</v>
+      </c>
+      <c r="G38" s="1">
+        <v>0</v>
+      </c>
+      <c r="H38" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39">
         <f>SUBTOTAL(109,[flash_percent])</f>
         <v>0</v>
       </c>
-      <c r="C38">
+      <c r="C39">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="D38">
+      <c r="D39">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="E38">
+      <c r="E39">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F38">
+      <c r="F39">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G38">
+      <c r="G39">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H38">
+      <c r="H39">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>

--- a/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
+++ b/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
@@ -20,7 +20,7 @@
     <t>AT32F415RBT7_WorkBench</t>
   </si>
   <si>
-    <t>lto-llvm-9f4555.o</t>
+    <t>lto-llvm-708540.o</t>
   </si>
   <si>
     <t>startup_at32f415.o</t>
@@ -249,7 +249,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-9f4555.o</c:v>
+                  <c:v>lto-llvm-708540.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>startup_at32f415.o</c:v>
@@ -267,10 +267,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>71.90672302246094</c:v>
+                  <c:v>71.99890899658203</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>28.0932788848877</c:v>
+                  <c:v>28.0010929107666</c:v>
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>0</c:v>
@@ -344,7 +344,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-9f4555.o</c:v>
+                  <c:v>lto-llvm-708540.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>mf_w.l</c:v>
@@ -464,112 +464,112 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>95.46787261962891</c:v>
+                  <c:v>95.46125793457031</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.865953683853149</c:v>
+                  <c:v>1.868675708770752</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.3724532127380371</c:v>
+                  <c:v>0.3729965388774872</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.3079192340373993</c:v>
+                  <c:v>0.3083684146404266</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.2138840258121491</c:v>
+                  <c:v>0.2141960263252258</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.2101963609457016</c:v>
+                  <c:v>0.2105029970407486</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.2046648859977722</c:v>
+                  <c:v>0.2049634456634522</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.1714759767055512</c:v>
+                  <c:v>0.1717261224985123</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.1622568517923355</c:v>
+                  <c:v>0.1624935418367386</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.1143173202872276</c:v>
+                  <c:v>0.1144840866327286</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.1014105305075645</c:v>
+                  <c:v>0.1015584617853165</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.09219139069318771</c:v>
+                  <c:v>0.09232587367296219</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.05715866014361382</c:v>
+                  <c:v>0.05724204331636429</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.05162717774510384</c:v>
+                  <c:v>0.05170248821377754</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.04978334903717041</c:v>
+                  <c:v>0.04985596984624863</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.04609569534659386</c:v>
+                  <c:v>0.04616293683648109</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.04609569534659386</c:v>
+                  <c:v>0.04616293683648109</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.04425186663866043</c:v>
+                  <c:v>0.04431641846895218</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.03687655553221703</c:v>
+                  <c:v>0.03693034872412682</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.0350327268242836</c:v>
+                  <c:v>0.0350838303565979</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.03318890184164047</c:v>
+                  <c:v>0.03323731571435928</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.03318890184164047</c:v>
+                  <c:v>0.03323731571435928</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.02950124442577362</c:v>
+                  <c:v>0.02954427897930145</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.02765741758048534</c:v>
+                  <c:v>0.02769776247441769</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.02765741758048534</c:v>
+                  <c:v>0.02769776247441769</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.02581358887255192</c:v>
+                  <c:v>0.02585124410688877</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.02581358887255192</c:v>
+                  <c:v>0.02585124410688877</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.02581358887255192</c:v>
+                  <c:v>0.02585124410688877</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.02581358887255192</c:v>
+                  <c:v>0.02585124410688877</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.02581358887255192</c:v>
+                  <c:v>0.02585124410688877</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.02396976202726364</c:v>
+                  <c:v>0.02400472760200501</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.01659445092082024</c:v>
+                  <c:v>0.01661865785717964</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.009219138883054256</c:v>
+                  <c:v>0.009232587181031704</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.007375311106443405</c:v>
+                  <c:v>0.007386069744825363</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.007375311106443405</c:v>
+                  <c:v>0.007386069744825363</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.003687655553221703</c:v>
+                  <c:v>0.003693034872412682</c:v>
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>0</c:v>
@@ -1036,16 +1036,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>71.90672302246094</v>
+        <v>71.99890899658203</v>
       </c>
       <c r="C3" s="1">
-        <v>2621</v>
+        <v>2633</v>
       </c>
       <c r="D3" s="1">
-        <v>103554</v>
+        <v>103396</v>
       </c>
       <c r="E3" s="1">
-        <v>26568</v>
+        <v>26410</v>
       </c>
       <c r="F3" s="1">
         <v>76726</v>
@@ -1054,7 +1054,7 @@
         <v>260</v>
       </c>
       <c r="H3" s="1">
-        <v>2361</v>
+        <v>2373</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1062,7 +1062,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>28.0932788848877</v>
+        <v>28.0010929107666</v>
       </c>
       <c r="C4" s="1">
         <v>1024</v>
@@ -1169,16 +1169,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>95.46787261962891</v>
+        <v>95.46125793457031</v>
       </c>
       <c r="C3" s="1">
-        <v>103554</v>
+        <v>103396</v>
       </c>
       <c r="D3" s="1">
-        <v>2621</v>
+        <v>2633</v>
       </c>
       <c r="E3" s="1">
-        <v>26568</v>
+        <v>26410</v>
       </c>
       <c r="F3" s="1">
         <v>76726</v>
@@ -1187,7 +1187,7 @@
         <v>260</v>
       </c>
       <c r="H3" s="1">
-        <v>2361</v>
+        <v>2373</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1195,7 +1195,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>1.865953683853149</v>
+        <v>1.868675708770752</v>
       </c>
       <c r="C4" s="1">
         <v>2024</v>
@@ -1221,7 +1221,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2">
-        <v>0.3724532127380371</v>
+        <v>0.3729965388774872</v>
       </c>
       <c r="C5" s="1">
         <v>404</v>
@@ -1247,7 +1247,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>0.3079192340373993</v>
+        <v>0.3083684146404266</v>
       </c>
       <c r="C6" s="1">
         <v>334</v>
@@ -1273,7 +1273,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>0.2138840258121491</v>
+        <v>0.2141960263252258</v>
       </c>
       <c r="C7" s="1">
         <v>232</v>
@@ -1299,7 +1299,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>0.2101963609457016</v>
+        <v>0.2105029970407486</v>
       </c>
       <c r="C8" s="1">
         <v>228</v>
@@ -1325,7 +1325,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.2046648859977722</v>
+        <v>0.2049634456634522</v>
       </c>
       <c r="C9" s="1">
         <v>222</v>
@@ -1351,7 +1351,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.1714759767055512</v>
+        <v>0.1717261224985123</v>
       </c>
       <c r="C10" s="1">
         <v>186</v>
@@ -1377,7 +1377,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.1622568517923355</v>
+        <v>0.1624935418367386</v>
       </c>
       <c r="C11" s="1">
         <v>176</v>
@@ -1403,7 +1403,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.1143173202872276</v>
+        <v>0.1144840866327286</v>
       </c>
       <c r="C12" s="1">
         <v>124</v>
@@ -1429,7 +1429,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.1014105305075645</v>
+        <v>0.1015584617853165</v>
       </c>
       <c r="C13" s="1">
         <v>110</v>
@@ -1455,7 +1455,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.09219139069318771</v>
+        <v>0.09232587367296219</v>
       </c>
       <c r="C14" s="1">
         <v>100</v>
@@ -1481,7 +1481,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.05715866014361382</v>
+        <v>0.05724204331636429</v>
       </c>
       <c r="C15" s="1">
         <v>62</v>
@@ -1507,7 +1507,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.05162717774510384</v>
+        <v>0.05170248821377754</v>
       </c>
       <c r="C16" s="1">
         <v>56</v>
@@ -1533,7 +1533,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.04978334903717041</v>
+        <v>0.04985596984624863</v>
       </c>
       <c r="C17" s="1">
         <v>54</v>
@@ -1559,7 +1559,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.04609569534659386</v>
+        <v>0.04616293683648109</v>
       </c>
       <c r="C18" s="1">
         <v>50</v>
@@ -1585,7 +1585,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.04609569534659386</v>
+        <v>0.04616293683648109</v>
       </c>
       <c r="C19" s="1">
         <v>50</v>
@@ -1611,7 +1611,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.04425186663866043</v>
+        <v>0.04431641846895218</v>
       </c>
       <c r="C20" s="1">
         <v>48</v>
@@ -1637,7 +1637,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.03687655553221703</v>
+        <v>0.03693034872412682</v>
       </c>
       <c r="C21" s="1">
         <v>40</v>
@@ -1663,7 +1663,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.0350327268242836</v>
+        <v>0.0350838303565979</v>
       </c>
       <c r="C22" s="1">
         <v>38</v>
@@ -1689,7 +1689,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.03318890184164047</v>
+        <v>0.03323731571435928</v>
       </c>
       <c r="C23" s="1">
         <v>36</v>
@@ -1715,7 +1715,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.03318890184164047</v>
+        <v>0.03323731571435928</v>
       </c>
       <c r="C24" s="1">
         <v>36</v>
@@ -1741,7 +1741,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>0.02950124442577362</v>
+        <v>0.02954427897930145</v>
       </c>
       <c r="C25" s="1">
         <v>32</v>
@@ -1767,7 +1767,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>0.02765741758048534</v>
+        <v>0.02769776247441769</v>
       </c>
       <c r="C26" s="1">
         <v>30</v>
@@ -1793,7 +1793,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2">
-        <v>0.02765741758048534</v>
+        <v>0.02769776247441769</v>
       </c>
       <c r="C27" s="1">
         <v>30</v>
@@ -1819,7 +1819,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="2">
-        <v>0.02581358887255192</v>
+        <v>0.02585124410688877</v>
       </c>
       <c r="C28" s="1">
         <v>28</v>
@@ -1845,7 +1845,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="2">
-        <v>0.02581358887255192</v>
+        <v>0.02585124410688877</v>
       </c>
       <c r="C29" s="1">
         <v>28</v>
@@ -1871,7 +1871,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="2">
-        <v>0.02581358887255192</v>
+        <v>0.02585124410688877</v>
       </c>
       <c r="C30" s="1">
         <v>28</v>
@@ -1897,7 +1897,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="2">
-        <v>0.02581358887255192</v>
+        <v>0.02585124410688877</v>
       </c>
       <c r="C31" s="1">
         <v>28</v>
@@ -1923,7 +1923,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="2">
-        <v>0.02581358887255192</v>
+        <v>0.02585124410688877</v>
       </c>
       <c r="C32" s="1">
         <v>28</v>
@@ -1949,7 +1949,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="2">
-        <v>0.02396976202726364</v>
+        <v>0.02400472760200501</v>
       </c>
       <c r="C33" s="1">
         <v>26</v>
@@ -1975,7 +1975,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.01659445092082024</v>
+        <v>0.01661865785717964</v>
       </c>
       <c r="C34" s="1">
         <v>18</v>
@@ -2001,7 +2001,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="2">
-        <v>0.009219138883054256</v>
+        <v>0.009232587181031704</v>
       </c>
       <c r="C35" s="1">
         <v>10</v>
@@ -2027,7 +2027,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="2">
-        <v>0.007375311106443405</v>
+        <v>0.007386069744825363</v>
       </c>
       <c r="C36" s="1">
         <v>8</v>
@@ -2053,7 +2053,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="2">
-        <v>0.007375311106443405</v>
+        <v>0.007386069744825363</v>
       </c>
       <c r="C37" s="1">
         <v>8</v>
@@ -2079,7 +2079,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="2">
-        <v>0.003687655553221703</v>
+        <v>0.003693034872412682</v>
       </c>
       <c r="C38" s="1">
         <v>4</v>

--- a/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
+++ b/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
@@ -20,7 +20,7 @@
     <t>AT32F415RBT7_WorkBench</t>
   </si>
   <si>
-    <t>lto-llvm-708540.o</t>
+    <t>lto-llvm-549529.o</t>
   </si>
   <si>
     <t>startup_at32f415.o</t>
@@ -249,7 +249,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-708540.o</c:v>
+                  <c:v>lto-llvm-549529.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>startup_at32f415.o</c:v>
@@ -267,10 +267,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>71.99890899658203</c:v>
+                  <c:v>72.02950286865234</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>28.0010929107666</c:v>
+                  <c:v>27.97049903869629</c:v>
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>0</c:v>
@@ -344,7 +344,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-708540.o</c:v>
+                  <c:v>lto-llvm-549529.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>mf_w.l</c:v>
@@ -464,112 +464,112 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>95.46125793457031</c:v>
+                  <c:v>95.46620178222656</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.868675708770752</c:v>
+                  <c:v>1.866642117500305</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.3729965388774872</c:v>
+                  <c:v>0.3725906014442444</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.3083684146404266</c:v>
+                  <c:v>0.3080328404903412</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.2141960263252258</c:v>
+                  <c:v>0.2139629274606705</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.2105029970407486</c:v>
+                  <c:v>0.2102739065885544</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.2049634456634522</c:v>
+                  <c:v>0.2047403901815414</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.1717261224985123</c:v>
+                  <c:v>0.1715392470359802</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.1624935418367386</c:v>
+                  <c:v>0.16231669485569</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.1144840866327286</c:v>
+                  <c:v>0.1143594980239868</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.1015584617853165</c:v>
+                  <c:v>0.1014479398727417</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.09232587367296219</c:v>
+                  <c:v>0.09222540259361267</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.05724204331636429</c:v>
+                  <c:v>0.05717974901199341</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.05170248821377754</c:v>
+                  <c:v>0.05164622515439987</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.04985596984624863</c:v>
+                  <c:v>0.04980171471834183</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.04616293683648109</c:v>
+                  <c:v>0.04611270129680634</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.04616293683648109</c:v>
+                  <c:v>0.04611270129680634</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.04431641846895218</c:v>
+                  <c:v>0.04426819086074829</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.03693034872412682</c:v>
+                  <c:v>0.03689016029238701</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.0350838303565979</c:v>
+                  <c:v>0.03504564985632896</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.03323731571435928</c:v>
+                  <c:v>0.03320114314556122</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.03323731571435928</c:v>
+                  <c:v>0.03320114314556122</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.02954427897930145</c:v>
+                  <c:v>0.02951212786138058</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.02769776247441769</c:v>
+                  <c:v>0.02766761928796768</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.02769776247441769</c:v>
+                  <c:v>0.02766761928796768</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.02585124410688877</c:v>
+                  <c:v>0.02582311257719994</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.02585124410688877</c:v>
+                  <c:v>0.02582311257719994</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.02585124410688877</c:v>
+                  <c:v>0.02582311257719994</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.02585124410688877</c:v>
+                  <c:v>0.02582311257719994</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.02585124410688877</c:v>
+                  <c:v>0.02582311257719994</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.02400472760200501</c:v>
+                  <c:v>0.02397860400378704</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.01661865785717964</c:v>
+                  <c:v>0.01660057157278061</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.009232587181031704</c:v>
+                  <c:v>0.009222540073096752</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.007386069744825363</c:v>
+                  <c:v>0.007378031965345144</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.007386069744825363</c:v>
+                  <c:v>0.007378031965345144</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.003693034872412682</c:v>
+                  <c:v>0.003689015982672572</c:v>
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>0</c:v>
@@ -1036,16 +1036,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>71.99890899658203</v>
+        <v>72.02950286865234</v>
       </c>
       <c r="C3" s="1">
-        <v>2633</v>
+        <v>2637</v>
       </c>
       <c r="D3" s="1">
-        <v>103396</v>
+        <v>103514</v>
       </c>
       <c r="E3" s="1">
-        <v>26410</v>
+        <v>26528</v>
       </c>
       <c r="F3" s="1">
         <v>76726</v>
@@ -1054,7 +1054,7 @@
         <v>260</v>
       </c>
       <c r="H3" s="1">
-        <v>2373</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1062,7 +1062,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>28.0010929107666</v>
+        <v>27.97049903869629</v>
       </c>
       <c r="C4" s="1">
         <v>1024</v>
@@ -1169,16 +1169,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>95.46125793457031</v>
+        <v>95.46620178222656</v>
       </c>
       <c r="C3" s="1">
-        <v>103396</v>
+        <v>103514</v>
       </c>
       <c r="D3" s="1">
-        <v>2633</v>
+        <v>2637</v>
       </c>
       <c r="E3" s="1">
-        <v>26410</v>
+        <v>26528</v>
       </c>
       <c r="F3" s="1">
         <v>76726</v>
@@ -1187,7 +1187,7 @@
         <v>260</v>
       </c>
       <c r="H3" s="1">
-        <v>2373</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1195,7 +1195,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>1.868675708770752</v>
+        <v>1.866642117500305</v>
       </c>
       <c r="C4" s="1">
         <v>2024</v>
@@ -1221,7 +1221,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2">
-        <v>0.3729965388774872</v>
+        <v>0.3725906014442444</v>
       </c>
       <c r="C5" s="1">
         <v>404</v>
@@ -1247,7 +1247,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>0.3083684146404266</v>
+        <v>0.3080328404903412</v>
       </c>
       <c r="C6" s="1">
         <v>334</v>
@@ -1273,7 +1273,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>0.2141960263252258</v>
+        <v>0.2139629274606705</v>
       </c>
       <c r="C7" s="1">
         <v>232</v>
@@ -1299,7 +1299,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>0.2105029970407486</v>
+        <v>0.2102739065885544</v>
       </c>
       <c r="C8" s="1">
         <v>228</v>
@@ -1325,7 +1325,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.2049634456634522</v>
+        <v>0.2047403901815414</v>
       </c>
       <c r="C9" s="1">
         <v>222</v>
@@ -1351,7 +1351,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.1717261224985123</v>
+        <v>0.1715392470359802</v>
       </c>
       <c r="C10" s="1">
         <v>186</v>
@@ -1377,7 +1377,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.1624935418367386</v>
+        <v>0.16231669485569</v>
       </c>
       <c r="C11" s="1">
         <v>176</v>
@@ -1403,7 +1403,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.1144840866327286</v>
+        <v>0.1143594980239868</v>
       </c>
       <c r="C12" s="1">
         <v>124</v>
@@ -1429,7 +1429,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.1015584617853165</v>
+        <v>0.1014479398727417</v>
       </c>
       <c r="C13" s="1">
         <v>110</v>
@@ -1455,7 +1455,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.09232587367296219</v>
+        <v>0.09222540259361267</v>
       </c>
       <c r="C14" s="1">
         <v>100</v>
@@ -1481,7 +1481,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.05724204331636429</v>
+        <v>0.05717974901199341</v>
       </c>
       <c r="C15" s="1">
         <v>62</v>
@@ -1507,7 +1507,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.05170248821377754</v>
+        <v>0.05164622515439987</v>
       </c>
       <c r="C16" s="1">
         <v>56</v>
@@ -1533,7 +1533,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.04985596984624863</v>
+        <v>0.04980171471834183</v>
       </c>
       <c r="C17" s="1">
         <v>54</v>
@@ -1559,7 +1559,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.04616293683648109</v>
+        <v>0.04611270129680634</v>
       </c>
       <c r="C18" s="1">
         <v>50</v>
@@ -1585,7 +1585,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.04616293683648109</v>
+        <v>0.04611270129680634</v>
       </c>
       <c r="C19" s="1">
         <v>50</v>
@@ -1611,7 +1611,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.04431641846895218</v>
+        <v>0.04426819086074829</v>
       </c>
       <c r="C20" s="1">
         <v>48</v>
@@ -1637,7 +1637,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.03693034872412682</v>
+        <v>0.03689016029238701</v>
       </c>
       <c r="C21" s="1">
         <v>40</v>
@@ -1663,7 +1663,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.0350838303565979</v>
+        <v>0.03504564985632896</v>
       </c>
       <c r="C22" s="1">
         <v>38</v>
@@ -1689,7 +1689,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.03323731571435928</v>
+        <v>0.03320114314556122</v>
       </c>
       <c r="C23" s="1">
         <v>36</v>
@@ -1715,7 +1715,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.03323731571435928</v>
+        <v>0.03320114314556122</v>
       </c>
       <c r="C24" s="1">
         <v>36</v>
@@ -1741,7 +1741,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>0.02954427897930145</v>
+        <v>0.02951212786138058</v>
       </c>
       <c r="C25" s="1">
         <v>32</v>
@@ -1767,7 +1767,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>0.02769776247441769</v>
+        <v>0.02766761928796768</v>
       </c>
       <c r="C26" s="1">
         <v>30</v>
@@ -1793,7 +1793,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2">
-        <v>0.02769776247441769</v>
+        <v>0.02766761928796768</v>
       </c>
       <c r="C27" s="1">
         <v>30</v>
@@ -1819,7 +1819,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="2">
-        <v>0.02585124410688877</v>
+        <v>0.02582311257719994</v>
       </c>
       <c r="C28" s="1">
         <v>28</v>
@@ -1845,7 +1845,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="2">
-        <v>0.02585124410688877</v>
+        <v>0.02582311257719994</v>
       </c>
       <c r="C29" s="1">
         <v>28</v>
@@ -1871,7 +1871,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="2">
-        <v>0.02585124410688877</v>
+        <v>0.02582311257719994</v>
       </c>
       <c r="C30" s="1">
         <v>28</v>
@@ -1897,7 +1897,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="2">
-        <v>0.02585124410688877</v>
+        <v>0.02582311257719994</v>
       </c>
       <c r="C31" s="1">
         <v>28</v>
@@ -1923,7 +1923,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="2">
-        <v>0.02585124410688877</v>
+        <v>0.02582311257719994</v>
       </c>
       <c r="C32" s="1">
         <v>28</v>
@@ -1949,7 +1949,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="2">
-        <v>0.02400472760200501</v>
+        <v>0.02397860400378704</v>
       </c>
       <c r="C33" s="1">
         <v>26</v>
@@ -1975,7 +1975,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.01661865785717964</v>
+        <v>0.01660057157278061</v>
       </c>
       <c r="C34" s="1">
         <v>18</v>
@@ -2001,7 +2001,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="2">
-        <v>0.009232587181031704</v>
+        <v>0.009222540073096752</v>
       </c>
       <c r="C35" s="1">
         <v>10</v>
@@ -2027,7 +2027,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="2">
-        <v>0.007386069744825363</v>
+        <v>0.007378031965345144</v>
       </c>
       <c r="C36" s="1">
         <v>8</v>
@@ -2053,7 +2053,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="2">
-        <v>0.007386069744825363</v>
+        <v>0.007378031965345144</v>
       </c>
       <c r="C37" s="1">
         <v>8</v>
@@ -2079,7 +2079,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="2">
-        <v>0.003693034872412682</v>
+        <v>0.003689015982672572</v>
       </c>
       <c r="C38" s="1">
         <v>4</v>

--- a/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
+++ b/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
@@ -20,7 +20,7 @@
     <t>AT32F415RBT7_WorkBench</t>
   </si>
   <si>
-    <t>lto-llvm-549529.o</t>
+    <t>lto-llvm-b20008.o</t>
   </si>
   <si>
     <t>startup_at32f415.o</t>
@@ -249,7 +249,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-549529.o</c:v>
+                  <c:v>lto-llvm-b20008.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>startup_at32f415.o</c:v>
@@ -267,10 +267,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>72.02950286865234</c:v>
+                  <c:v>85.95721435546875</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>27.97049903869629</c:v>
+                  <c:v>14.04278659820557</c:v>
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>0</c:v>
@@ -344,7 +344,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-549529.o</c:v>
+                  <c:v>lto-llvm-b20008.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>mf_w.l</c:v>
@@ -464,112 +464,112 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>95.46620178222656</c:v>
+                  <c:v>95.52003479003906</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.866642117500305</c:v>
+                  <c:v>1.84447705745697</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.3725906014442444</c:v>
+                  <c:v>0.3681663572788239</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.3080328404903412</c:v>
+                  <c:v>0.304375171661377</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.2139629274606705</c:v>
+                  <c:v>0.2114222645759583</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.2102739065885544</c:v>
+                  <c:v>0.2077770531177521</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.2047403901815414</c:v>
+                  <c:v>0.2023092359304428</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.1715392470359802</c:v>
+                  <c:v>0.1695023328065872</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.16231669485569</c:v>
+                  <c:v>0.1603893041610718</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.1143594980239868</c:v>
+                  <c:v>0.1130015552043915</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.1014479398727417</c:v>
+                  <c:v>0.1002433151006699</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.09222540259361267</c:v>
+                  <c:v>0.09113028645515442</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.05717974901199341</c:v>
+                  <c:v>0.05650077760219574</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.05164622515439987</c:v>
+                  <c:v>0.05103296041488648</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.04980171471834183</c:v>
+                  <c:v>0.04921035468578339</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.04611270129680634</c:v>
+                  <c:v>0.04556514322757721</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.04611270129680634</c:v>
+                  <c:v>0.04556514322757721</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.04426819086074829</c:v>
+                  <c:v>0.04374253749847412</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.03689016029238701</c:v>
+                  <c:v>0.03645211458206177</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.03504564985632896</c:v>
+                  <c:v>0.03462950885295868</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.03320114314556122</c:v>
+                  <c:v>0.03280690312385559</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.03320114314556122</c:v>
+                  <c:v>0.03280690312385559</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.02951212786138058</c:v>
+                  <c:v>0.02916169166564941</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.02766761928796768</c:v>
+                  <c:v>0.02733908593654633</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.02766761928796768</c:v>
+                  <c:v>0.02733908593654633</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.02582311257719994</c:v>
+                  <c:v>0.02551648020744324</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.02582311257719994</c:v>
+                  <c:v>0.02551648020744324</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.02582311257719994</c:v>
+                  <c:v>0.02551648020744324</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.02582311257719994</c:v>
+                  <c:v>0.02551648020744324</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.02582311257719994</c:v>
+                  <c:v>0.02551648020744324</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.02397860400378704</c:v>
+                  <c:v>0.02369387447834015</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.01660057157278061</c:v>
+                  <c:v>0.0164034515619278</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.009222540073096752</c:v>
+                  <c:v>0.009113028645515442</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.007378031965345144</c:v>
+                  <c:v>0.007290422916412354</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.007378031965345144</c:v>
+                  <c:v>0.007290422916412354</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.003689015982672572</c:v>
+                  <c:v>0.003645211458206177</c:v>
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>0</c:v>
@@ -1036,25 +1036,25 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>72.02950286865234</v>
+        <v>85.95721435546875</v>
       </c>
       <c r="C3" s="1">
-        <v>2637</v>
+        <v>6268</v>
       </c>
       <c r="D3" s="1">
-        <v>103514</v>
+        <v>104817</v>
       </c>
       <c r="E3" s="1">
-        <v>26528</v>
+        <v>27830</v>
       </c>
       <c r="F3" s="1">
         <v>76726</v>
       </c>
       <c r="G3" s="1">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H3" s="1">
-        <v>2377</v>
+        <v>6007</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1062,7 +1062,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>27.97049903869629</v>
+        <v>14.04278659820557</v>
       </c>
       <c r="C4" s="1">
         <v>1024</v>
@@ -1169,25 +1169,25 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>95.46620178222656</v>
+        <v>95.52003479003906</v>
       </c>
       <c r="C3" s="1">
-        <v>103514</v>
+        <v>104817</v>
       </c>
       <c r="D3" s="1">
-        <v>2637</v>
+        <v>6268</v>
       </c>
       <c r="E3" s="1">
-        <v>26528</v>
+        <v>27830</v>
       </c>
       <c r="F3" s="1">
         <v>76726</v>
       </c>
       <c r="G3" s="1">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H3" s="1">
-        <v>2377</v>
+        <v>6007</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1195,7 +1195,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>1.866642117500305</v>
+        <v>1.84447705745697</v>
       </c>
       <c r="C4" s="1">
         <v>2024</v>
@@ -1221,7 +1221,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2">
-        <v>0.3725906014442444</v>
+        <v>0.3681663572788239</v>
       </c>
       <c r="C5" s="1">
         <v>404</v>
@@ -1247,7 +1247,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>0.3080328404903412</v>
+        <v>0.304375171661377</v>
       </c>
       <c r="C6" s="1">
         <v>334</v>
@@ -1273,7 +1273,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>0.2139629274606705</v>
+        <v>0.2114222645759583</v>
       </c>
       <c r="C7" s="1">
         <v>232</v>
@@ -1299,7 +1299,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>0.2102739065885544</v>
+        <v>0.2077770531177521</v>
       </c>
       <c r="C8" s="1">
         <v>228</v>
@@ -1325,7 +1325,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.2047403901815414</v>
+        <v>0.2023092359304428</v>
       </c>
       <c r="C9" s="1">
         <v>222</v>
@@ -1351,7 +1351,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.1715392470359802</v>
+        <v>0.1695023328065872</v>
       </c>
       <c r="C10" s="1">
         <v>186</v>
@@ -1377,7 +1377,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.16231669485569</v>
+        <v>0.1603893041610718</v>
       </c>
       <c r="C11" s="1">
         <v>176</v>
@@ -1403,7 +1403,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.1143594980239868</v>
+        <v>0.1130015552043915</v>
       </c>
       <c r="C12" s="1">
         <v>124</v>
@@ -1429,7 +1429,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.1014479398727417</v>
+        <v>0.1002433151006699</v>
       </c>
       <c r="C13" s="1">
         <v>110</v>
@@ -1455,7 +1455,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.09222540259361267</v>
+        <v>0.09113028645515442</v>
       </c>
       <c r="C14" s="1">
         <v>100</v>
@@ -1481,7 +1481,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.05717974901199341</v>
+        <v>0.05650077760219574</v>
       </c>
       <c r="C15" s="1">
         <v>62</v>
@@ -1507,7 +1507,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.05164622515439987</v>
+        <v>0.05103296041488648</v>
       </c>
       <c r="C16" s="1">
         <v>56</v>
@@ -1533,7 +1533,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.04980171471834183</v>
+        <v>0.04921035468578339</v>
       </c>
       <c r="C17" s="1">
         <v>54</v>
@@ -1559,7 +1559,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.04611270129680634</v>
+        <v>0.04556514322757721</v>
       </c>
       <c r="C18" s="1">
         <v>50</v>
@@ -1585,7 +1585,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.04611270129680634</v>
+        <v>0.04556514322757721</v>
       </c>
       <c r="C19" s="1">
         <v>50</v>
@@ -1611,7 +1611,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.04426819086074829</v>
+        <v>0.04374253749847412</v>
       </c>
       <c r="C20" s="1">
         <v>48</v>
@@ -1637,7 +1637,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.03689016029238701</v>
+        <v>0.03645211458206177</v>
       </c>
       <c r="C21" s="1">
         <v>40</v>
@@ -1663,7 +1663,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.03504564985632896</v>
+        <v>0.03462950885295868</v>
       </c>
       <c r="C22" s="1">
         <v>38</v>
@@ -1689,7 +1689,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.03320114314556122</v>
+        <v>0.03280690312385559</v>
       </c>
       <c r="C23" s="1">
         <v>36</v>
@@ -1715,7 +1715,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.03320114314556122</v>
+        <v>0.03280690312385559</v>
       </c>
       <c r="C24" s="1">
         <v>36</v>
@@ -1741,7 +1741,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>0.02951212786138058</v>
+        <v>0.02916169166564941</v>
       </c>
       <c r="C25" s="1">
         <v>32</v>
@@ -1767,7 +1767,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>0.02766761928796768</v>
+        <v>0.02733908593654633</v>
       </c>
       <c r="C26" s="1">
         <v>30</v>
@@ -1793,7 +1793,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2">
-        <v>0.02766761928796768</v>
+        <v>0.02733908593654633</v>
       </c>
       <c r="C27" s="1">
         <v>30</v>
@@ -1819,7 +1819,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="2">
-        <v>0.02582311257719994</v>
+        <v>0.02551648020744324</v>
       </c>
       <c r="C28" s="1">
         <v>28</v>
@@ -1845,7 +1845,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="2">
-        <v>0.02582311257719994</v>
+        <v>0.02551648020744324</v>
       </c>
       <c r="C29" s="1">
         <v>28</v>
@@ -1871,7 +1871,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="2">
-        <v>0.02582311257719994</v>
+        <v>0.02551648020744324</v>
       </c>
       <c r="C30" s="1">
         <v>28</v>
@@ -1897,7 +1897,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="2">
-        <v>0.02582311257719994</v>
+        <v>0.02551648020744324</v>
       </c>
       <c r="C31" s="1">
         <v>28</v>
@@ -1923,7 +1923,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="2">
-        <v>0.02582311257719994</v>
+        <v>0.02551648020744324</v>
       </c>
       <c r="C32" s="1">
         <v>28</v>
@@ -1949,7 +1949,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="2">
-        <v>0.02397860400378704</v>
+        <v>0.02369387447834015</v>
       </c>
       <c r="C33" s="1">
         <v>26</v>
@@ -1975,7 +1975,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.01660057157278061</v>
+        <v>0.0164034515619278</v>
       </c>
       <c r="C34" s="1">
         <v>18</v>
@@ -2001,7 +2001,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="2">
-        <v>0.009222540073096752</v>
+        <v>0.009113028645515442</v>
       </c>
       <c r="C35" s="1">
         <v>10</v>
@@ -2027,7 +2027,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="2">
-        <v>0.007378031965345144</v>
+        <v>0.007290422916412354</v>
       </c>
       <c r="C36" s="1">
         <v>8</v>
@@ -2053,7 +2053,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="2">
-        <v>0.007378031965345144</v>
+        <v>0.007290422916412354</v>
       </c>
       <c r="C37" s="1">
         <v>8</v>
@@ -2079,7 +2079,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="2">
-        <v>0.003689015982672572</v>
+        <v>0.003645211458206177</v>
       </c>
       <c r="C38" s="1">
         <v>4</v>

--- a/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
+++ b/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
@@ -20,7 +20,7 @@
     <t>AT32F415RBT7_WorkBench</t>
   </si>
   <si>
-    <t>lto-llvm-b20008.o</t>
+    <t>lto-llvm-c53498.o</t>
   </si>
   <si>
     <t>startup_at32f415.o</t>
@@ -249,7 +249,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-b20008.o</c:v>
+                  <c:v>lto-llvm-c53498.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>startup_at32f415.o</c:v>
@@ -344,7 +344,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-b20008.o</c:v>
+                  <c:v>lto-llvm-c53498.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>mf_w.l</c:v>

--- a/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
+++ b/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
@@ -20,7 +20,7 @@
     <t>AT32F415RBT7_WorkBench</t>
   </si>
   <si>
-    <t>lto-llvm-c53498.o</t>
+    <t>lto-llvm-bca84d.o</t>
   </si>
   <si>
     <t>startup_at32f415.o</t>
@@ -249,7 +249,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-c53498.o</c:v>
+                  <c:v>lto-llvm-bca84d.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>startup_at32f415.o</c:v>
@@ -267,10 +267,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>85.95721435546875</c:v>
+                  <c:v>85.96491241455078</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>14.04278659820557</c:v>
+                  <c:v>14.03508758544922</c:v>
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>0</c:v>
@@ -344,7 +344,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-c53498.o</c:v>
+                  <c:v>lto-llvm-bca84d.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>mf_w.l</c:v>
@@ -464,112 +464,112 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>95.52003479003906</c:v>
+                  <c:v>95.55318450927734</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.84447705745697</c:v>
+                  <c:v>1.83082926273346</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.3681663572788239</c:v>
+                  <c:v>0.3654421865940094</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.304375171661377</c:v>
+                  <c:v>0.3021230101585388</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.2114222645759583</c:v>
+                  <c:v>0.2098578959703445</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.2077770531177521</c:v>
+                  <c:v>0.2062396556138992</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.2023092359304428</c:v>
+                  <c:v>0.2008122950792313</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.1695023328065872</c:v>
+                  <c:v>0.1682481318712235</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.1603893041610718</c:v>
+                  <c:v>0.1592025458812714</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.1130015552043915</c:v>
+                  <c:v>0.1121654286980629</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.1002433151006699</c:v>
+                  <c:v>0.0995015874505043</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.09113028645515442</c:v>
+                  <c:v>0.09045598655939102</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.05650077760219574</c:v>
+                  <c:v>0.05608271434903145</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.05103296041488648</c:v>
+                  <c:v>0.05065535381436348</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.04921035468578339</c:v>
+                  <c:v>0.04884623363614082</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.04556514322757721</c:v>
+                  <c:v>0.04522799327969551</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.04556514322757721</c:v>
+                  <c:v>0.04522799327969551</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.04374253749847412</c:v>
+                  <c:v>0.04341887310147286</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.03645211458206177</c:v>
+                  <c:v>0.03618239611387253</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.03462950885295868</c:v>
+                  <c:v>0.03437327593564987</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.03280690312385559</c:v>
+                  <c:v>0.03256415575742722</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.03280690312385559</c:v>
+                  <c:v>0.03256415575742722</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.02916169166564941</c:v>
+                  <c:v>0.02894591726362705</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.02733908593654633</c:v>
+                  <c:v>0.0271367970854044</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.02733908593654633</c:v>
+                  <c:v>0.0271367970854044</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.02551648020744324</c:v>
+                  <c:v>0.02532767690718174</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.02551648020744324</c:v>
+                  <c:v>0.02532767690718174</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.02551648020744324</c:v>
+                  <c:v>0.02532767690718174</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.02551648020744324</c:v>
+                  <c:v>0.02532767690718174</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.02551648020744324</c:v>
+                  <c:v>0.02532767690718174</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.02369387447834015</c:v>
+                  <c:v>0.02351855672895908</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.0164034515619278</c:v>
+                  <c:v>0.01628207787871361</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.009113028645515442</c:v>
+                  <c:v>0.009045599028468132</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.007290422916412354</c:v>
+                  <c:v>0.007236479315906763</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.007290422916412354</c:v>
+                  <c:v>0.007236479315906763</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.003645211458206177</c:v>
+                  <c:v>0.003618239657953382</c:v>
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>0</c:v>
@@ -1036,25 +1036,25 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>85.95721435546875</v>
+        <v>85.96491241455078</v>
       </c>
       <c r="C3" s="1">
-        <v>6268</v>
+        <v>6272</v>
       </c>
       <c r="D3" s="1">
-        <v>104817</v>
+        <v>105635</v>
       </c>
       <c r="E3" s="1">
-        <v>27830</v>
+        <v>29640</v>
       </c>
       <c r="F3" s="1">
-        <v>76726</v>
+        <v>75734</v>
       </c>
       <c r="G3" s="1">
         <v>261</v>
       </c>
       <c r="H3" s="1">
-        <v>6007</v>
+        <v>6011</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1062,7 +1062,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>14.04278659820557</v>
+        <v>14.03508758544922</v>
       </c>
       <c r="C4" s="1">
         <v>1024</v>
@@ -1169,25 +1169,25 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>95.52003479003906</v>
+        <v>95.55318450927734</v>
       </c>
       <c r="C3" s="1">
-        <v>104817</v>
+        <v>105635</v>
       </c>
       <c r="D3" s="1">
-        <v>6268</v>
+        <v>6272</v>
       </c>
       <c r="E3" s="1">
-        <v>27830</v>
+        <v>29640</v>
       </c>
       <c r="F3" s="1">
-        <v>76726</v>
+        <v>75734</v>
       </c>
       <c r="G3" s="1">
         <v>261</v>
       </c>
       <c r="H3" s="1">
-        <v>6007</v>
+        <v>6011</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1195,7 +1195,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>1.84447705745697</v>
+        <v>1.83082926273346</v>
       </c>
       <c r="C4" s="1">
         <v>2024</v>
@@ -1221,7 +1221,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2">
-        <v>0.3681663572788239</v>
+        <v>0.3654421865940094</v>
       </c>
       <c r="C5" s="1">
         <v>404</v>
@@ -1247,7 +1247,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>0.304375171661377</v>
+        <v>0.3021230101585388</v>
       </c>
       <c r="C6" s="1">
         <v>334</v>
@@ -1273,7 +1273,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>0.2114222645759583</v>
+        <v>0.2098578959703445</v>
       </c>
       <c r="C7" s="1">
         <v>232</v>
@@ -1299,7 +1299,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>0.2077770531177521</v>
+        <v>0.2062396556138992</v>
       </c>
       <c r="C8" s="1">
         <v>228</v>
@@ -1325,7 +1325,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.2023092359304428</v>
+        <v>0.2008122950792313</v>
       </c>
       <c r="C9" s="1">
         <v>222</v>
@@ -1351,7 +1351,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.1695023328065872</v>
+        <v>0.1682481318712235</v>
       </c>
       <c r="C10" s="1">
         <v>186</v>
@@ -1377,7 +1377,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.1603893041610718</v>
+        <v>0.1592025458812714</v>
       </c>
       <c r="C11" s="1">
         <v>176</v>
@@ -1403,7 +1403,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.1130015552043915</v>
+        <v>0.1121654286980629</v>
       </c>
       <c r="C12" s="1">
         <v>124</v>
@@ -1429,7 +1429,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.1002433151006699</v>
+        <v>0.0995015874505043</v>
       </c>
       <c r="C13" s="1">
         <v>110</v>
@@ -1455,7 +1455,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.09113028645515442</v>
+        <v>0.09045598655939102</v>
       </c>
       <c r="C14" s="1">
         <v>100</v>
@@ -1481,7 +1481,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.05650077760219574</v>
+        <v>0.05608271434903145</v>
       </c>
       <c r="C15" s="1">
         <v>62</v>
@@ -1507,7 +1507,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.05103296041488648</v>
+        <v>0.05065535381436348</v>
       </c>
       <c r="C16" s="1">
         <v>56</v>
@@ -1533,7 +1533,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.04921035468578339</v>
+        <v>0.04884623363614082</v>
       </c>
       <c r="C17" s="1">
         <v>54</v>
@@ -1559,7 +1559,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.04556514322757721</v>
+        <v>0.04522799327969551</v>
       </c>
       <c r="C18" s="1">
         <v>50</v>
@@ -1585,7 +1585,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.04556514322757721</v>
+        <v>0.04522799327969551</v>
       </c>
       <c r="C19" s="1">
         <v>50</v>
@@ -1611,7 +1611,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.04374253749847412</v>
+        <v>0.04341887310147286</v>
       </c>
       <c r="C20" s="1">
         <v>48</v>
@@ -1637,7 +1637,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.03645211458206177</v>
+        <v>0.03618239611387253</v>
       </c>
       <c r="C21" s="1">
         <v>40</v>
@@ -1663,7 +1663,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.03462950885295868</v>
+        <v>0.03437327593564987</v>
       </c>
       <c r="C22" s="1">
         <v>38</v>
@@ -1689,7 +1689,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.03280690312385559</v>
+        <v>0.03256415575742722</v>
       </c>
       <c r="C23" s="1">
         <v>36</v>
@@ -1715,7 +1715,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.03280690312385559</v>
+        <v>0.03256415575742722</v>
       </c>
       <c r="C24" s="1">
         <v>36</v>
@@ -1741,7 +1741,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>0.02916169166564941</v>
+        <v>0.02894591726362705</v>
       </c>
       <c r="C25" s="1">
         <v>32</v>
@@ -1767,7 +1767,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>0.02733908593654633</v>
+        <v>0.0271367970854044</v>
       </c>
       <c r="C26" s="1">
         <v>30</v>
@@ -1793,7 +1793,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2">
-        <v>0.02733908593654633</v>
+        <v>0.0271367970854044</v>
       </c>
       <c r="C27" s="1">
         <v>30</v>
@@ -1819,7 +1819,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="2">
-        <v>0.02551648020744324</v>
+        <v>0.02532767690718174</v>
       </c>
       <c r="C28" s="1">
         <v>28</v>
@@ -1845,7 +1845,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="2">
-        <v>0.02551648020744324</v>
+        <v>0.02532767690718174</v>
       </c>
       <c r="C29" s="1">
         <v>28</v>
@@ -1871,7 +1871,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="2">
-        <v>0.02551648020744324</v>
+        <v>0.02532767690718174</v>
       </c>
       <c r="C30" s="1">
         <v>28</v>
@@ -1897,7 +1897,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="2">
-        <v>0.02551648020744324</v>
+        <v>0.02532767690718174</v>
       </c>
       <c r="C31" s="1">
         <v>28</v>
@@ -1923,7 +1923,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="2">
-        <v>0.02551648020744324</v>
+        <v>0.02532767690718174</v>
       </c>
       <c r="C32" s="1">
         <v>28</v>
@@ -1949,7 +1949,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="2">
-        <v>0.02369387447834015</v>
+        <v>0.02351855672895908</v>
       </c>
       <c r="C33" s="1">
         <v>26</v>
@@ -1975,7 +1975,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.0164034515619278</v>
+        <v>0.01628207787871361</v>
       </c>
       <c r="C34" s="1">
         <v>18</v>
@@ -2001,7 +2001,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="2">
-        <v>0.009113028645515442</v>
+        <v>0.009045599028468132</v>
       </c>
       <c r="C35" s="1">
         <v>10</v>
@@ -2027,7 +2027,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="2">
-        <v>0.007290422916412354</v>
+        <v>0.007236479315906763</v>
       </c>
       <c r="C36" s="1">
         <v>8</v>
@@ -2053,7 +2053,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="2">
-        <v>0.007290422916412354</v>
+        <v>0.007236479315906763</v>
       </c>
       <c r="C37" s="1">
         <v>8</v>
@@ -2079,7 +2079,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="2">
-        <v>0.003645211458206177</v>
+        <v>0.003618239657953382</v>
       </c>
       <c r="C38" s="1">
         <v>4</v>

--- a/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
+++ b/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
@@ -20,7 +20,7 @@
     <t>AT32F415RBT7_WorkBench</t>
   </si>
   <si>
-    <t>lto-llvm-bca84d.o</t>
+    <t>lto-llvm-04919d.o</t>
   </si>
   <si>
     <t>startup_at32f415.o</t>
@@ -249,7 +249,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-bca84d.o</c:v>
+                  <c:v>lto-llvm-04919d.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>startup_at32f415.o</c:v>
@@ -344,7 +344,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-bca84d.o</c:v>
+                  <c:v>lto-llvm-04919d.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>mf_w.l</c:v>
@@ -464,112 +464,112 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>95.55318450927734</c:v>
+                  <c:v>95.56681823730469</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.83082926273346</c:v>
+                  <c:v>1.825215697288513</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.3654421865940094</c:v>
+                  <c:v>0.3643217086791992</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.3021230101585388</c:v>
+                  <c:v>0.3011966645717621</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.2098578959703445</c:v>
+                  <c:v>0.209214448928833</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.2062396556138992</c:v>
+                  <c:v>0.2056073099374771</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.2008122950792313</c:v>
+                  <c:v>0.2001965939998627</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.1682481318712235</c:v>
+                  <c:v>0.1677322834730148</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.1592025458812714</c:v>
+                  <c:v>0.1587144136428833</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.1121654286980629</c:v>
+                  <c:v>0.1118215173482895</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.0995015874505043</c:v>
+                  <c:v>0.09919650852680206</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.09045598655939102</c:v>
+                  <c:v>0.09017864614725113</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.05608271434903145</c:v>
+                  <c:v>0.05591075867414475</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.05065535381436348</c:v>
+                  <c:v>0.05050003901124001</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.04884623363614082</c:v>
+                  <c:v>0.04869646951556206</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.04522799327969551</c:v>
+                  <c:v>0.04508932307362557</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.04522799327969551</c:v>
+                  <c:v>0.04508932307362557</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.04341887310147286</c:v>
+                  <c:v>0.04328574985265732</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.03618239611387253</c:v>
+                  <c:v>0.03607145696878433</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.03437327593564987</c:v>
+                  <c:v>0.03426788374781609</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.03256415575742722</c:v>
+                  <c:v>0.03246431052684784</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.03256415575742722</c:v>
+                  <c:v>0.03246431052684784</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.02894591726362705</c:v>
+                  <c:v>0.0288571659475565</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.0271367970854044</c:v>
+                  <c:v>0.02705359272658825</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.0271367970854044</c:v>
+                  <c:v>0.02705359272658825</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.02532767690718174</c:v>
+                  <c:v>0.02525001950562</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.02532767690718174</c:v>
+                  <c:v>0.02525001950562</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.02532767690718174</c:v>
+                  <c:v>0.02525001950562</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.02532767690718174</c:v>
+                  <c:v>0.02525001950562</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.02532767690718174</c:v>
+                  <c:v>0.02525001950562</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.02351855672895908</c:v>
+                  <c:v>0.02344644814729691</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.01628207787871361</c:v>
+                  <c:v>0.01623215526342392</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.009045599028468132</c:v>
+                  <c:v>0.009017864242196083</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.007236479315906763</c:v>
+                  <c:v>0.007214291486889124</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.007236479315906763</c:v>
+                  <c:v>0.007214291486889124</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.003618239657953382</c:v>
+                  <c:v>0.003607145743444562</c:v>
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>0</c:v>
@@ -1042,10 +1042,10 @@
         <v>6272</v>
       </c>
       <c r="D3" s="1">
-        <v>105635</v>
+        <v>105975</v>
       </c>
       <c r="E3" s="1">
-        <v>29640</v>
+        <v>29980</v>
       </c>
       <c r="F3" s="1">
         <v>75734</v>
@@ -1169,16 +1169,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>95.55318450927734</v>
+        <v>95.56681823730469</v>
       </c>
       <c r="C3" s="1">
-        <v>105635</v>
+        <v>105975</v>
       </c>
       <c r="D3" s="1">
         <v>6272</v>
       </c>
       <c r="E3" s="1">
-        <v>29640</v>
+        <v>29980</v>
       </c>
       <c r="F3" s="1">
         <v>75734</v>
@@ -1195,7 +1195,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>1.83082926273346</v>
+        <v>1.825215697288513</v>
       </c>
       <c r="C4" s="1">
         <v>2024</v>
@@ -1221,7 +1221,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2">
-        <v>0.3654421865940094</v>
+        <v>0.3643217086791992</v>
       </c>
       <c r="C5" s="1">
         <v>404</v>
@@ -1247,7 +1247,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>0.3021230101585388</v>
+        <v>0.3011966645717621</v>
       </c>
       <c r="C6" s="1">
         <v>334</v>
@@ -1273,7 +1273,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>0.2098578959703445</v>
+        <v>0.209214448928833</v>
       </c>
       <c r="C7" s="1">
         <v>232</v>
@@ -1299,7 +1299,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>0.2062396556138992</v>
+        <v>0.2056073099374771</v>
       </c>
       <c r="C8" s="1">
         <v>228</v>
@@ -1325,7 +1325,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.2008122950792313</v>
+        <v>0.2001965939998627</v>
       </c>
       <c r="C9" s="1">
         <v>222</v>
@@ -1351,7 +1351,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.1682481318712235</v>
+        <v>0.1677322834730148</v>
       </c>
       <c r="C10" s="1">
         <v>186</v>
@@ -1377,7 +1377,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.1592025458812714</v>
+        <v>0.1587144136428833</v>
       </c>
       <c r="C11" s="1">
         <v>176</v>
@@ -1403,7 +1403,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.1121654286980629</v>
+        <v>0.1118215173482895</v>
       </c>
       <c r="C12" s="1">
         <v>124</v>
@@ -1429,7 +1429,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.0995015874505043</v>
+        <v>0.09919650852680206</v>
       </c>
       <c r="C13" s="1">
         <v>110</v>
@@ -1455,7 +1455,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.09045598655939102</v>
+        <v>0.09017864614725113</v>
       </c>
       <c r="C14" s="1">
         <v>100</v>
@@ -1481,7 +1481,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.05608271434903145</v>
+        <v>0.05591075867414475</v>
       </c>
       <c r="C15" s="1">
         <v>62</v>
@@ -1507,7 +1507,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.05065535381436348</v>
+        <v>0.05050003901124001</v>
       </c>
       <c r="C16" s="1">
         <v>56</v>
@@ -1533,7 +1533,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.04884623363614082</v>
+        <v>0.04869646951556206</v>
       </c>
       <c r="C17" s="1">
         <v>54</v>
@@ -1559,7 +1559,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.04522799327969551</v>
+        <v>0.04508932307362557</v>
       </c>
       <c r="C18" s="1">
         <v>50</v>
@@ -1585,7 +1585,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.04522799327969551</v>
+        <v>0.04508932307362557</v>
       </c>
       <c r="C19" s="1">
         <v>50</v>
@@ -1611,7 +1611,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.04341887310147286</v>
+        <v>0.04328574985265732</v>
       </c>
       <c r="C20" s="1">
         <v>48</v>
@@ -1637,7 +1637,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.03618239611387253</v>
+        <v>0.03607145696878433</v>
       </c>
       <c r="C21" s="1">
         <v>40</v>
@@ -1663,7 +1663,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.03437327593564987</v>
+        <v>0.03426788374781609</v>
       </c>
       <c r="C22" s="1">
         <v>38</v>
@@ -1689,7 +1689,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.03256415575742722</v>
+        <v>0.03246431052684784</v>
       </c>
       <c r="C23" s="1">
         <v>36</v>
@@ -1715,7 +1715,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.03256415575742722</v>
+        <v>0.03246431052684784</v>
       </c>
       <c r="C24" s="1">
         <v>36</v>
@@ -1741,7 +1741,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>0.02894591726362705</v>
+        <v>0.0288571659475565</v>
       </c>
       <c r="C25" s="1">
         <v>32</v>
@@ -1767,7 +1767,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>0.0271367970854044</v>
+        <v>0.02705359272658825</v>
       </c>
       <c r="C26" s="1">
         <v>30</v>
@@ -1793,7 +1793,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2">
-        <v>0.0271367970854044</v>
+        <v>0.02705359272658825</v>
       </c>
       <c r="C27" s="1">
         <v>30</v>
@@ -1819,7 +1819,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="2">
-        <v>0.02532767690718174</v>
+        <v>0.02525001950562</v>
       </c>
       <c r="C28" s="1">
         <v>28</v>
@@ -1845,7 +1845,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="2">
-        <v>0.02532767690718174</v>
+        <v>0.02525001950562</v>
       </c>
       <c r="C29" s="1">
         <v>28</v>
@@ -1871,7 +1871,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="2">
-        <v>0.02532767690718174</v>
+        <v>0.02525001950562</v>
       </c>
       <c r="C30" s="1">
         <v>28</v>
@@ -1897,7 +1897,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="2">
-        <v>0.02532767690718174</v>
+        <v>0.02525001950562</v>
       </c>
       <c r="C31" s="1">
         <v>28</v>
@@ -1923,7 +1923,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="2">
-        <v>0.02532767690718174</v>
+        <v>0.02525001950562</v>
       </c>
       <c r="C32" s="1">
         <v>28</v>
@@ -1949,7 +1949,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="2">
-        <v>0.02351855672895908</v>
+        <v>0.02344644814729691</v>
       </c>
       <c r="C33" s="1">
         <v>26</v>
@@ -1975,7 +1975,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.01628207787871361</v>
+        <v>0.01623215526342392</v>
       </c>
       <c r="C34" s="1">
         <v>18</v>
@@ -2001,7 +2001,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="2">
-        <v>0.009045599028468132</v>
+        <v>0.009017864242196083</v>
       </c>
       <c r="C35" s="1">
         <v>10</v>
@@ -2027,7 +2027,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="2">
-        <v>0.007236479315906763</v>
+        <v>0.007214291486889124</v>
       </c>
       <c r="C36" s="1">
         <v>8</v>
@@ -2053,7 +2053,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="2">
-        <v>0.007236479315906763</v>
+        <v>0.007214291486889124</v>
       </c>
       <c r="C37" s="1">
         <v>8</v>
@@ -2079,7 +2079,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="2">
-        <v>0.003618239657953382</v>
+        <v>0.003607145743444562</v>
       </c>
       <c r="C38" s="1">
         <v>4</v>

--- a/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
+++ b/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
@@ -20,7 +20,7 @@
     <t>AT32F415RBT7_WorkBench</t>
   </si>
   <si>
-    <t>lto-llvm-04919d.o</t>
+    <t>lto-llvm-36bf41.o</t>
   </si>
   <si>
     <t>startup_at32f415.o</t>
@@ -249,7 +249,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-04919d.o</c:v>
+                  <c:v>lto-llvm-36bf41.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>startup_at32f415.o</c:v>
@@ -267,10 +267,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>85.96491241455078</c:v>
+                  <c:v>85.85635375976563</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>14.03508758544922</c:v>
+                  <c:v>14.14364624023438</c:v>
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>0</c:v>
@@ -344,7 +344,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-04919d.o</c:v>
+                  <c:v>lto-llvm-36bf41.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>mf_w.l</c:v>
@@ -464,112 +464,112 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>95.56681823730469</c:v>
+                  <c:v>95.55864715576172</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.825215697288513</c:v>
+                  <c:v>1.828579664230347</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.3643217086791992</c:v>
+                  <c:v>0.3649931848049164</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.3011966645717621</c:v>
+                  <c:v>0.3017517924308777</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.209214448928833</c:v>
+                  <c:v>0.2096000462770462</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.2056073099374771</c:v>
+                  <c:v>0.2059862464666367</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.2001965939998627</c:v>
+                  <c:v>0.2005655616521835</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.1677322834730148</c:v>
+                  <c:v>0.1680414080619812</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.1587144136428833</c:v>
+                  <c:v>0.1590069234371185</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.1118215173482895</c:v>
+                  <c:v>0.112027607858181</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.09919650852680206</c:v>
+                  <c:v>0.09937933087348938</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.09017864614725113</c:v>
+                  <c:v>0.09034484624862671</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.05591075867414475</c:v>
+                  <c:v>0.0560138039290905</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.05050003901124001</c:v>
+                  <c:v>0.05059311538934708</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.04869646951556206</c:v>
+                  <c:v>0.0487862154841423</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.04508932307362557</c:v>
+                  <c:v>0.04517242312431335</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.04508932307362557</c:v>
+                  <c:v>0.04517242312431335</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.04328574985265732</c:v>
+                  <c:v>0.04336552694439888</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.03607145696878433</c:v>
+                  <c:v>0.03613793849945068</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.03426788374781609</c:v>
+                  <c:v>0.03433104231953621</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.03246431052684784</c:v>
+                  <c:v>0.03252414613962174</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.03246431052684784</c:v>
+                  <c:v>0.03252414613962174</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.0288571659475565</c:v>
+                  <c:v>0.02891035005450249</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.02705359272658825</c:v>
+                  <c:v>0.02710345387458801</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.02705359272658825</c:v>
+                  <c:v>0.02710345387458801</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.02525001950562</c:v>
+                  <c:v>0.02529655769467354</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.02525001950562</c:v>
+                  <c:v>0.02529655769467354</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.02525001950562</c:v>
+                  <c:v>0.02529655769467354</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.02525001950562</c:v>
+                  <c:v>0.02529655769467354</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.02525001950562</c:v>
+                  <c:v>0.02529655769467354</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.02344644814729691</c:v>
+                  <c:v>0.02348965965211391</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.01623215526342392</c:v>
+                  <c:v>0.01626207306981087</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.009017864242196083</c:v>
+                  <c:v>0.009034484624862671</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.007214291486889124</c:v>
+                  <c:v>0.007227587513625622</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.007214291486889124</c:v>
+                  <c:v>0.007227587513625622</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.003607145743444562</c:v>
+                  <c:v>0.003613793756812811</c:v>
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>0</c:v>
@@ -1036,16 +1036,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>85.96491241455078</v>
+        <v>85.85635375976563</v>
       </c>
       <c r="C3" s="1">
-        <v>6272</v>
+        <v>6216</v>
       </c>
       <c r="D3" s="1">
-        <v>105975</v>
+        <v>105771</v>
       </c>
       <c r="E3" s="1">
-        <v>29980</v>
+        <v>29776</v>
       </c>
       <c r="F3" s="1">
         <v>75734</v>
@@ -1054,7 +1054,7 @@
         <v>261</v>
       </c>
       <c r="H3" s="1">
-        <v>6011</v>
+        <v>5955</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1062,7 +1062,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>14.03508758544922</v>
+        <v>14.14364624023438</v>
       </c>
       <c r="C4" s="1">
         <v>1024</v>
@@ -1169,16 +1169,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>95.56681823730469</v>
+        <v>95.55864715576172</v>
       </c>
       <c r="C3" s="1">
-        <v>105975</v>
+        <v>105771</v>
       </c>
       <c r="D3" s="1">
-        <v>6272</v>
+        <v>6216</v>
       </c>
       <c r="E3" s="1">
-        <v>29980</v>
+        <v>29776</v>
       </c>
       <c r="F3" s="1">
         <v>75734</v>
@@ -1187,7 +1187,7 @@
         <v>261</v>
       </c>
       <c r="H3" s="1">
-        <v>6011</v>
+        <v>5955</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1195,7 +1195,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>1.825215697288513</v>
+        <v>1.828579664230347</v>
       </c>
       <c r="C4" s="1">
         <v>2024</v>
@@ -1221,7 +1221,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2">
-        <v>0.3643217086791992</v>
+        <v>0.3649931848049164</v>
       </c>
       <c r="C5" s="1">
         <v>404</v>
@@ -1247,7 +1247,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>0.3011966645717621</v>
+        <v>0.3017517924308777</v>
       </c>
       <c r="C6" s="1">
         <v>334</v>
@@ -1273,7 +1273,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>0.209214448928833</v>
+        <v>0.2096000462770462</v>
       </c>
       <c r="C7" s="1">
         <v>232</v>
@@ -1299,7 +1299,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>0.2056073099374771</v>
+        <v>0.2059862464666367</v>
       </c>
       <c r="C8" s="1">
         <v>228</v>
@@ -1325,7 +1325,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.2001965939998627</v>
+        <v>0.2005655616521835</v>
       </c>
       <c r="C9" s="1">
         <v>222</v>
@@ -1351,7 +1351,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.1677322834730148</v>
+        <v>0.1680414080619812</v>
       </c>
       <c r="C10" s="1">
         <v>186</v>
@@ -1377,7 +1377,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.1587144136428833</v>
+        <v>0.1590069234371185</v>
       </c>
       <c r="C11" s="1">
         <v>176</v>
@@ -1403,7 +1403,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.1118215173482895</v>
+        <v>0.112027607858181</v>
       </c>
       <c r="C12" s="1">
         <v>124</v>
@@ -1429,7 +1429,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.09919650852680206</v>
+        <v>0.09937933087348938</v>
       </c>
       <c r="C13" s="1">
         <v>110</v>
@@ -1455,7 +1455,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.09017864614725113</v>
+        <v>0.09034484624862671</v>
       </c>
       <c r="C14" s="1">
         <v>100</v>
@@ -1481,7 +1481,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.05591075867414475</v>
+        <v>0.0560138039290905</v>
       </c>
       <c r="C15" s="1">
         <v>62</v>
@@ -1507,7 +1507,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.05050003901124001</v>
+        <v>0.05059311538934708</v>
       </c>
       <c r="C16" s="1">
         <v>56</v>
@@ -1533,7 +1533,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.04869646951556206</v>
+        <v>0.0487862154841423</v>
       </c>
       <c r="C17" s="1">
         <v>54</v>
@@ -1559,7 +1559,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.04508932307362557</v>
+        <v>0.04517242312431335</v>
       </c>
       <c r="C18" s="1">
         <v>50</v>
@@ -1585,7 +1585,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.04508932307362557</v>
+        <v>0.04517242312431335</v>
       </c>
       <c r="C19" s="1">
         <v>50</v>
@@ -1611,7 +1611,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.04328574985265732</v>
+        <v>0.04336552694439888</v>
       </c>
       <c r="C20" s="1">
         <v>48</v>
@@ -1637,7 +1637,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.03607145696878433</v>
+        <v>0.03613793849945068</v>
       </c>
       <c r="C21" s="1">
         <v>40</v>
@@ -1663,7 +1663,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.03426788374781609</v>
+        <v>0.03433104231953621</v>
       </c>
       <c r="C22" s="1">
         <v>38</v>
@@ -1689,7 +1689,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.03246431052684784</v>
+        <v>0.03252414613962174</v>
       </c>
       <c r="C23" s="1">
         <v>36</v>
@@ -1715,7 +1715,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.03246431052684784</v>
+        <v>0.03252414613962174</v>
       </c>
       <c r="C24" s="1">
         <v>36</v>
@@ -1741,7 +1741,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>0.0288571659475565</v>
+        <v>0.02891035005450249</v>
       </c>
       <c r="C25" s="1">
         <v>32</v>
@@ -1767,7 +1767,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>0.02705359272658825</v>
+        <v>0.02710345387458801</v>
       </c>
       <c r="C26" s="1">
         <v>30</v>
@@ -1793,7 +1793,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2">
-        <v>0.02705359272658825</v>
+        <v>0.02710345387458801</v>
       </c>
       <c r="C27" s="1">
         <v>30</v>
@@ -1819,7 +1819,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="2">
-        <v>0.02525001950562</v>
+        <v>0.02529655769467354</v>
       </c>
       <c r="C28" s="1">
         <v>28</v>
@@ -1845,7 +1845,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="2">
-        <v>0.02525001950562</v>
+        <v>0.02529655769467354</v>
       </c>
       <c r="C29" s="1">
         <v>28</v>
@@ -1871,7 +1871,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="2">
-        <v>0.02525001950562</v>
+        <v>0.02529655769467354</v>
       </c>
       <c r="C30" s="1">
         <v>28</v>
@@ -1897,7 +1897,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="2">
-        <v>0.02525001950562</v>
+        <v>0.02529655769467354</v>
       </c>
       <c r="C31" s="1">
         <v>28</v>
@@ -1923,7 +1923,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="2">
-        <v>0.02525001950562</v>
+        <v>0.02529655769467354</v>
       </c>
       <c r="C32" s="1">
         <v>28</v>
@@ -1949,7 +1949,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="2">
-        <v>0.02344644814729691</v>
+        <v>0.02348965965211391</v>
       </c>
       <c r="C33" s="1">
         <v>26</v>
@@ -1975,7 +1975,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.01623215526342392</v>
+        <v>0.01626207306981087</v>
       </c>
       <c r="C34" s="1">
         <v>18</v>
@@ -2001,7 +2001,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="2">
-        <v>0.009017864242196083</v>
+        <v>0.009034484624862671</v>
       </c>
       <c r="C35" s="1">
         <v>10</v>
@@ -2027,7 +2027,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="2">
-        <v>0.007214291486889124</v>
+        <v>0.007227587513625622</v>
       </c>
       <c r="C36" s="1">
         <v>8</v>
@@ -2053,7 +2053,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="2">
-        <v>0.007214291486889124</v>
+        <v>0.007227587513625622</v>
       </c>
       <c r="C37" s="1">
         <v>8</v>
@@ -2079,7 +2079,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="2">
-        <v>0.003607145743444562</v>
+        <v>0.003613793756812811</v>
       </c>
       <c r="C38" s="1">
         <v>4</v>

--- a/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
+++ b/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
@@ -20,7 +20,7 @@
     <t>AT32F415RBT7_WorkBench</t>
   </si>
   <si>
-    <t>lto-llvm-36bf41.o</t>
+    <t>lto-llvm-2f24cf.o</t>
   </si>
   <si>
     <t>startup_at32f415.o</t>
@@ -249,7 +249,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-36bf41.o</c:v>
+                  <c:v>lto-llvm-2f24cf.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>startup_at32f415.o</c:v>
@@ -267,10 +267,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>85.85635375976563</c:v>
+                  <c:v>85.96491241455078</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>14.14364624023438</c:v>
+                  <c:v>14.03508758544922</c:v>
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>0</c:v>
@@ -344,7 +344,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-36bf41.o</c:v>
+                  <c:v>lto-llvm-2f24cf.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>mf_w.l</c:v>
@@ -464,112 +464,112 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>95.55864715576172</c:v>
+                  <c:v>95.61090850830078</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.828579664230347</c:v>
+                  <c:v>1.807062149047852</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.3649931848049164</c:v>
+                  <c:v>0.3606981933116913</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.3017517924308777</c:v>
+                  <c:v>0.2982009649276733</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.2096000462770462</c:v>
+                  <c:v>0.2071336060762405</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.2059862464666367</c:v>
+                  <c:v>0.2035623341798782</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.2005655616521835</c:v>
+                  <c:v>0.198205441236496</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.1680414080619812</c:v>
+                  <c:v>0.1660640090703964</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.1590069234371185</c:v>
+                  <c:v>0.1571358442306519</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.112027607858181</c:v>
+                  <c:v>0.1107093468308449</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.09937933087348938</c:v>
+                  <c:v>0.09820990264415741</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.09034484624862671</c:v>
+                  <c:v>0.08928173035383225</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.0560138039290905</c:v>
+                  <c:v>0.05535467341542244</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.05059311538934708</c:v>
+                  <c:v>0.04999776929616928</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.0487862154841423</c:v>
+                  <c:v>0.04821213334798813</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.04517242312431335</c:v>
+                  <c:v>0.04464086517691612</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.04517242312431335</c:v>
+                  <c:v>0.04464086517691612</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.04336552694439888</c:v>
+                  <c:v>0.04285522922873497</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.03613793849945068</c:v>
+                  <c:v>0.03571269288659096</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.03433104231953621</c:v>
+                  <c:v>0.03392705693840981</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.03252414613962174</c:v>
+                  <c:v>0.03214142099022865</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.03252414613962174</c:v>
+                  <c:v>0.03214142099022865</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.02891035005450249</c:v>
+                  <c:v>0.02857015281915665</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.02710345387458801</c:v>
+                  <c:v>0.02678451873362064</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.02710345387458801</c:v>
+                  <c:v>0.02678451873362064</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.02529655769467354</c:v>
+                  <c:v>0.02499888464808464</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.02529655769467354</c:v>
+                  <c:v>0.02499888464808464</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.02529655769467354</c:v>
+                  <c:v>0.02499888464808464</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.02529655769467354</c:v>
+                  <c:v>0.02499888464808464</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.02529655769467354</c:v>
+                  <c:v>0.02499888464808464</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.02348965965211391</c:v>
+                  <c:v>0.02321324869990349</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.01626207306981087</c:v>
+                  <c:v>0.01607071049511433</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.009034484624862671</c:v>
+                  <c:v>0.008928173221647739</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.007227587513625622</c:v>
+                  <c:v>0.007142538204789162</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.007227587513625622</c:v>
+                  <c:v>0.007142538204789162</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.003613793756812811</c:v>
+                  <c:v>0.003571269102394581</c:v>
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>0</c:v>
@@ -1036,16 +1036,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>85.85635375976563</v>
+        <v>85.96491241455078</v>
       </c>
       <c r="C3" s="1">
-        <v>6216</v>
+        <v>6272</v>
       </c>
       <c r="D3" s="1">
-        <v>105771</v>
+        <v>107089</v>
       </c>
       <c r="E3" s="1">
-        <v>29776</v>
+        <v>31094</v>
       </c>
       <c r="F3" s="1">
         <v>75734</v>
@@ -1054,7 +1054,7 @@
         <v>261</v>
       </c>
       <c r="H3" s="1">
-        <v>5955</v>
+        <v>6011</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1062,7 +1062,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>14.14364624023438</v>
+        <v>14.03508758544922</v>
       </c>
       <c r="C4" s="1">
         <v>1024</v>
@@ -1169,16 +1169,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>95.55864715576172</v>
+        <v>95.61090850830078</v>
       </c>
       <c r="C3" s="1">
-        <v>105771</v>
+        <v>107089</v>
       </c>
       <c r="D3" s="1">
-        <v>6216</v>
+        <v>6272</v>
       </c>
       <c r="E3" s="1">
-        <v>29776</v>
+        <v>31094</v>
       </c>
       <c r="F3" s="1">
         <v>75734</v>
@@ -1187,7 +1187,7 @@
         <v>261</v>
       </c>
       <c r="H3" s="1">
-        <v>5955</v>
+        <v>6011</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1195,7 +1195,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>1.828579664230347</v>
+        <v>1.807062149047852</v>
       </c>
       <c r="C4" s="1">
         <v>2024</v>
@@ -1221,7 +1221,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2">
-        <v>0.3649931848049164</v>
+        <v>0.3606981933116913</v>
       </c>
       <c r="C5" s="1">
         <v>404</v>
@@ -1247,7 +1247,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>0.3017517924308777</v>
+        <v>0.2982009649276733</v>
       </c>
       <c r="C6" s="1">
         <v>334</v>
@@ -1273,7 +1273,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>0.2096000462770462</v>
+        <v>0.2071336060762405</v>
       </c>
       <c r="C7" s="1">
         <v>232</v>
@@ -1299,7 +1299,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>0.2059862464666367</v>
+        <v>0.2035623341798782</v>
       </c>
       <c r="C8" s="1">
         <v>228</v>
@@ -1325,7 +1325,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.2005655616521835</v>
+        <v>0.198205441236496</v>
       </c>
       <c r="C9" s="1">
         <v>222</v>
@@ -1351,7 +1351,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.1680414080619812</v>
+        <v>0.1660640090703964</v>
       </c>
       <c r="C10" s="1">
         <v>186</v>
@@ -1377,7 +1377,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.1590069234371185</v>
+        <v>0.1571358442306519</v>
       </c>
       <c r="C11" s="1">
         <v>176</v>
@@ -1403,7 +1403,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.112027607858181</v>
+        <v>0.1107093468308449</v>
       </c>
       <c r="C12" s="1">
         <v>124</v>
@@ -1429,7 +1429,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.09937933087348938</v>
+        <v>0.09820990264415741</v>
       </c>
       <c r="C13" s="1">
         <v>110</v>
@@ -1455,7 +1455,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.09034484624862671</v>
+        <v>0.08928173035383225</v>
       </c>
       <c r="C14" s="1">
         <v>100</v>
@@ -1481,7 +1481,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.0560138039290905</v>
+        <v>0.05535467341542244</v>
       </c>
       <c r="C15" s="1">
         <v>62</v>
@@ -1507,7 +1507,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.05059311538934708</v>
+        <v>0.04999776929616928</v>
       </c>
       <c r="C16" s="1">
         <v>56</v>
@@ -1533,7 +1533,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.0487862154841423</v>
+        <v>0.04821213334798813</v>
       </c>
       <c r="C17" s="1">
         <v>54</v>
@@ -1559,7 +1559,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.04517242312431335</v>
+        <v>0.04464086517691612</v>
       </c>
       <c r="C18" s="1">
         <v>50</v>
@@ -1585,7 +1585,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.04517242312431335</v>
+        <v>0.04464086517691612</v>
       </c>
       <c r="C19" s="1">
         <v>50</v>
@@ -1611,7 +1611,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.04336552694439888</v>
+        <v>0.04285522922873497</v>
       </c>
       <c r="C20" s="1">
         <v>48</v>
@@ -1637,7 +1637,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.03613793849945068</v>
+        <v>0.03571269288659096</v>
       </c>
       <c r="C21" s="1">
         <v>40</v>
@@ -1663,7 +1663,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.03433104231953621</v>
+        <v>0.03392705693840981</v>
       </c>
       <c r="C22" s="1">
         <v>38</v>
@@ -1689,7 +1689,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.03252414613962174</v>
+        <v>0.03214142099022865</v>
       </c>
       <c r="C23" s="1">
         <v>36</v>
@@ -1715,7 +1715,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.03252414613962174</v>
+        <v>0.03214142099022865</v>
       </c>
       <c r="C24" s="1">
         <v>36</v>
@@ -1741,7 +1741,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>0.02891035005450249</v>
+        <v>0.02857015281915665</v>
       </c>
       <c r="C25" s="1">
         <v>32</v>
@@ -1767,7 +1767,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>0.02710345387458801</v>
+        <v>0.02678451873362064</v>
       </c>
       <c r="C26" s="1">
         <v>30</v>
@@ -1793,7 +1793,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2">
-        <v>0.02710345387458801</v>
+        <v>0.02678451873362064</v>
       </c>
       <c r="C27" s="1">
         <v>30</v>
@@ -1819,7 +1819,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="2">
-        <v>0.02529655769467354</v>
+        <v>0.02499888464808464</v>
       </c>
       <c r="C28" s="1">
         <v>28</v>
@@ -1845,7 +1845,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="2">
-        <v>0.02529655769467354</v>
+        <v>0.02499888464808464</v>
       </c>
       <c r="C29" s="1">
         <v>28</v>
@@ -1871,7 +1871,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="2">
-        <v>0.02529655769467354</v>
+        <v>0.02499888464808464</v>
       </c>
       <c r="C30" s="1">
         <v>28</v>
@@ -1897,7 +1897,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="2">
-        <v>0.02529655769467354</v>
+        <v>0.02499888464808464</v>
       </c>
       <c r="C31" s="1">
         <v>28</v>
@@ -1923,7 +1923,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="2">
-        <v>0.02529655769467354</v>
+        <v>0.02499888464808464</v>
       </c>
       <c r="C32" s="1">
         <v>28</v>
@@ -1949,7 +1949,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="2">
-        <v>0.02348965965211391</v>
+        <v>0.02321324869990349</v>
       </c>
       <c r="C33" s="1">
         <v>26</v>
@@ -1975,7 +1975,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.01626207306981087</v>
+        <v>0.01607071049511433</v>
       </c>
       <c r="C34" s="1">
         <v>18</v>
@@ -2001,7 +2001,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="2">
-        <v>0.009034484624862671</v>
+        <v>0.008928173221647739</v>
       </c>
       <c r="C35" s="1">
         <v>10</v>
@@ -2027,7 +2027,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="2">
-        <v>0.007227587513625622</v>
+        <v>0.007142538204789162</v>
       </c>
       <c r="C36" s="1">
         <v>8</v>
@@ -2053,7 +2053,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="2">
-        <v>0.007227587513625622</v>
+        <v>0.007142538204789162</v>
       </c>
       <c r="C37" s="1">
         <v>8</v>
@@ -2079,7 +2079,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="2">
-        <v>0.003613793756812811</v>
+        <v>0.003571269102394581</v>
       </c>
       <c r="C38" s="1">
         <v>4</v>

--- a/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
+++ b/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
@@ -20,7 +20,7 @@
     <t>AT32F415RBT7_WorkBench</t>
   </si>
   <si>
-    <t>lto-llvm-2f24cf.o</t>
+    <t>lto-llvm-a62878.o</t>
   </si>
   <si>
     <t>startup_at32f415.o</t>
@@ -249,7 +249,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-2f24cf.o</c:v>
+                  <c:v>lto-llvm-a62878.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>startup_at32f415.o</c:v>
@@ -267,10 +267,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>85.96491241455078</c:v>
+                  <c:v>91.61274719238281</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>14.03508758544922</c:v>
+                  <c:v>8.387255668640137</c:v>
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>0</c:v>
@@ -344,7 +344,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-2f24cf.o</c:v>
+                  <c:v>lto-llvm-a62878.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>mf_w.l</c:v>
@@ -464,112 +464,112 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>95.61090850830078</c:v>
+                  <c:v>95.64755249023438</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.807062149047852</c:v>
+                  <c:v>1.791975021362305</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.3606981933116913</c:v>
+                  <c:v>0.3576867282390595</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.2982009649276733</c:v>
+                  <c:v>0.2957113087177277</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.2071336060762405</c:v>
+                  <c:v>0.2054042518138886</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.2035623341798782</c:v>
+                  <c:v>0.2018627971410751</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.198205441236496</c:v>
+                  <c:v>0.1965506225824356</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.1660640090703964</c:v>
+                  <c:v>0.1646775454282761</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.1571358442306519</c:v>
+                  <c:v>0.1558239161968231</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.1107093468308449</c:v>
+                  <c:v>0.1097850352525711</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.09820990264415741</c:v>
+                  <c:v>0.09738995134830475</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.08928173035383225</c:v>
+                  <c:v>0.08853631466627121</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.05535467341542244</c:v>
+                  <c:v>0.05489251762628555</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.04999776929616928</c:v>
+                  <c:v>0.04958033934235573</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.04821213334798813</c:v>
+                  <c:v>0.04780961200594902</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.04464086517691612</c:v>
+                  <c:v>0.04426815733313561</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.04464086517691612</c:v>
+                  <c:v>0.04426815733313561</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.04285522922873497</c:v>
+                  <c:v>0.0424974337220192</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.03571269288659096</c:v>
+                  <c:v>0.03541452810168266</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.03392705693840981</c:v>
+                  <c:v>0.03364380076527596</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.03214142099022865</c:v>
+                  <c:v>0.03187307342886925</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.03214142099022865</c:v>
+                  <c:v>0.03187307342886925</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.02857015281915665</c:v>
+                  <c:v>0.02833162248134613</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.02678451873362064</c:v>
+                  <c:v>0.02656089514493942</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.02678451873362064</c:v>
+                  <c:v>0.02656089514493942</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.02499888464808464</c:v>
+                  <c:v>0.02479016967117786</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.02499888464808464</c:v>
+                  <c:v>0.02479016967117786</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.02499888464808464</c:v>
+                  <c:v>0.02479016967117786</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.02499888464808464</c:v>
+                  <c:v>0.02479016967117786</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.02499888464808464</c:v>
+                  <c:v>0.02479016967117786</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.02321324869990349</c:v>
+                  <c:v>0.02301944233477116</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.01607071049511433</c:v>
+                  <c:v>0.01593653671443462</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.008928173221647739</c:v>
+                  <c:v>0.008853632025420666</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.007142538204789162</c:v>
+                  <c:v>0.007082905620336533</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.007142538204789162</c:v>
+                  <c:v>0.007082905620336533</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.003571269102394581</c:v>
+                  <c:v>0.003541452810168266</c:v>
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>0</c:v>
@@ -1036,25 +1036,25 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>85.96491241455078</v>
+        <v>91.61274719238281</v>
       </c>
       <c r="C3" s="1">
-        <v>6272</v>
+        <v>11185</v>
       </c>
       <c r="D3" s="1">
-        <v>107089</v>
+        <v>108032</v>
       </c>
       <c r="E3" s="1">
-        <v>31094</v>
+        <v>32020</v>
       </c>
       <c r="F3" s="1">
-        <v>75734</v>
+        <v>75751</v>
       </c>
       <c r="G3" s="1">
         <v>261</v>
       </c>
       <c r="H3" s="1">
-        <v>6011</v>
+        <v>10924</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1062,7 +1062,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>14.03508758544922</v>
+        <v>8.387255668640137</v>
       </c>
       <c r="C4" s="1">
         <v>1024</v>
@@ -1169,25 +1169,25 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>95.61090850830078</v>
+        <v>95.64755249023438</v>
       </c>
       <c r="C3" s="1">
-        <v>107089</v>
+        <v>108032</v>
       </c>
       <c r="D3" s="1">
-        <v>6272</v>
+        <v>11185</v>
       </c>
       <c r="E3" s="1">
-        <v>31094</v>
+        <v>32020</v>
       </c>
       <c r="F3" s="1">
-        <v>75734</v>
+        <v>75751</v>
       </c>
       <c r="G3" s="1">
         <v>261</v>
       </c>
       <c r="H3" s="1">
-        <v>6011</v>
+        <v>10924</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1195,7 +1195,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>1.807062149047852</v>
+        <v>1.791975021362305</v>
       </c>
       <c r="C4" s="1">
         <v>2024</v>
@@ -1221,7 +1221,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2">
-        <v>0.3606981933116913</v>
+        <v>0.3576867282390595</v>
       </c>
       <c r="C5" s="1">
         <v>404</v>
@@ -1247,7 +1247,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>0.2982009649276733</v>
+        <v>0.2957113087177277</v>
       </c>
       <c r="C6" s="1">
         <v>334</v>
@@ -1273,7 +1273,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>0.2071336060762405</v>
+        <v>0.2054042518138886</v>
       </c>
       <c r="C7" s="1">
         <v>232</v>
@@ -1299,7 +1299,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>0.2035623341798782</v>
+        <v>0.2018627971410751</v>
       </c>
       <c r="C8" s="1">
         <v>228</v>
@@ -1325,7 +1325,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.198205441236496</v>
+        <v>0.1965506225824356</v>
       </c>
       <c r="C9" s="1">
         <v>222</v>
@@ -1351,7 +1351,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.1660640090703964</v>
+        <v>0.1646775454282761</v>
       </c>
       <c r="C10" s="1">
         <v>186</v>
@@ -1377,7 +1377,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.1571358442306519</v>
+        <v>0.1558239161968231</v>
       </c>
       <c r="C11" s="1">
         <v>176</v>
@@ -1403,7 +1403,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.1107093468308449</v>
+        <v>0.1097850352525711</v>
       </c>
       <c r="C12" s="1">
         <v>124</v>
@@ -1429,7 +1429,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.09820990264415741</v>
+        <v>0.09738995134830475</v>
       </c>
       <c r="C13" s="1">
         <v>110</v>
@@ -1455,7 +1455,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.08928173035383225</v>
+        <v>0.08853631466627121</v>
       </c>
       <c r="C14" s="1">
         <v>100</v>
@@ -1481,7 +1481,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.05535467341542244</v>
+        <v>0.05489251762628555</v>
       </c>
       <c r="C15" s="1">
         <v>62</v>
@@ -1507,7 +1507,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.04999776929616928</v>
+        <v>0.04958033934235573</v>
       </c>
       <c r="C16" s="1">
         <v>56</v>
@@ -1533,7 +1533,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.04821213334798813</v>
+        <v>0.04780961200594902</v>
       </c>
       <c r="C17" s="1">
         <v>54</v>
@@ -1559,7 +1559,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.04464086517691612</v>
+        <v>0.04426815733313561</v>
       </c>
       <c r="C18" s="1">
         <v>50</v>
@@ -1585,7 +1585,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.04464086517691612</v>
+        <v>0.04426815733313561</v>
       </c>
       <c r="C19" s="1">
         <v>50</v>
@@ -1611,7 +1611,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.04285522922873497</v>
+        <v>0.0424974337220192</v>
       </c>
       <c r="C20" s="1">
         <v>48</v>
@@ -1637,7 +1637,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.03571269288659096</v>
+        <v>0.03541452810168266</v>
       </c>
       <c r="C21" s="1">
         <v>40</v>
@@ -1663,7 +1663,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.03392705693840981</v>
+        <v>0.03364380076527596</v>
       </c>
       <c r="C22" s="1">
         <v>38</v>
@@ -1689,7 +1689,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.03214142099022865</v>
+        <v>0.03187307342886925</v>
       </c>
       <c r="C23" s="1">
         <v>36</v>
@@ -1715,7 +1715,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.03214142099022865</v>
+        <v>0.03187307342886925</v>
       </c>
       <c r="C24" s="1">
         <v>36</v>
@@ -1741,7 +1741,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>0.02857015281915665</v>
+        <v>0.02833162248134613</v>
       </c>
       <c r="C25" s="1">
         <v>32</v>
@@ -1767,7 +1767,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>0.02678451873362064</v>
+        <v>0.02656089514493942</v>
       </c>
       <c r="C26" s="1">
         <v>30</v>
@@ -1793,7 +1793,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2">
-        <v>0.02678451873362064</v>
+        <v>0.02656089514493942</v>
       </c>
       <c r="C27" s="1">
         <v>30</v>
@@ -1819,7 +1819,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="2">
-        <v>0.02499888464808464</v>
+        <v>0.02479016967117786</v>
       </c>
       <c r="C28" s="1">
         <v>28</v>
@@ -1845,7 +1845,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="2">
-        <v>0.02499888464808464</v>
+        <v>0.02479016967117786</v>
       </c>
       <c r="C29" s="1">
         <v>28</v>
@@ -1871,7 +1871,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="2">
-        <v>0.02499888464808464</v>
+        <v>0.02479016967117786</v>
       </c>
       <c r="C30" s="1">
         <v>28</v>
@@ -1897,7 +1897,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="2">
-        <v>0.02499888464808464</v>
+        <v>0.02479016967117786</v>
       </c>
       <c r="C31" s="1">
         <v>28</v>
@@ -1923,7 +1923,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="2">
-        <v>0.02499888464808464</v>
+        <v>0.02479016967117786</v>
       </c>
       <c r="C32" s="1">
         <v>28</v>
@@ -1949,7 +1949,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="2">
-        <v>0.02321324869990349</v>
+        <v>0.02301944233477116</v>
       </c>
       <c r="C33" s="1">
         <v>26</v>
@@ -1975,7 +1975,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.01607071049511433</v>
+        <v>0.01593653671443462</v>
       </c>
       <c r="C34" s="1">
         <v>18</v>
@@ -2001,7 +2001,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="2">
-        <v>0.008928173221647739</v>
+        <v>0.008853632025420666</v>
       </c>
       <c r="C35" s="1">
         <v>10</v>
@@ -2027,7 +2027,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="2">
-        <v>0.007142538204789162</v>
+        <v>0.007082905620336533</v>
       </c>
       <c r="C36" s="1">
         <v>8</v>
@@ -2053,7 +2053,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="2">
-        <v>0.007142538204789162</v>
+        <v>0.007082905620336533</v>
       </c>
       <c r="C37" s="1">
         <v>8</v>
@@ -2079,7 +2079,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="2">
-        <v>0.003571269102394581</v>
+        <v>0.003541452810168266</v>
       </c>
       <c r="C38" s="1">
         <v>4</v>

--- a/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
+++ b/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
@@ -20,7 +20,7 @@
     <t>AT32F415RBT7_WorkBench</t>
   </si>
   <si>
-    <t>lto-llvm-a62878.o</t>
+    <t>lto-llvm-5453c4.o</t>
   </si>
   <si>
     <t>startup_at32f415.o</t>
@@ -249,7 +249,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-a62878.o</c:v>
+                  <c:v>lto-llvm-5453c4.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>startup_at32f415.o</c:v>
@@ -344,7 +344,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-a62878.o</c:v>
+                  <c:v>lto-llvm-5453c4.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>mf_w.l</c:v>
@@ -464,112 +464,112 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>95.64755249023438</c:v>
+                  <c:v>95.65017700195313</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.791975021362305</c:v>
+                  <c:v>1.790896892547607</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.3576867282390595</c:v>
+                  <c:v>0.3574714958667755</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.2957113087177277</c:v>
+                  <c:v>0.2955333888530731</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.2054042518138886</c:v>
+                  <c:v>0.2052806615829468</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.2018627971410751</c:v>
+                  <c:v>0.2017413526773453</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.1965506225824356</c:v>
+                  <c:v>0.1964323669672012</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.1646775454282761</c:v>
+                  <c:v>0.1645784676074982</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.1558239161968231</c:v>
+                  <c:v>0.1557301580905914</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.1097850352525711</c:v>
+                  <c:v>0.1097189784049988</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.09738995134830475</c:v>
+                  <c:v>0.09733135253190994</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.08853631466627121</c:v>
+                  <c:v>0.0884830430150032</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.05489251762628555</c:v>
+                  <c:v>0.05485948920249939</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.04958033934235573</c:v>
+                  <c:v>0.04955050721764565</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.04780961200594902</c:v>
+                  <c:v>0.0477808453142643</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.04426815733313561</c:v>
+                  <c:v>0.0442415215075016</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.04426815733313561</c:v>
+                  <c:v>0.0442415215075016</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.0424974337220192</c:v>
+                  <c:v>0.04247186332941055</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.03541452810168266</c:v>
+                  <c:v>0.03539321944117546</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.03364380076527596</c:v>
+                  <c:v>0.03362355753779411</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.03187307342886925</c:v>
+                  <c:v>0.03185389563441277</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.03187307342886925</c:v>
+                  <c:v>0.03185389563441277</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.02833162248134613</c:v>
+                  <c:v>0.02831457555294037</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.02656089514493942</c:v>
+                  <c:v>0.02654491364955902</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.02656089514493942</c:v>
+                  <c:v>0.02654491364955902</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.02479016967117786</c:v>
+                  <c:v>0.02477525360882282</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.02479016967117786</c:v>
+                  <c:v>0.02477525360882282</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.02479016967117786</c:v>
+                  <c:v>0.02477525360882282</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.02479016967117786</c:v>
+                  <c:v>0.02477525360882282</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.02479016967117786</c:v>
+                  <c:v>0.02477525360882282</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.02301944233477116</c:v>
+                  <c:v>0.02300559170544148</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.01593653671443462</c:v>
+                  <c:v>0.01592694781720638</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.008853632025420666</c:v>
+                  <c:v>0.008848304860293865</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.007082905620336533</c:v>
+                  <c:v>0.007078643888235092</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.007082905620336533</c:v>
+                  <c:v>0.007078643888235092</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.003541452810168266</c:v>
+                  <c:v>0.003539321944117546</c:v>
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>0</c:v>
@@ -1042,10 +1042,10 @@
         <v>11185</v>
       </c>
       <c r="D3" s="1">
-        <v>108032</v>
+        <v>108100</v>
       </c>
       <c r="E3" s="1">
-        <v>32020</v>
+        <v>32088</v>
       </c>
       <c r="F3" s="1">
         <v>75751</v>
@@ -1169,16 +1169,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>95.64755249023438</v>
+        <v>95.65017700195313</v>
       </c>
       <c r="C3" s="1">
-        <v>108032</v>
+        <v>108100</v>
       </c>
       <c r="D3" s="1">
         <v>11185</v>
       </c>
       <c r="E3" s="1">
-        <v>32020</v>
+        <v>32088</v>
       </c>
       <c r="F3" s="1">
         <v>75751</v>
@@ -1195,7 +1195,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>1.791975021362305</v>
+        <v>1.790896892547607</v>
       </c>
       <c r="C4" s="1">
         <v>2024</v>
@@ -1221,7 +1221,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2">
-        <v>0.3576867282390595</v>
+        <v>0.3574714958667755</v>
       </c>
       <c r="C5" s="1">
         <v>404</v>
@@ -1247,7 +1247,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>0.2957113087177277</v>
+        <v>0.2955333888530731</v>
       </c>
       <c r="C6" s="1">
         <v>334</v>
@@ -1273,7 +1273,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>0.2054042518138886</v>
+        <v>0.2052806615829468</v>
       </c>
       <c r="C7" s="1">
         <v>232</v>
@@ -1299,7 +1299,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>0.2018627971410751</v>
+        <v>0.2017413526773453</v>
       </c>
       <c r="C8" s="1">
         <v>228</v>
@@ -1325,7 +1325,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.1965506225824356</v>
+        <v>0.1964323669672012</v>
       </c>
       <c r="C9" s="1">
         <v>222</v>
@@ -1351,7 +1351,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.1646775454282761</v>
+        <v>0.1645784676074982</v>
       </c>
       <c r="C10" s="1">
         <v>186</v>
@@ -1377,7 +1377,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.1558239161968231</v>
+        <v>0.1557301580905914</v>
       </c>
       <c r="C11" s="1">
         <v>176</v>
@@ -1403,7 +1403,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.1097850352525711</v>
+        <v>0.1097189784049988</v>
       </c>
       <c r="C12" s="1">
         <v>124</v>
@@ -1429,7 +1429,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.09738995134830475</v>
+        <v>0.09733135253190994</v>
       </c>
       <c r="C13" s="1">
         <v>110</v>
@@ -1455,7 +1455,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.08853631466627121</v>
+        <v>0.0884830430150032</v>
       </c>
       <c r="C14" s="1">
         <v>100</v>
@@ -1481,7 +1481,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.05489251762628555</v>
+        <v>0.05485948920249939</v>
       </c>
       <c r="C15" s="1">
         <v>62</v>
@@ -1507,7 +1507,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.04958033934235573</v>
+        <v>0.04955050721764565</v>
       </c>
       <c r="C16" s="1">
         <v>56</v>
@@ -1533,7 +1533,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.04780961200594902</v>
+        <v>0.0477808453142643</v>
       </c>
       <c r="C17" s="1">
         <v>54</v>
@@ -1559,7 +1559,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.04426815733313561</v>
+        <v>0.0442415215075016</v>
       </c>
       <c r="C18" s="1">
         <v>50</v>
@@ -1585,7 +1585,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.04426815733313561</v>
+        <v>0.0442415215075016</v>
       </c>
       <c r="C19" s="1">
         <v>50</v>
@@ -1611,7 +1611,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.0424974337220192</v>
+        <v>0.04247186332941055</v>
       </c>
       <c r="C20" s="1">
         <v>48</v>
@@ -1637,7 +1637,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.03541452810168266</v>
+        <v>0.03539321944117546</v>
       </c>
       <c r="C21" s="1">
         <v>40</v>
@@ -1663,7 +1663,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.03364380076527596</v>
+        <v>0.03362355753779411</v>
       </c>
       <c r="C22" s="1">
         <v>38</v>
@@ -1689,7 +1689,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.03187307342886925</v>
+        <v>0.03185389563441277</v>
       </c>
       <c r="C23" s="1">
         <v>36</v>
@@ -1715,7 +1715,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.03187307342886925</v>
+        <v>0.03185389563441277</v>
       </c>
       <c r="C24" s="1">
         <v>36</v>
@@ -1741,7 +1741,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>0.02833162248134613</v>
+        <v>0.02831457555294037</v>
       </c>
       <c r="C25" s="1">
         <v>32</v>
@@ -1767,7 +1767,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>0.02656089514493942</v>
+        <v>0.02654491364955902</v>
       </c>
       <c r="C26" s="1">
         <v>30</v>
@@ -1793,7 +1793,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2">
-        <v>0.02656089514493942</v>
+        <v>0.02654491364955902</v>
       </c>
       <c r="C27" s="1">
         <v>30</v>
@@ -1819,7 +1819,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="2">
-        <v>0.02479016967117786</v>
+        <v>0.02477525360882282</v>
       </c>
       <c r="C28" s="1">
         <v>28</v>
@@ -1845,7 +1845,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="2">
-        <v>0.02479016967117786</v>
+        <v>0.02477525360882282</v>
       </c>
       <c r="C29" s="1">
         <v>28</v>
@@ -1871,7 +1871,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="2">
-        <v>0.02479016967117786</v>
+        <v>0.02477525360882282</v>
       </c>
       <c r="C30" s="1">
         <v>28</v>
@@ -1897,7 +1897,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="2">
-        <v>0.02479016967117786</v>
+        <v>0.02477525360882282</v>
       </c>
       <c r="C31" s="1">
         <v>28</v>
@@ -1923,7 +1923,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="2">
-        <v>0.02479016967117786</v>
+        <v>0.02477525360882282</v>
       </c>
       <c r="C32" s="1">
         <v>28</v>
@@ -1949,7 +1949,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="2">
-        <v>0.02301944233477116</v>
+        <v>0.02300559170544148</v>
       </c>
       <c r="C33" s="1">
         <v>26</v>
@@ -1975,7 +1975,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.01593653671443462</v>
+        <v>0.01592694781720638</v>
       </c>
       <c r="C34" s="1">
         <v>18</v>
@@ -2001,7 +2001,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="2">
-        <v>0.008853632025420666</v>
+        <v>0.008848304860293865</v>
       </c>
       <c r="C35" s="1">
         <v>10</v>
@@ -2027,7 +2027,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="2">
-        <v>0.007082905620336533</v>
+        <v>0.007078643888235092</v>
       </c>
       <c r="C36" s="1">
         <v>8</v>
@@ -2053,7 +2053,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="2">
-        <v>0.007082905620336533</v>
+        <v>0.007078643888235092</v>
       </c>
       <c r="C37" s="1">
         <v>8</v>
@@ -2079,7 +2079,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="2">
-        <v>0.003541452810168266</v>
+        <v>0.003539321944117546</v>
       </c>
       <c r="C38" s="1">
         <v>4</v>

--- a/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
+++ b/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
@@ -20,7 +20,7 @@
     <t>AT32F415RBT7_WorkBench</t>
   </si>
   <si>
-    <t>lto-llvm-5453c4.o</t>
+    <t>lto-llvm-51a62a.o</t>
   </si>
   <si>
     <t>startup_at32f415.o</t>
@@ -249,7 +249,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-5453c4.o</c:v>
+                  <c:v>lto-llvm-51a62a.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>startup_at32f415.o</c:v>
@@ -344,7 +344,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-5453c4.o</c:v>
+                  <c:v>lto-llvm-51a62a.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>mf_w.l</c:v>

--- a/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
+++ b/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
@@ -20,7 +20,7 @@
     <t>AT32F415RBT7_WorkBench</t>
   </si>
   <si>
-    <t>lto-llvm-51a62a.o</t>
+    <t>lto-llvm-162165.o</t>
   </si>
   <si>
     <t>startup_at32f415.o</t>
@@ -249,7 +249,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-51a62a.o</c:v>
+                  <c:v>lto-llvm-162165.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>startup_at32f415.o</c:v>
@@ -344,7 +344,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-51a62a.o</c:v>
+                  <c:v>lto-llvm-162165.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>mf_w.l</c:v>
@@ -464,112 +464,112 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>95.65017700195313</c:v>
+                  <c:v>95.65040588378906</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.790896892547607</c:v>
+                  <c:v>1.790801763534546</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.3574714958667755</c:v>
+                  <c:v>0.3574525415897369</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.2955333888530731</c:v>
+                  <c:v>0.2955176830291748</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.2052806615829468</c:v>
+                  <c:v>0.2052697688341141</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.2017413526773453</c:v>
+                  <c:v>0.2017306387424469</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.1964323669672012</c:v>
+                  <c:v>0.1964219361543655</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.1645784676074982</c:v>
+                  <c:v>0.1645697355270386</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.1557301580905914</c:v>
+                  <c:v>0.1557218879461289</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.1097189784049988</c:v>
+                  <c:v>0.109713152050972</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.09733135253190994</c:v>
+                  <c:v>0.09732618182897568</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.0884830430150032</c:v>
+                  <c:v>0.08847834914922714</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.05485948920249939</c:v>
+                  <c:v>0.05485657602548599</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.04955050721764565</c:v>
+                  <c:v>0.04954787716269493</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.0477808453142643</c:v>
+                  <c:v>0.04777830839157105</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.0442415215075016</c:v>
+                  <c:v>0.04423917457461357</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.0442415215075016</c:v>
+                  <c:v>0.04423917457461357</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.04247186332941055</c:v>
+                  <c:v>0.04246960952877998</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.03539321944117546</c:v>
+                  <c:v>0.03539133816957474</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.03362355753779411</c:v>
+                  <c:v>0.03362177312374115</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.03185389563441277</c:v>
+                  <c:v>0.03185220435261726</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.03185389563441277</c:v>
+                  <c:v>0.03185220435261726</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.02831457555294037</c:v>
+                  <c:v>0.02831307239830494</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.02654491364955902</c:v>
+                  <c:v>0.0265435054898262</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.02654491364955902</c:v>
+                  <c:v>0.0265435054898262</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.02477525360882282</c:v>
+                  <c:v>0.02477393858134747</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.02477525360882282</c:v>
+                  <c:v>0.02477393858134747</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.02477525360882282</c:v>
+                  <c:v>0.02477393858134747</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.02477525360882282</c:v>
+                  <c:v>0.02477393858134747</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.02477525360882282</c:v>
+                  <c:v>0.02477393858134747</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.02300559170544148</c:v>
+                  <c:v>0.02300437167286873</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.01592694781720638</c:v>
+                  <c:v>0.01592610217630863</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.008848304860293865</c:v>
+                  <c:v>0.008847834542393684</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.007078643888235092</c:v>
+                  <c:v>0.007078268099576235</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.007078643888235092</c:v>
+                  <c:v>0.007078268099576235</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.003539321944117546</c:v>
+                  <c:v>0.003539134049788117</c:v>
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>0</c:v>
@@ -1042,10 +1042,10 @@
         <v>11185</v>
       </c>
       <c r="D3" s="1">
-        <v>108100</v>
+        <v>108106</v>
       </c>
       <c r="E3" s="1">
-        <v>32088</v>
+        <v>32094</v>
       </c>
       <c r="F3" s="1">
         <v>75751</v>
@@ -1169,16 +1169,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>95.65017700195313</v>
+        <v>95.65040588378906</v>
       </c>
       <c r="C3" s="1">
-        <v>108100</v>
+        <v>108106</v>
       </c>
       <c r="D3" s="1">
         <v>11185</v>
       </c>
       <c r="E3" s="1">
-        <v>32088</v>
+        <v>32094</v>
       </c>
       <c r="F3" s="1">
         <v>75751</v>
@@ -1195,7 +1195,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>1.790896892547607</v>
+        <v>1.790801763534546</v>
       </c>
       <c r="C4" s="1">
         <v>2024</v>
@@ -1221,7 +1221,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2">
-        <v>0.3574714958667755</v>
+        <v>0.3574525415897369</v>
       </c>
       <c r="C5" s="1">
         <v>404</v>
@@ -1247,7 +1247,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>0.2955333888530731</v>
+        <v>0.2955176830291748</v>
       </c>
       <c r="C6" s="1">
         <v>334</v>
@@ -1273,7 +1273,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>0.2052806615829468</v>
+        <v>0.2052697688341141</v>
       </c>
       <c r="C7" s="1">
         <v>232</v>
@@ -1299,7 +1299,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>0.2017413526773453</v>
+        <v>0.2017306387424469</v>
       </c>
       <c r="C8" s="1">
         <v>228</v>
@@ -1325,7 +1325,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.1964323669672012</v>
+        <v>0.1964219361543655</v>
       </c>
       <c r="C9" s="1">
         <v>222</v>
@@ -1351,7 +1351,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.1645784676074982</v>
+        <v>0.1645697355270386</v>
       </c>
       <c r="C10" s="1">
         <v>186</v>
@@ -1377,7 +1377,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.1557301580905914</v>
+        <v>0.1557218879461289</v>
       </c>
       <c r="C11" s="1">
         <v>176</v>
@@ -1403,7 +1403,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.1097189784049988</v>
+        <v>0.109713152050972</v>
       </c>
       <c r="C12" s="1">
         <v>124</v>
@@ -1429,7 +1429,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.09733135253190994</v>
+        <v>0.09732618182897568</v>
       </c>
       <c r="C13" s="1">
         <v>110</v>
@@ -1455,7 +1455,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.0884830430150032</v>
+        <v>0.08847834914922714</v>
       </c>
       <c r="C14" s="1">
         <v>100</v>
@@ -1481,7 +1481,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.05485948920249939</v>
+        <v>0.05485657602548599</v>
       </c>
       <c r="C15" s="1">
         <v>62</v>
@@ -1507,7 +1507,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.04955050721764565</v>
+        <v>0.04954787716269493</v>
       </c>
       <c r="C16" s="1">
         <v>56</v>
@@ -1533,7 +1533,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.0477808453142643</v>
+        <v>0.04777830839157105</v>
       </c>
       <c r="C17" s="1">
         <v>54</v>
@@ -1559,7 +1559,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.0442415215075016</v>
+        <v>0.04423917457461357</v>
       </c>
       <c r="C18" s="1">
         <v>50</v>
@@ -1585,7 +1585,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.0442415215075016</v>
+        <v>0.04423917457461357</v>
       </c>
       <c r="C19" s="1">
         <v>50</v>
@@ -1611,7 +1611,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.04247186332941055</v>
+        <v>0.04246960952877998</v>
       </c>
       <c r="C20" s="1">
         <v>48</v>
@@ -1637,7 +1637,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.03539321944117546</v>
+        <v>0.03539133816957474</v>
       </c>
       <c r="C21" s="1">
         <v>40</v>
@@ -1663,7 +1663,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.03362355753779411</v>
+        <v>0.03362177312374115</v>
       </c>
       <c r="C22" s="1">
         <v>38</v>
@@ -1689,7 +1689,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.03185389563441277</v>
+        <v>0.03185220435261726</v>
       </c>
       <c r="C23" s="1">
         <v>36</v>
@@ -1715,7 +1715,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.03185389563441277</v>
+        <v>0.03185220435261726</v>
       </c>
       <c r="C24" s="1">
         <v>36</v>
@@ -1741,7 +1741,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>0.02831457555294037</v>
+        <v>0.02831307239830494</v>
       </c>
       <c r="C25" s="1">
         <v>32</v>
@@ -1767,7 +1767,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>0.02654491364955902</v>
+        <v>0.0265435054898262</v>
       </c>
       <c r="C26" s="1">
         <v>30</v>
@@ -1793,7 +1793,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2">
-        <v>0.02654491364955902</v>
+        <v>0.0265435054898262</v>
       </c>
       <c r="C27" s="1">
         <v>30</v>
@@ -1819,7 +1819,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="2">
-        <v>0.02477525360882282</v>
+        <v>0.02477393858134747</v>
       </c>
       <c r="C28" s="1">
         <v>28</v>
@@ -1845,7 +1845,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="2">
-        <v>0.02477525360882282</v>
+        <v>0.02477393858134747</v>
       </c>
       <c r="C29" s="1">
         <v>28</v>
@@ -1871,7 +1871,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="2">
-        <v>0.02477525360882282</v>
+        <v>0.02477393858134747</v>
       </c>
       <c r="C30" s="1">
         <v>28</v>
@@ -1897,7 +1897,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="2">
-        <v>0.02477525360882282</v>
+        <v>0.02477393858134747</v>
       </c>
       <c r="C31" s="1">
         <v>28</v>
@@ -1923,7 +1923,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="2">
-        <v>0.02477525360882282</v>
+        <v>0.02477393858134747</v>
       </c>
       <c r="C32" s="1">
         <v>28</v>
@@ -1949,7 +1949,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="2">
-        <v>0.02300559170544148</v>
+        <v>0.02300437167286873</v>
       </c>
       <c r="C33" s="1">
         <v>26</v>
@@ -1975,7 +1975,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.01592694781720638</v>
+        <v>0.01592610217630863</v>
       </c>
       <c r="C34" s="1">
         <v>18</v>
@@ -2001,7 +2001,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="2">
-        <v>0.008848304860293865</v>
+        <v>0.008847834542393684</v>
       </c>
       <c r="C35" s="1">
         <v>10</v>
@@ -2027,7 +2027,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="2">
-        <v>0.007078643888235092</v>
+        <v>0.007078268099576235</v>
       </c>
       <c r="C36" s="1">
         <v>8</v>
@@ -2053,7 +2053,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="2">
-        <v>0.007078643888235092</v>
+        <v>0.007078268099576235</v>
       </c>
       <c r="C37" s="1">
         <v>8</v>
@@ -2079,7 +2079,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="2">
-        <v>0.003539321944117546</v>
+        <v>0.003539134049788117</v>
       </c>
       <c r="C38" s="1">
         <v>4</v>

--- a/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
+++ b/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
@@ -20,7 +20,7 @@
     <t>AT32F415RBT7_WorkBench</t>
   </si>
   <si>
-    <t>lto-llvm-162165.o</t>
+    <t>lto-llvm-004ba7.o</t>
   </si>
   <si>
     <t>startup_at32f415.o</t>
@@ -249,7 +249,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-162165.o</c:v>
+                  <c:v>lto-llvm-004ba7.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>startup_at32f415.o</c:v>
@@ -344,7 +344,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-162165.o</c:v>
+                  <c:v>lto-llvm-004ba7.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>mf_w.l</c:v>
@@ -464,112 +464,112 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>95.65040588378906</c:v>
+                  <c:v>95.64986419677734</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.790801763534546</c:v>
+                  <c:v>1.7910236120224</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.3574525415897369</c:v>
+                  <c:v>0.3574968278408051</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.2955176830291748</c:v>
+                  <c:v>0.2955543100833893</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.2052697688341141</c:v>
+                  <c:v>0.205295205116272</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.2017306387424469</c:v>
+                  <c:v>0.201755627989769</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.1964219361543655</c:v>
+                  <c:v>0.1964462697505951</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.1645697355270386</c:v>
+                  <c:v>0.1645901203155518</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.1557218879461289</c:v>
+                  <c:v>0.1557411849498749</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.109713152050972</c:v>
+                  <c:v>0.1097267419099808</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.09732618182897568</c:v>
+                  <c:v>0.0973382443189621</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.08847834914922714</c:v>
+                  <c:v>0.08848930895328522</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.05485657602548599</c:v>
+                  <c:v>0.05486337095499039</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.04954787716269493</c:v>
+                  <c:v>0.0495540127158165</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.04777830839157105</c:v>
+                  <c:v>0.0477842278778553</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.04423917457461357</c:v>
+                  <c:v>0.04424465447664261</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.04423917457461357</c:v>
+                  <c:v>0.04424465447664261</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.04246960952877998</c:v>
+                  <c:v>0.04247486963868141</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.03539133816957474</c:v>
+                  <c:v>0.03539572283625603</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.03362177312374115</c:v>
+                  <c:v>0.03362593799829483</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.03185220435261726</c:v>
+                  <c:v>0.03185615316033363</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.03185220435261726</c:v>
+                  <c:v>0.03185615316033363</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.02831307239830494</c:v>
+                  <c:v>0.02831657975912094</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.0265435054898262</c:v>
+                  <c:v>0.0265467930585146</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.0265435054898262</c:v>
+                  <c:v>0.0265467930585146</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.02477393858134747</c:v>
+                  <c:v>0.02477700635790825</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.02477393858134747</c:v>
+                  <c:v>0.02477700635790825</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.02477393858134747</c:v>
+                  <c:v>0.02477700635790825</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.02477393858134747</c:v>
+                  <c:v>0.02477700635790825</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.02477393858134747</c:v>
+                  <c:v>0.02477700635790825</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.02300437167286873</c:v>
+                  <c:v>0.02300722151994705</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.01592610217630863</c:v>
+                  <c:v>0.01592807658016682</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.008847834542393684</c:v>
+                  <c:v>0.008848930709064007</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.007078268099576235</c:v>
+                  <c:v>0.007079144939780235</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.007078268099576235</c:v>
+                  <c:v>0.007079144939780235</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.003539134049788117</c:v>
+                  <c:v>0.003539572469890118</c:v>
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>0</c:v>
@@ -1042,10 +1042,10 @@
         <v>11185</v>
       </c>
       <c r="D3" s="1">
-        <v>108106</v>
+        <v>108092</v>
       </c>
       <c r="E3" s="1">
-        <v>32094</v>
+        <v>32080</v>
       </c>
       <c r="F3" s="1">
         <v>75751</v>
@@ -1169,16 +1169,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>95.65040588378906</v>
+        <v>95.64986419677734</v>
       </c>
       <c r="C3" s="1">
-        <v>108106</v>
+        <v>108092</v>
       </c>
       <c r="D3" s="1">
         <v>11185</v>
       </c>
       <c r="E3" s="1">
-        <v>32094</v>
+        <v>32080</v>
       </c>
       <c r="F3" s="1">
         <v>75751</v>
@@ -1195,7 +1195,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>1.790801763534546</v>
+        <v>1.7910236120224</v>
       </c>
       <c r="C4" s="1">
         <v>2024</v>
@@ -1221,7 +1221,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2">
-        <v>0.3574525415897369</v>
+        <v>0.3574968278408051</v>
       </c>
       <c r="C5" s="1">
         <v>404</v>
@@ -1247,7 +1247,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>0.2955176830291748</v>
+        <v>0.2955543100833893</v>
       </c>
       <c r="C6" s="1">
         <v>334</v>
@@ -1273,7 +1273,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>0.2052697688341141</v>
+        <v>0.205295205116272</v>
       </c>
       <c r="C7" s="1">
         <v>232</v>
@@ -1299,7 +1299,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>0.2017306387424469</v>
+        <v>0.201755627989769</v>
       </c>
       <c r="C8" s="1">
         <v>228</v>
@@ -1325,7 +1325,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.1964219361543655</v>
+        <v>0.1964462697505951</v>
       </c>
       <c r="C9" s="1">
         <v>222</v>
@@ -1351,7 +1351,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.1645697355270386</v>
+        <v>0.1645901203155518</v>
       </c>
       <c r="C10" s="1">
         <v>186</v>
@@ -1377,7 +1377,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.1557218879461289</v>
+        <v>0.1557411849498749</v>
       </c>
       <c r="C11" s="1">
         <v>176</v>
@@ -1403,7 +1403,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.109713152050972</v>
+        <v>0.1097267419099808</v>
       </c>
       <c r="C12" s="1">
         <v>124</v>
@@ -1429,7 +1429,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.09732618182897568</v>
+        <v>0.0973382443189621</v>
       </c>
       <c r="C13" s="1">
         <v>110</v>
@@ -1455,7 +1455,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.08847834914922714</v>
+        <v>0.08848930895328522</v>
       </c>
       <c r="C14" s="1">
         <v>100</v>
@@ -1481,7 +1481,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.05485657602548599</v>
+        <v>0.05486337095499039</v>
       </c>
       <c r="C15" s="1">
         <v>62</v>
@@ -1507,7 +1507,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.04954787716269493</v>
+        <v>0.0495540127158165</v>
       </c>
       <c r="C16" s="1">
         <v>56</v>
@@ -1533,7 +1533,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.04777830839157105</v>
+        <v>0.0477842278778553</v>
       </c>
       <c r="C17" s="1">
         <v>54</v>
@@ -1559,7 +1559,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.04423917457461357</v>
+        <v>0.04424465447664261</v>
       </c>
       <c r="C18" s="1">
         <v>50</v>
@@ -1585,7 +1585,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.04423917457461357</v>
+        <v>0.04424465447664261</v>
       </c>
       <c r="C19" s="1">
         <v>50</v>
@@ -1611,7 +1611,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.04246960952877998</v>
+        <v>0.04247486963868141</v>
       </c>
       <c r="C20" s="1">
         <v>48</v>
@@ -1637,7 +1637,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.03539133816957474</v>
+        <v>0.03539572283625603</v>
       </c>
       <c r="C21" s="1">
         <v>40</v>
@@ -1663,7 +1663,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.03362177312374115</v>
+        <v>0.03362593799829483</v>
       </c>
       <c r="C22" s="1">
         <v>38</v>
@@ -1689,7 +1689,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.03185220435261726</v>
+        <v>0.03185615316033363</v>
       </c>
       <c r="C23" s="1">
         <v>36</v>
@@ -1715,7 +1715,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.03185220435261726</v>
+        <v>0.03185615316033363</v>
       </c>
       <c r="C24" s="1">
         <v>36</v>
@@ -1741,7 +1741,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>0.02831307239830494</v>
+        <v>0.02831657975912094</v>
       </c>
       <c r="C25" s="1">
         <v>32</v>
@@ -1767,7 +1767,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>0.0265435054898262</v>
+        <v>0.0265467930585146</v>
       </c>
       <c r="C26" s="1">
         <v>30</v>
@@ -1793,7 +1793,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2">
-        <v>0.0265435054898262</v>
+        <v>0.0265467930585146</v>
       </c>
       <c r="C27" s="1">
         <v>30</v>
@@ -1819,7 +1819,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="2">
-        <v>0.02477393858134747</v>
+        <v>0.02477700635790825</v>
       </c>
       <c r="C28" s="1">
         <v>28</v>
@@ -1845,7 +1845,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="2">
-        <v>0.02477393858134747</v>
+        <v>0.02477700635790825</v>
       </c>
       <c r="C29" s="1">
         <v>28</v>
@@ -1871,7 +1871,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="2">
-        <v>0.02477393858134747</v>
+        <v>0.02477700635790825</v>
       </c>
       <c r="C30" s="1">
         <v>28</v>
@@ -1897,7 +1897,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="2">
-        <v>0.02477393858134747</v>
+        <v>0.02477700635790825</v>
       </c>
       <c r="C31" s="1">
         <v>28</v>
@@ -1923,7 +1923,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="2">
-        <v>0.02477393858134747</v>
+        <v>0.02477700635790825</v>
       </c>
       <c r="C32" s="1">
         <v>28</v>
@@ -1949,7 +1949,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="2">
-        <v>0.02300437167286873</v>
+        <v>0.02300722151994705</v>
       </c>
       <c r="C33" s="1">
         <v>26</v>
@@ -1975,7 +1975,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.01592610217630863</v>
+        <v>0.01592807658016682</v>
       </c>
       <c r="C34" s="1">
         <v>18</v>
@@ -2001,7 +2001,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="2">
-        <v>0.008847834542393684</v>
+        <v>0.008848930709064007</v>
       </c>
       <c r="C35" s="1">
         <v>10</v>
@@ -2027,7 +2027,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="2">
-        <v>0.007078268099576235</v>
+        <v>0.007079144939780235</v>
       </c>
       <c r="C36" s="1">
         <v>8</v>
@@ -2053,7 +2053,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="2">
-        <v>0.007078268099576235</v>
+        <v>0.007079144939780235</v>
       </c>
       <c r="C37" s="1">
         <v>8</v>
@@ -2079,7 +2079,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="2">
-        <v>0.003539134049788117</v>
+        <v>0.003539572469890118</v>
       </c>
       <c r="C38" s="1">
         <v>4</v>
